--- a/MAW_Guidebook/MAW_4_5_Artefaktwaffen_DPS_Survival.xlsx
+++ b/MAW_Guidebook/MAW_4_5_Artefaktwaffen_DPS_Survival.xlsx
@@ -132,7 +132,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="58">
+  <x:cellXfs count="59">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -239,6 +239,9 @@
     <x:xf numFmtId="202" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -247,7 +250,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MAWDPS" displayName="MAWDPS" ref="A11:AJ62" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MAWDPS" displayName="MAWDPS" ref="A11:AJ63" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="36">
     <x:tableColumn id="1" name="Rang"/>
     <x:tableColumn id="2" name="Waffe / Artefakt"/>
@@ -291,7 +294,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MAWSurvival" displayName="MAWSurvival" ref="A11:AJ62" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MAWSurvival" displayName="MAWSurvival" ref="A11:AJ63" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="36">
     <x:tableColumn id="1" name="Rang"/>
     <x:tableColumn id="2" name="Waffe / Artefakt"/>
@@ -569,7 +572,7 @@
   <x:sheetData>
     <x:row r="1" ht="37" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>MAW 4.5  |  BEST OF DPS</x:v>
+        <x:v>MAW 4.5  |  BEST OF DPS · Stand: Release-Tag 4.5</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -586,7 +589,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="9" t="str">
-        <x:v>51 Artefakt-/Reliktwaffen · MM6/7/8 Merge · 2H/1H, Speere, Maces, Staffs, Dolche, Bögen und Armbrust</x:v>
+        <x:v>52 Artefakt-/Reliktwaffen · MM6/7/8 Merge · 2H/1H, Speere, Maces, Staffs, Dolche, Bögen und Armbrüste</x:v>
       </x:c>
       <x:c r="B2" s="9"/>
       <x:c r="C2" s="9"/>
@@ -618,6 +621,23 @@
       <x:c r="L3" s="13"/>
       <x:c r="M3" s="13"/>
     </x:row>
+    <x:row r="4" ht="33" customHeight="1">
+      <x:c r="A4" s="58" t="str">
+        <x:v>Stand: Werte, Formeln und Quellenlinks beziehen sich auf den Release-Tag 4.5 von MAW. Im aktuellen main ist das Artefaktsystem umgebaut (Scripts/Modules/MawCore/Artifacts.lua) – dort gelten andere Werte. Korrektur 24.10.2026: Der Resistenzterm mit Gewicht 1/8 ist die schwächste der sechs Resistenzen (zzMaw-Stats.lua, Damage-Kind 12), nicht Spirit. Korrektur 24.10.2026 (2): DPS neu nach Lua-Modell, Texte gegen Lua geprüft, Ania Selving ergänzt.</x:v>
+      </x:c>
+      <x:c r="B4" s="58"/>
+      <x:c r="C4" s="58"/>
+      <x:c r="D4" s="58"/>
+      <x:c r="E4" s="58"/>
+      <x:c r="F4" s="58"/>
+      <x:c r="G4" s="58"/>
+      <x:c r="H4" s="58"/>
+      <x:c r="I4" s="58"/>
+      <x:c r="J4" s="58"/>
+      <x:c r="K4" s="58"/>
+      <x:c r="L4" s="58"/>
+      <x:c r="M4" s="58"/>
+    </x:row>
     <x:row r="5" ht="22" customHeight="1">
       <x:c r="A5" s="16" t="str">
         <x:v>Basis-HP</x:v>
@@ -684,7 +704,7 @@
     </x:row>
     <x:row r="7" ht="29" customHeight="1">
       <x:c r="A7" s="23" t="str">
-        <x:v>* Nur Vitality-Parameter (grün) sind editierbar gedacht. HP/Endurance = 5 ist ein transparenter Szenario-Annahmewert, KEINE bestätigte Spielkonstante. DPS bleibt Benchmark (Lv100 / 20 GM).</x:v>
+        <x:v>* Nur die grünen Parameter sind zum Ändern gedacht. HP je Endurance = 5 ist eine Annahme: Im Code gilt HP = HPFactor·⌊End/5⌋ + maxHP·End/1000 (×Bodybuilding), also klassenabhängig (zzMaw-Items.lua:3549-3570, Tag 4.5).</x:v>
       </x:c>
       <x:c r="B7" s="23"/>
       <x:c r="C7" s="23"/>
@@ -738,6 +758,23 @@
       <x:c r="L9" s="36"/>
       <x:c r="M9" s="36"/>
     </x:row>
+    <x:row r="10" ht="33" customHeight="1">
+      <x:c r="A10" s="58" t="str">
+        <x:v>DPS-Modell: Nachbildung der MAW-Tooltip-DPS (calcPowerVitality, zzMaw-Stats.lua, Tag 4.5) für eine Modellfigur Lv 100, Waffen-Skill GM 20, Armsmaster GM 20, Basiswerte 100, Mensch ohne Klassenboni, eine Waffe ohne Schild, Monster-Lv 100. Ohne Element-/Zusatzschaden (am Tag 4.5 genullt), ohne Speer-Shred und Buffs. Rassengebundene Waffen (Elderaxe, Elfbane, Lightning Crossbow) ohne Rassenbonus. Engine-Annahmen: Might- und Accuracy-Grundeffekt, Bow-Skill-Addition. Artefakte ohne Ladungen angenommen (MaxCharges = 0, zzMaw-Items.lua:3220-3235). ModAttackDelay (Puck/Merlin/Percival) enthalten.</x:v>
+      </x:c>
+      <x:c r="B10" s="58"/>
+      <x:c r="C10" s="58"/>
+      <x:c r="D10" s="58"/>
+      <x:c r="E10" s="58"/>
+      <x:c r="F10" s="58"/>
+      <x:c r="G10" s="58"/>
+      <x:c r="H10" s="58"/>
+      <x:c r="I10" s="58"/>
+      <x:c r="J10" s="58"/>
+      <x:c r="K10" s="58"/>
+      <x:c r="L10" s="58"/>
+      <x:c r="M10" s="58"/>
+    </x:row>
     <x:row r="11" ht="34" customHeight="1">
       <x:c r="A11" s="40" t="str">
         <x:v>Rang</x:v>
@@ -848,54 +885,54 @@
         <x:v>Originalschaden</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="49" customHeight="1">
+    <x:row r="12" ht="66" customHeight="1">
       <x:c r="A12" s="44" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B12" s="44" t="str">
-        <x:v>Conan</x:v>
+        <x:v>Ania Selving</x:v>
       </x:c>
       <x:c r="C12" s="44" t="str">
-        <x:v>2H-Axt</x:v>
+        <x:v>Armbrust</x:v>
       </x:c>
       <x:c r="D12" s="44" t="str">
-        <x:v>MM6</x:v>
+        <x:v>MM7</x:v>
       </x:c>
       <x:c r="E12" s="50" t="n">
         <x:f>ROUND(X12*Y12,0)</x:f>
-        <x:v>1016</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="F12" s="51" t="n">
-        <x:f>ROUND(($B$5+N12*$H$5+W12)/(1-(AH12/2+(AA12+AB12+AC12+AD12+AE12+AF12)/16+AG12/8)),0)</x:f>
-        <x:v>3842</x:v>
+        <x:f>ROUND(($B$5+N12*$H$5+W12)/(1-(AH12/2+(AA12+AB12+AC12+AD12+AE12+AF12)/16+MIN(AA12:AF12)/8)),0)</x:f>
+        <x:v>3485</x:v>
       </x:c>
       <x:c r="G12" s="51" t="n">
         <x:f>F12-$B$8</x:f>
-        <x:v>0</x:v>
+        <x:v>-357</x:v>
       </x:c>
       <x:c r="H12" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I12" s="44" t="str">
-        <x:v>+150 Accuracy (MAW, auf Level 100: +187,5); verbessert Treffer und Kritschaden.</x:v>
+        <x:v>+150 Accuracy, −25 AC vor Levelskalierung.</x:v>
       </x:c>
       <x:c r="J12" s="44" t="str">
-        <x:v>Verdoppelt Treffer gegen Drachen und Dämonen; geskripteter zusätzlicher Treffer-Schaden von 10, skaliert mit Level.</x:v>
+        <x:v>Bow-Skill +5 vor Levelskalierung (Level 100: +6) und sehr hohe Accuracy; kein zusätzlicher Trefferproc.</x:v>
       </x:c>
       <x:c r="K12" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L12" s="44" t="str">
-        <x:v>Slayer ×2 und geskripteter Zusatzschaden nicht im phys. DPS enthalten.</x:v>
+        <x:v>Skillbonus in Modell-DPS.</x:v>
       </x:c>
       <x:c r="M12" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
       </x:c>
       <x:c r="N12" s="54" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O12" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>-31.25</x:v>
       </x:c>
       <x:c r="P12" s="54" t="n">
         <x:v>0</x:v>
@@ -922,7 +959,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X12" s="44" t="n">
-        <x:v>1016</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="Y12" s="44" t="n">
         <x:v>1</x:v>
@@ -960,57 +997,58 @@
       </x:c>
       <x:c r="AH12" s="56" t="n">
         <x:f>1-((5+$J$5*2)/(10+$J$5*2+MAX(0,$D$5+O12)))*(1/(1+MAX(0,$D$5+O12)/(90+$J$5*0.25)))</x:f>
-        <x:v>0.6462865716429107</x:v>
+        <x:v>0.5397333821420944</x:v>
       </x:c>
       <x:c r="AI12" s="44" t="str">
-        <x:v>Skript + Text</x:v>
+        <x:v>MAW-Stats + MAW-Skills; ITEMS.txt-Equip-Stat lautet "Bow" statt "Missile" (Datenauffälligkeit)</x:v>
       </x:c>
       <x:c r="AJ12" s="44" t="str">
-        <x:v>10d10+20</x:v>
+        <x:v>5d2+12</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="49" customHeight="1">
+    <x:row r="13" ht="100" customHeight="1">
       <x:c r="A13" s="44" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B13" s="44" t="str">
-        <x:v>Volcano</x:v>
+        <x:v>Longseeker</x:v>
       </x:c>
       <x:c r="C13" s="44" t="str">
-        <x:v>2H-Axt</x:v>
+        <x:v>Bogen</x:v>
       </x:c>
       <x:c r="D13" s="44" t="str">
         <x:v>MM8</x:v>
       </x:c>
       <x:c r="E13" s="50" t="n">
         <x:f>ROUND(X13*Y13,0)</x:f>
-        <x:v>891</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="F13" s="51" t="n">
-        <x:f>ROUND(($B$5+N13*$H$5+W13)/(1-(AH13/2+(AA13+AB13+AC13+AD13+AE13+AF13)/16+AG13/8)),0)</x:f>
-        <x:v>3986</x:v>
+        <x:f>ROUND(($B$5+N13*$H$5+W13)/(1-(AH13/2+(AA13+AB13+AC13+AD13+AE13+AF13)/16+MIN(AA13:AF13)/8)),0)</x:f>
+        <x:v>3842</x:v>
       </x:c>
       <x:c r="G13" s="51" t="n">
         <x:f>F13-$B$8</x:f>
-        <x:v>144</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H13" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I13" s="44" t="str">
-        <x:v>+100 Feuerresistenz vor Skalierung; bei Level 100 +125.</x:v>
+        <x:v>+50 Accuracy vor Skalierung; kein defensiver Stat.</x:v>
       </x:c>
       <x:c r="J13" s="44" t="str">
-        <x:v>Feuer-Zusatzschaden pro Treffer; besser bei Gegnern mit niedriger Feuerresistenz.</x:v>
+        <x:v>Swift laut Itemtext (MM8-Engine/Itemtext, nicht in Lua), vom MAW-Angriffstempo nicht berücksichtigt (zzMAW-Skills.lua:185 setzt t.Result neu, Swift nur über Enchant 41/59); Bow-Skill +4 vor Levelskalierung (Level 100: +5).</x:v>
       </x:c>
       <x:c r="K13" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L13" s="44" t="str">
-        <x:v>Elementarschaden nicht eingerechnet.</x:v>
+        <x:v>Swift nicht in DPS (wirkt am Tag 4.5 nicht).</x:v>
       </x:c>
       <x:c r="M13" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMAW-Skills.lua</x:v>
       </x:c>
       <x:c r="N13" s="54" t="n">
         <x:v>0</x:v>
@@ -1019,7 +1057,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="P13" s="54" t="n">
-        <x:v>125</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Q13" s="54" t="n">
         <x:v>0</x:v>
@@ -1043,7 +1081,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X13" s="44" t="n">
-        <x:v>891</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="Y13" s="44" t="n">
         <x:v>1</x:v>
@@ -1053,7 +1091,7 @@
       </x:c>
       <x:c r="AA13" s="56" t="n">
         <x:f>IF($F$5+P13&gt;=65000,1,1-1/(1+($F$5+P13)/(60+$J$5*0.5)))</x:f>
-        <x:v>0.6140350877192982</x:v>
+        <x:v>0.3125</x:v>
       </x:c>
       <x:c r="AB13" s="56" t="n">
         <x:f>IF($F$5+Q13&gt;=65000,1,1-1/(1+($F$5+Q13)/(60+$J$5*0.5)))</x:f>
@@ -1084,57 +1122,58 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI13" s="44" t="str">
-        <x:v>Text + MAW-Stats</x:v>
+        <x:v>Itemtext + MAW-Skills</x:v>
       </x:c>
       <x:c r="AJ13" s="44" t="str">
-        <x:v>10d8+25</x:v>
+        <x:v>6d2+14</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="49" customHeight="1">
+    <x:row r="14" ht="100" customHeight="1">
       <x:c r="A14" s="44" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B14" s="44" t="str">
-        <x:v>Hercules</x:v>
+        <x:v>Ghoulsbane</x:v>
       </x:c>
       <x:c r="C14" s="44" t="str">
-        <x:v>2H-Schwert</x:v>
+        <x:v>2H-Axt</x:v>
       </x:c>
       <x:c r="D14" s="44" t="str">
-        <x:v>MM6</x:v>
+        <x:v>MM7</x:v>
       </x:c>
       <x:c r="E14" s="50" t="n">
         <x:f>ROUND(X14*Y14,0)</x:f>
-        <x:v>885</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="F14" s="51" t="n">
-        <x:f>ROUND(($B$5+N14*$H$5+W14)/(1-(AH14/2+(AA14+AB14+AC14+AD14+AE14+AF14)/16+AG14/8)),0)</x:f>
-        <x:v>4562</x:v>
+        <x:f>ROUND(($B$5+N14*$H$5+W14)/(1-(AH14/2+(AA14+AB14+AC14+AD14+AE14+AF14)/16+MIN(AA14:AF14)/8)),0)</x:f>
+        <x:v>3842</x:v>
       </x:c>
       <x:c r="G14" s="51" t="n">
         <x:f>F14-$B$8</x:f>
-        <x:v>720</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H14" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I14" s="44" t="str">
-        <x:v>+100 Might, +60 Endurance, −30 Intellect vor MAW-Levelskalierung.</x:v>
+        <x:v>Immunität gegen Paralyse laut ExtraArtifacts.</x:v>
       </x:c>
       <x:c r="J14" s="44" t="str">
-        <x:v>Starkes Zweihandschwert; hohes Might steigert physischen Schaden.</x:v>
+        <x:v>Geskripteter Feuerschaden 15 Basis je Treffer (×2 bei Level 100), gegen Untote verdoppelt – nur der Zusatzschaden, nicht der Waffentreffer; am Tag 4.5 von zzMaw_Legendaries.lua:19 (t.Result=0) wieder genullt.</x:v>
       </x:c>
       <x:c r="K14" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L14" s="44" t="str">
-        <x:v>Keine zusätzlichen Trefferprocs modelliert.</x:v>
+        <x:v>Undead-Slaying und Feuerschaden nicht enthalten.</x:v>
       </x:c>
       <x:c r="M14" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N14" s="54" t="n">
-        <x:v>75</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="O14" s="54" t="n">
         <x:v>0</x:v>
@@ -1164,7 +1203,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X14" s="44" t="n">
-        <x:v>885</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="Y14" s="44" t="n">
         <x:v>1</x:v>
@@ -1205,60 +1244,60 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI14" s="44" t="str">
-        <x:v>MAW-Stats</x:v>
+        <x:v>Skript</x:v>
       </x:c>
       <x:c r="AJ14" s="44" t="str">
-        <x:v>6d12+20</x:v>
+        <x:v>1d18+30</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="49" customHeight="1">
+    <x:row r="15" ht="50" customHeight="1">
       <x:c r="A15" s="44" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B15" s="44" t="str">
-        <x:v>Amuck</x:v>
+        <x:v>Hercules</x:v>
       </x:c>
       <x:c r="C15" s="44" t="str">
-        <x:v>2H-Axt</x:v>
+        <x:v>2H-Schwert</x:v>
       </x:c>
       <x:c r="D15" s="44" t="str">
-        <x:v>MM7</x:v>
+        <x:v>MM6</x:v>
       </x:c>
       <x:c r="E15" s="50" t="n">
         <x:f>ROUND(X15*Y15,0)</x:f>
-        <x:v>851</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="F15" s="51" t="n">
-        <x:f>ROUND(($B$5+N15*$H$5+W15)/(1-(AH15/2+(AA15+AB15+AC15+AD15+AE15+AF15)/16+AG15/8)),0)</x:f>
-        <x:v>4773</x:v>
+        <x:f>ROUND(($B$5+N15*$H$5+W15)/(1-(AH15/2+(AA15+AB15+AC15+AD15+AE15+AF15)/16+MIN(AA15:AF15)/8)),0)</x:f>
+        <x:v>4562</x:v>
       </x:c>
       <x:c r="G15" s="51" t="n">
         <x:f>F15-$B$8</x:f>
-        <x:v>931</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="H15" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I15" s="44" t="str">
-        <x:v>+100 Might, +100 Endurance und −15 AC laut Gegenstandsbonus (je mit Levelskalierung).</x:v>
+        <x:v>+100 Might, +60 Endurance, −30 Intellect vor MAW-Levelskalierung.</x:v>
       </x:c>
       <x:c r="J15" s="44" t="str">
-        <x:v>Hoher physischer Grundschaden; kein geskripteter Trefferproc gefunden.</x:v>
+        <x:v>Starkes Zweihandschwert; hohes Might steigert physischen Schaden.</x:v>
       </x:c>
       <x:c r="K15" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L15" s="44" t="str">
-        <x:v>Keine besonderen Schadensprocs in Benchmark.</x:v>
+        <x:v>Keine zusätzlichen Trefferprocs modelliert.</x:v>
       </x:c>
       <x:c r="M15" s="44" t="str">
         <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
       </x:c>
       <x:c r="N15" s="54" t="n">
-        <x:v>125</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="O15" s="54" t="n">
-        <x:v>-18.75</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="P15" s="54" t="n">
         <x:v>0</x:v>
@@ -1285,7 +1324,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X15" s="44" t="n">
-        <x:v>851</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="Y15" s="44" t="n">
         <x:v>1</x:v>
@@ -1323,34 +1362,34 @@
       </x:c>
       <x:c r="AH15" s="56" t="n">
         <x:f>1-((5+$J$5*2)/(10+$J$5*2+MAX(0,$D$5+O15)))*(1/(1+MAX(0,$D$5+O15)/(90+$J$5*0.25)))</x:f>
-        <x:v>0.5875454470900194</x:v>
+        <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI15" s="44" t="str">
         <x:v>MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ15" s="44" t="str">
-        <x:v>8d9+16</x:v>
+        <x:v>4d5+16</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="49" customHeight="1">
+    <x:row r="16" ht="100" customHeight="1">
       <x:c r="A16" s="44" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B16" s="44" t="str">
-        <x:v>Finality</x:v>
+        <x:v>Percival</x:v>
       </x:c>
       <x:c r="C16" s="44" t="str">
-        <x:v>2H-Schwert</x:v>
+        <x:v>Bogen</x:v>
       </x:c>
       <x:c r="D16" s="44" t="str">
-        <x:v>MM8</x:v>
+        <x:v>MM6</x:v>
       </x:c>
       <x:c r="E16" s="50" t="n">
         <x:f>ROUND(X16*Y16,0)</x:f>
-        <x:v>851</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="F16" s="51" t="n">
-        <x:f>ROUND(($B$5+N16*$H$5+W16)/(1-(AH16/2+(AA16+AB16+AC16+AD16+AE16+AF16)/16+AG16/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N16*$H$5+W16)/(1-(AH16/2+(AA16+AB16+AC16+AD16+AE16+AF16)/16+MIN(AA16:AF16)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G16" s="51" t="n">
@@ -1361,19 +1400,20 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I16" s="44" t="str">
-        <x:v>+120 Accuracy, −20 Speed vor Levelskalierung.</x:v>
+        <x:v>+40 Speed vor Skalierung; Bonus-Erholung reduziert Schaden nicht direkt.</x:v>
       </x:c>
       <x:c r="J16" s="44" t="str">
-        <x:v>Feuerschaden pro Treffer und Slow (verlangsamt das Ziel).</x:v>
+        <x:v>Fireball (Zauber 6) beim Pfeiltreffer (geskriptet), besonders gegen Gruppen; Angriffsverzögerung −20 (ExtraArtifacts), effektiv ca. −10 %.</x:v>
       </x:c>
       <x:c r="K16" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L16" s="44" t="str">
-        <x:v>Feuer und Slow nicht in DPS.</x:v>
+        <x:v>Angriffsverzögerung −20 (×0,9, ExtraArtifacts.lua:269) ist im Modell-DPS enthalten; Fireball-Explosion beim Pfeiltreffer nicht.</x:v>
       </x:c>
       <x:c r="M16" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
       </x:c>
       <x:c r="N16" s="54" t="n">
         <x:v>0</x:v>
@@ -1406,7 +1446,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X16" s="44" t="n">
-        <x:v>851</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="Y16" s="44" t="n">
         <x:v>1</x:v>
@@ -1447,31 +1487,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI16" s="44" t="str">
-        <x:v>Text + MAW-Stats</x:v>
+        <x:v>Skript + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ16" s="44" t="str">
-        <x:v>8d8+25</x:v>
+        <x:v>6d2+13</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="49" customHeight="1">
+    <x:row r="17" ht="100" customHeight="1">
       <x:c r="A17" s="44" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B17" s="44" t="str">
-        <x:v>Iron Feather</x:v>
+        <x:v>Finality</x:v>
       </x:c>
       <x:c r="C17" s="44" t="str">
         <x:v>2H-Schwert</x:v>
       </x:c>
       <x:c r="D17" s="44" t="str">
-        <x:v>MM7</x:v>
+        <x:v>MM8</x:v>
       </x:c>
       <x:c r="E17" s="50" t="n">
         <x:f>ROUND(X17*Y17,0)</x:f>
-        <x:v>766</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="F17" s="51" t="n">
-        <x:f>ROUND(($B$5+N17*$H$5+W17)/(1-(AH17/2+(AA17+AB17+AC17+AD17+AE17+AF17)/16+AG17/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N17*$H$5+W17)/(1-(AH17/2+(AA17+AB17+AC17+AD17+AE17+AF17)/16+MIN(AA17:AF17)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G17" s="51" t="n">
@@ -1482,19 +1522,20 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I17" s="44" t="str">
-        <x:v>+80 Might vor Levelskalierung.</x:v>
+        <x:v>+120 Accuracy, −20 Speed vor Levelskalierung.</x:v>
       </x:c>
       <x:c r="J17" s="44" t="str">
-        <x:v>Geskripteter zusätzlicher Luft-/Elektrizitätsschaden von 15 Basis je Treffer.</x:v>
+        <x:v>Feuerschaden 20–40 und Slow (verlangsamt das Ziel) laut Itemtext (MM8-Engine/Itemtext, nicht in Lua); Feuerschaden vermutlich wirkungslos, da zzMaw_Legendaries.lua:19 ItemAdditionalDamage am Tag 4.5 auf 0 setzt.</x:v>
       </x:c>
       <x:c r="K17" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L17" s="44" t="str">
-        <x:v>Luftschaden nicht in DPS.</x:v>
+        <x:v>Feuer und Slow nicht in DPS.</x:v>
       </x:c>
       <x:c r="M17" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N17" s="54" t="n">
         <x:v>0</x:v>
@@ -1527,7 +1568,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X17" s="44" t="n">
-        <x:v>766</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="Y17" s="44" t="n">
         <x:v>1</x:v>
@@ -1568,31 +1609,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI17" s="44" t="str">
-        <x:v>Skript</x:v>
+        <x:v>Text + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ17" s="44" t="str">
-        <x:v>9d10+25</x:v>
+        <x:v>4d5+19</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="49" customHeight="1">
+    <x:row r="18" ht="149" customHeight="1">
       <x:c r="A18" s="44" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B18" s="44" t="str">
-        <x:v>Longseeker</x:v>
+        <x:v>Ullyses</x:v>
       </x:c>
       <x:c r="C18" s="44" t="str">
         <x:v>Bogen</x:v>
       </x:c>
       <x:c r="D18" s="44" t="str">
-        <x:v>MM8</x:v>
+        <x:v>MM7</x:v>
       </x:c>
       <x:c r="E18" s="50" t="n">
         <x:f>ROUND(X18*Y18,0)</x:f>
-        <x:v>736</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="F18" s="51" t="n">
-        <x:f>ROUND(($B$5+N18*$H$5+W18)/(1-(AH18/2+(AA18+AB18+AC18+AD18+AE18+AF18)/16+AG18/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N18*$H$5+W18)/(1-(AH18/2+(AA18+AB18+AC18+AD18+AE18+AF18)/16+MIN(AA18:AF18)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G18" s="51" t="n">
@@ -1603,19 +1644,21 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I18" s="44" t="str">
-        <x:v>+50 Accuracy vor Skalierung; kein defensiver Stat.</x:v>
+        <x:v>+80 Accuracy vor Skalierung.</x:v>
       </x:c>
       <x:c r="J18" s="44" t="str">
-        <x:v>Schneller Bogen laut Itemtext, zusätzlich Bow-Skill +4 (MAW: +5 bei Level 100).</x:v>
+        <x:v>Geskripteter Wasserschaden 15 Basis je Treffer (×2 bei Level 100), Eisgeschoss als Projektil; am Tag 4.5 von zzMaw_Legendaries.lua:19 (t.Result=0) wieder genullt.</x:v>
       </x:c>
       <x:c r="K18" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L18" s="44" t="str">
-        <x:v>Swift-Auswirkung nicht in DPS.</x:v>
+        <x:v>Wasserschaden nicht in DPS.</x:v>
       </x:c>
       <x:c r="M18" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N18" s="54" t="n">
         <x:v>0</x:v>
@@ -1648,7 +1691,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X18" s="44" t="n">
-        <x:v>736</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="Y18" s="44" t="n">
         <x:v>1</x:v>
@@ -1689,60 +1732,60 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI18" s="44" t="str">
-        <x:v>Itemtext + MAW-Skills</x:v>
+        <x:v>Skript + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ18" s="44" t="str">
-        <x:v>15d2+14</x:v>
+        <x:v>6d2+14</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="49" customHeight="1">
+    <x:row r="19" ht="50" customHeight="1">
       <x:c r="A19" s="44" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B19" s="44" t="str">
-        <x:v>Elfbane</x:v>
+        <x:v>Amuck</x:v>
       </x:c>
       <x:c r="C19" s="44" t="str">
-        <x:v>2H-Schwert</x:v>
+        <x:v>2H-Axt</x:v>
       </x:c>
       <x:c r="D19" s="44" t="str">
         <x:v>MM7</x:v>
       </x:c>
       <x:c r="E19" s="50" t="n">
         <x:f>ROUND(X19*Y19,0)</x:f>
-        <x:v>685</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="F19" s="51" t="n">
-        <x:f>ROUND(($B$5+N19*$H$5+W19)/(1-(AH19/2+(AA19+AB19+AC19+AD19+AE19+AF19)/16+AG19/8)),0)</x:f>
-        <x:v>3842</x:v>
+        <x:f>ROUND(($B$5+N19*$H$5+W19)/(1-(AH19/2+(AA19+AB19+AC19+AD19+AE19+AF19)/16+MIN(AA19:AF19)/8)),0)</x:f>
+        <x:v>4773</x:v>
       </x:c>
       <x:c r="G19" s="51" t="n">
         <x:f>F19-$B$8</x:f>
-        <x:v>0</x:v>
+        <x:v>931</x:v>
       </x:c>
       <x:c r="H19" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I19" s="44" t="str">
-        <x:v>+100 Speed vor Levelskalierung; Schutz-/Schildbonus nicht in Vitality-Modell enthalten.</x:v>
+        <x:v>+100 Might, +100 Endurance und −15 AC laut Gegenstandsbonus (je mit Levelskalierung).</x:v>
       </x:c>
       <x:c r="J19" s="44" t="str">
-        <x:v>Doppelter Trefferschaden gegen Elfen; zusätzlich Schutzzauber laut Itemtext.</x:v>
+        <x:v>Hoher physischer Grundschaden; kein geskripteter Trefferproc gefunden.</x:v>
       </x:c>
       <x:c r="K19" s="44" t="str">
-        <x:v>Nur Goblins (laut ExtraArtifacts).</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="L19" s="44" t="str">
-        <x:v>Elf-Slaying und Shielding nicht in DPS.</x:v>
+        <x:v>Keine besonderen Schadensprocs in Benchmark.</x:v>
       </x:c>
       <x:c r="M19" s="44" t="str">
         <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
       </x:c>
       <x:c r="N19" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="O19" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>-18.75</x:v>
       </x:c>
       <x:c r="P19" s="54" t="n">
         <x:v>0</x:v>
@@ -1769,7 +1812,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X19" s="44" t="n">
-        <x:v>685</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="Y19" s="44" t="n">
         <x:v>1</x:v>
@@ -1807,57 +1850,59 @@
       </x:c>
       <x:c r="AH19" s="56" t="n">
         <x:f>1-((5+$J$5*2)/(10+$J$5*2+MAX(0,$D$5+O19)))*(1/(1+MAX(0,$D$5+O19)/(90+$J$5*0.25)))</x:f>
-        <x:v>0.6462865716429107</x:v>
+        <x:v>0.5875454470900194</x:v>
       </x:c>
       <x:c r="AI19" s="44" t="str">
-        <x:v>Skript + MAW-Stats</x:v>
+        <x:v>MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ19" s="44" t="str">
-        <x:v>8d8+32</x:v>
+        <x:v>3d7+15</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="49" customHeight="1">
+    <x:row r="20" ht="149" customHeight="1">
       <x:c r="A20" s="44" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B20" s="44" t="str">
-        <x:v>Ghoulsbane</x:v>
+        <x:v>Artemis</x:v>
       </x:c>
       <x:c r="C20" s="44" t="str">
-        <x:v>2H-Axt</x:v>
+        <x:v>Bogen</x:v>
       </x:c>
       <x:c r="D20" s="44" t="str">
-        <x:v>MM7</x:v>
+        <x:v>MM6</x:v>
       </x:c>
       <x:c r="E20" s="50" t="n">
         <x:f>ROUND(X20*Y20,0)</x:f>
-        <x:v>683</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="F20" s="51" t="n">
-        <x:f>ROUND(($B$5+N20*$H$5+W20)/(1-(AH20/2+(AA20+AB20+AC20+AD20+AE20+AF20)/16+AG20/8)),0)</x:f>
-        <x:v>3842</x:v>
+        <x:f>ROUND(($B$5+N20*$H$5+W20)/(1-(AH20/2+(AA20+AB20+AC20+AD20+AE20+AF20)/16+MIN(AA20:AF20)/8)),0)</x:f>
+        <x:v>3519</x:v>
       </x:c>
       <x:c r="G20" s="51" t="n">
         <x:f>F20-$B$8</x:f>
-        <x:v>0</x:v>
+        <x:v>-323</x:v>
       </x:c>
       <x:c r="H20" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I20" s="44" t="str">
-        <x:v>Immunität gegen Paralyse laut ExtraArtifacts.</x:v>
+        <x:v>−20 auf vier Elementarresistenzen vor Skalierung; schlechtere Abwehr.</x:v>
       </x:c>
       <x:c r="J20" s="44" t="str">
-        <x:v>Untote erleiden doppelten Trefferschaden; zusätzlich geskripteter Feuerschaden (15 Basis je Treffer).</x:v>
+        <x:v>Geskripteter Luft-/Elektrizitätsschaden 20 Basis je Treffer (×2 bei Level 100); am Tag 4.5 von zzMaw_Legendaries.lua:19 (t.Result=0) wieder genullt.</x:v>
       </x:c>
       <x:c r="K20" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L20" s="44" t="str">
-        <x:v>Undead-Slaying und Feuerschaden nicht enthalten.</x:v>
+        <x:v>Luftschaden nicht in DPS.</x:v>
       </x:c>
       <x:c r="M20" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N20" s="54" t="n">
         <x:v>0</x:v>
@@ -1866,16 +1911,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="P20" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>-25</x:v>
       </x:c>
       <x:c r="Q20" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>-25</x:v>
       </x:c>
       <x:c r="R20" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>-25</x:v>
       </x:c>
       <x:c r="S20" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>-25</x:v>
       </x:c>
       <x:c r="T20" s="54" t="n">
         <x:v>0</x:v>
@@ -1890,7 +1935,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X20" s="44" t="n">
-        <x:v>683</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="Y20" s="44" t="n">
         <x:v>1</x:v>
@@ -1900,19 +1945,19 @@
       </x:c>
       <x:c r="AA20" s="56" t="n">
         <x:f>IF($F$5+P20&gt;=65000,1,1-1/(1+($F$5+P20)/(60+$J$5*0.5)))</x:f>
-        <x:v>0.3125</x:v>
+        <x:v>0.18518518518518523</x:v>
       </x:c>
       <x:c r="AB20" s="56" t="n">
         <x:f>IF($F$5+Q20&gt;=65000,1,1-1/(1+($F$5+Q20)/(60+$J$5*0.5)))</x:f>
-        <x:v>0.3125</x:v>
+        <x:v>0.18518518518518523</x:v>
       </x:c>
       <x:c r="AC20" s="56" t="n">
         <x:f>IF($F$5+R20&gt;=65000,1,1-1/(1+($F$5+R20)/(60+$J$5*0.5)))</x:f>
-        <x:v>0.3125</x:v>
+        <x:v>0.18518518518518523</x:v>
       </x:c>
       <x:c r="AD20" s="56" t="n">
         <x:f>IF($F$5+S20&gt;=65000,1,1-1/(1+($F$5+S20)/(60+$J$5*0.5)))</x:f>
-        <x:v>0.3125</x:v>
+        <x:v>0.18518518518518523</x:v>
       </x:c>
       <x:c r="AE20" s="56" t="n">
         <x:f>IF($F$5+T20&gt;=65000,1,1-1/(1+($F$5+T20)/(60+$J$5*0.5)))</x:f>
@@ -1931,51 +1976,51 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI20" s="44" t="str">
-        <x:v>Skript</x:v>
+        <x:v>Skript + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ20" s="44" t="str">
-        <x:v>6d9+19</x:v>
+        <x:v>6d2+15</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="49" customHeight="1">
+    <x:row r="21" ht="50" customHeight="1">
       <x:c r="A21" s="44" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B21" s="44" t="str">
-        <x:v>Wallace</x:v>
+        <x:v>Tournament Bow</x:v>
       </x:c>
       <x:c r="C21" s="44" t="str">
-        <x:v>1H-Schwert</x:v>
+        <x:v>Bogen</x:v>
       </x:c>
       <x:c r="D21" s="44" t="str">
-        <x:v>MM7</x:v>
+        <x:v>MM8</x:v>
       </x:c>
       <x:c r="E21" s="50" t="n">
         <x:f>ROUND(X21*Y21,0)</x:f>
-        <x:v>649</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="F21" s="51" t="n">
-        <x:f>ROUND(($B$5+N21*$H$5+W21)/(1-(AH21/2+(AA21+AB21+AC21+AD21+AE21+AF21)/16+AG21/8)),0)</x:f>
-        <x:v>3842</x:v>
+        <x:f>ROUND(($B$5+N21*$H$5+W21)/(1-(AH21/2+(AA21+AB21+AC21+AD21+AE21+AF21)/16+MIN(AA21:AF21)/8)),0)</x:f>
+        <x:v>3562</x:v>
       </x:c>
       <x:c r="G21" s="51" t="n">
         <x:f>F21-$B$8</x:f>
-        <x:v>0</x:v>
+        <x:v>-280</x:v>
       </x:c>
       <x:c r="H21" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I21" s="44" t="str">
-        <x:v>+40 Personality vor Levelskalierung, kaum direkter Vitality-Effekt.</x:v>
+        <x:v>+100 Accuracy, −20 AC vor Levelskalierung (MAW-Code, wie Itemtext).</x:v>
       </x:c>
       <x:c r="J21" s="44" t="str">
-        <x:v>+10 Armsmaster (MAW bei Level 100 +13): steigert physischen Schaden und Tempo.</x:v>
+        <x:v>Bow-Skill +4 vor Levelskalierung (Level 100: +5; Itemtext nennt +5) und hohe Accuracy; kein zusätzlicher Trefferproc.</x:v>
       </x:c>
       <x:c r="K21" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L21" s="44" t="str">
-        <x:v>Skillbonus ist im Modell-DPS berücksichtigt.</x:v>
+        <x:v>Skillbonus in Modell-DPS.</x:v>
       </x:c>
       <x:c r="M21" s="44" t="str">
         <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
@@ -1984,7 +2029,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O21" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>-25</x:v>
       </x:c>
       <x:c r="P21" s="54" t="n">
         <x:v>0</x:v>
@@ -2011,7 +2056,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X21" s="44" t="n">
-        <x:v>649</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="Y21" s="44" t="n">
         <x:v>1</x:v>
@@ -2049,57 +2094,58 @@
       </x:c>
       <x:c r="AH21" s="56" t="n">
         <x:f>1-((5+$J$5*2)/(10+$J$5*2+MAX(0,$D$5+O21)))*(1/(1+MAX(0,$D$5+O21)/(90+$J$5*0.25)))</x:f>
-        <x:v>0.6462865716429107</x:v>
+        <x:v>0.5646352723915051</x:v>
       </x:c>
       <x:c r="AI21" s="44" t="str">
-        <x:v>MAW-Stats</x:v>
+        <x:v>MAW-Stats + MAW-Skills</x:v>
       </x:c>
       <x:c r="AJ21" s="44" t="str">
-        <x:v>5d4+30</x:v>
+        <x:v>6d2+14</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="49" customHeight="1">
+    <x:row r="22" ht="100" customHeight="1">
       <x:c r="A22" s="44" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="B22" s="44" t="str">
-        <x:v>Ullyses</x:v>
+        <x:v>Volcano</x:v>
       </x:c>
       <x:c r="C22" s="44" t="str">
-        <x:v>Bogen</x:v>
+        <x:v>2H-Axt</x:v>
       </x:c>
       <x:c r="D22" s="44" t="str">
-        <x:v>MM7</x:v>
+        <x:v>MM8</x:v>
       </x:c>
       <x:c r="E22" s="50" t="n">
         <x:f>ROUND(X22*Y22,0)</x:f>
-        <x:v>634</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="F22" s="51" t="n">
-        <x:f>ROUND(($B$5+N22*$H$5+W22)/(1-(AH22/2+(AA22+AB22+AC22+AD22+AE22+AF22)/16+AG22/8)),0)</x:f>
-        <x:v>3842</x:v>
+        <x:f>ROUND(($B$5+N22*$H$5+W22)/(1-(AH22/2+(AA22+AB22+AC22+AD22+AE22+AF22)/16+MIN(AA22:AF22)/8)),0)</x:f>
+        <x:v>3986</x:v>
       </x:c>
       <x:c r="G22" s="51" t="n">
         <x:f>F22-$B$8</x:f>
-        <x:v>0</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="H22" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I22" s="44" t="str">
-        <x:v>+80 Accuracy vor Skalierung.</x:v>
+        <x:v>+100 Feuerresistenz vor Skalierung; bei Level 100 +125.</x:v>
       </x:c>
       <x:c r="J22" s="44" t="str">
-        <x:v>Geskripteter Wasserschaden (+15 Basis) bei Treffer.</x:v>
+        <x:v>Feuerschaden 20–40 pro Treffer laut Itemtext (MM8-Engine/Itemtext, nicht in Lua); vermutlich wirkungslos, da zzMaw_Legendaries.lua:19 ItemAdditionalDamage am Tag 4.5 auf 0 setzt.</x:v>
       </x:c>
       <x:c r="K22" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L22" s="44" t="str">
-        <x:v>Wasserschaden nicht in DPS.</x:v>
+        <x:v>Elementarschaden nicht eingerechnet.</x:v>
       </x:c>
       <x:c r="M22" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N22" s="54" t="n">
         <x:v>0</x:v>
@@ -2108,7 +2154,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="P22" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="Q22" s="54" t="n">
         <x:v>0</x:v>
@@ -2132,7 +2178,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X22" s="44" t="n">
-        <x:v>634</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="Y22" s="44" t="n">
         <x:v>1</x:v>
@@ -2142,7 +2188,7 @@
       </x:c>
       <x:c r="AA22" s="56" t="n">
         <x:f>IF($F$5+P22&gt;=65000,1,1-1/(1+($F$5+P22)/(60+$J$5*0.5)))</x:f>
-        <x:v>0.3125</x:v>
+        <x:v>0.6140350877192982</x:v>
       </x:c>
       <x:c r="AB22" s="56" t="n">
         <x:f>IF($F$5+Q22&gt;=65000,1,1-1/(1+($F$5+Q22)/(60+$J$5*0.5)))</x:f>
@@ -2173,54 +2219,56 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI22" s="44" t="str">
-        <x:v>Skript</x:v>
+        <x:v>Text + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ22" s="44" t="str">
-        <x:v>10d4+14</x:v>
+        <x:v>3d7+19</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="49" customHeight="1">
+    <x:row r="23" ht="149" customHeight="1">
       <x:c r="A23" s="44" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B23" s="44" t="str">
-        <x:v>Artemis</x:v>
+        <x:v>Conan</x:v>
       </x:c>
       <x:c r="C23" s="44" t="str">
-        <x:v>Bogen</x:v>
+        <x:v>2H-Axt</x:v>
       </x:c>
       <x:c r="D23" s="44" t="str">
         <x:v>MM6</x:v>
       </x:c>
       <x:c r="E23" s="50" t="n">
         <x:f>ROUND(X23*Y23,0)</x:f>
-        <x:v>601</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F23" s="51" t="n">
-        <x:f>ROUND(($B$5+N23*$H$5+W23)/(1-(AH23/2+(AA23+AB23+AC23+AD23+AE23+AF23)/16+AG23/8)),0)</x:f>
-        <x:v>3620</x:v>
+        <x:f>ROUND(($B$5+N23*$H$5+W23)/(1-(AH23/2+(AA23+AB23+AC23+AD23+AE23+AF23)/16+MIN(AA23:AF23)/8)),0)</x:f>
+        <x:v>3842</x:v>
       </x:c>
       <x:c r="G23" s="51" t="n">
         <x:f>F23-$B$8</x:f>
-        <x:v>-222</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H23" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I23" s="44" t="str">
-        <x:v>−20 auf vier Elementarresistenzen vor Skalierung; schlechtere Abwehr.</x:v>
+        <x:v>+150 Accuracy (MAW, auf Level 100: +187,5); verbessert Treffer und Kritschaden.</x:v>
       </x:c>
       <x:c r="J23" s="44" t="str">
-        <x:v>Geskripteter Luft-/Elektrizitätsschaden (+20 Basis).</x:v>
+        <x:v>Geskripteter Zusatzschaden 10 Basis je Treffer (×2 bei Level 100), gegen Drachen/Dämonen verdoppelt – nur der Zusatzschaden, nicht der Waffentreffer; am Tag 4.5 von zzMaw_Legendaries.lua:19 (t.Result=0) wieder genullt.</x:v>
       </x:c>
       <x:c r="K23" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L23" s="44" t="str">
-        <x:v>Luftschaden nicht in DPS.</x:v>
+        <x:v>Zusatzschaden inkl. Slayer-Verdopplung nicht im phys. DPS (am Tag 4.5 ohnehin genullt).</x:v>
       </x:c>
       <x:c r="M23" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N23" s="54" t="n">
         <x:v>0</x:v>
@@ -2229,16 +2277,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="P23" s="54" t="n">
-        <x:v>-25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Q23" s="54" t="n">
-        <x:v>-25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="R23" s="54" t="n">
-        <x:v>-25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="S23" s="54" t="n">
-        <x:v>-25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="T23" s="54" t="n">
         <x:v>0</x:v>
@@ -2253,7 +2301,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X23" s="44" t="n">
-        <x:v>601</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="Y23" s="44" t="n">
         <x:v>1</x:v>
@@ -2263,19 +2311,19 @@
       </x:c>
       <x:c r="AA23" s="56" t="n">
         <x:f>IF($F$5+P23&gt;=65000,1,1-1/(1+($F$5+P23)/(60+$J$5*0.5)))</x:f>
-        <x:v>0.18518518518518523</x:v>
+        <x:v>0.3125</x:v>
       </x:c>
       <x:c r="AB23" s="56" t="n">
         <x:f>IF($F$5+Q23&gt;=65000,1,1-1/(1+($F$5+Q23)/(60+$J$5*0.5)))</x:f>
-        <x:v>0.18518518518518523</x:v>
+        <x:v>0.3125</x:v>
       </x:c>
       <x:c r="AC23" s="56" t="n">
         <x:f>IF($F$5+R23&gt;=65000,1,1-1/(1+($F$5+R23)/(60+$J$5*0.5)))</x:f>
-        <x:v>0.18518518518518523</x:v>
+        <x:v>0.3125</x:v>
       </x:c>
       <x:c r="AD23" s="56" t="n">
         <x:f>IF($F$5+S23&gt;=65000,1,1-1/(1+($F$5+S23)/(60+$J$5*0.5)))</x:f>
-        <x:v>0.18518518518518523</x:v>
+        <x:v>0.3125</x:v>
       </x:c>
       <x:c r="AE23" s="56" t="n">
         <x:f>IF($F$5+T23&gt;=65000,1,1-1/(1+($F$5+T23)/(60+$J$5*0.5)))</x:f>
@@ -2297,48 +2345,48 @@
         <x:v>Skript + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ23" s="44" t="str">
-        <x:v>12d3+15</x:v>
+        <x:v>3d7+14</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="49" customHeight="1">
+    <x:row r="24" ht="50" customHeight="1">
       <x:c r="A24" s="44" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B24" s="44" t="str">
-        <x:v>Terminus</x:v>
+        <x:v>Wallace</x:v>
       </x:c>
       <x:c r="C24" s="44" t="str">
         <x:v>1H-Schwert</x:v>
       </x:c>
       <x:c r="D24" s="44" t="str">
-        <x:v>MM8</x:v>
+        <x:v>MM7</x:v>
       </x:c>
       <x:c r="E24" s="50" t="n">
         <x:f>ROUND(X24*Y24,0)</x:f>
-        <x:v>574</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="F24" s="51" t="n">
-        <x:f>ROUND(($B$5+N24*$H$5+W24)/(1-(AH24/2+(AA24+AB24+AC24+AD24+AE24+AF24)/16+AG24/8)),0)</x:f>
-        <x:v>3986</x:v>
+        <x:f>ROUND(($B$5+N24*$H$5+W24)/(1-(AH24/2+(AA24+AB24+AC24+AD24+AE24+AF24)/16+MIN(AA24:AF24)/8)),0)</x:f>
+        <x:v>3842</x:v>
       </x:c>
       <x:c r="G24" s="51" t="n">
         <x:f>F24-$B$8</x:f>
-        <x:v>144</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H24" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I24" s="44" t="str">
-        <x:v>+100 Luftresistenz vor Levelskalierung.</x:v>
+        <x:v>+40 Personality vor Levelskalierung, kaum direkter Vitality-Effekt.</x:v>
       </x:c>
       <x:c r="J24" s="44" t="str">
-        <x:v>+7 Armsmaster (MAW Level 100 +9), steigert physischen Schaden und Angriffstempo.</x:v>
+        <x:v>+10 Armsmaster (MAW bei Level 100 +13): steigert physischen Schaden und Tempo.</x:v>
       </x:c>
       <x:c r="K24" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L24" s="44" t="str">
-        <x:v>Armsmaster berücksichtigt.</x:v>
+        <x:v>Skillbonus ist im Modell-DPS berücksichtigt.</x:v>
       </x:c>
       <x:c r="M24" s="44" t="str">
         <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
@@ -2353,7 +2401,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q24" s="54" t="n">
-        <x:v>125</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="R24" s="54" t="n">
         <x:v>0</x:v>
@@ -2374,7 +2422,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X24" s="44" t="n">
-        <x:v>574</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="Y24" s="44" t="n">
         <x:v>1</x:v>
@@ -2388,7 +2436,7 @@
       </x:c>
       <x:c r="AB24" s="56" t="n">
         <x:f>IF($F$5+Q24&gt;=65000,1,1-1/(1+($F$5+Q24)/(60+$J$5*0.5)))</x:f>
-        <x:v>0.6140350877192982</x:v>
+        <x:v>0.3125</x:v>
       </x:c>
       <x:c r="AC24" s="56" t="n">
         <x:f>IF($F$5+R24&gt;=65000,1,1-1/(1+($F$5+R24)/(60+$J$5*0.5)))</x:f>
@@ -2418,48 +2466,48 @@
         <x:v>MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ24" s="44" t="str">
-        <x:v>8d4+20</x:v>
+        <x:v>3d4+15</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="49" customHeight="1">
+    <x:row r="25" ht="50" customHeight="1">
       <x:c r="A25" s="44" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="B25" s="44" t="str">
-        <x:v>Elderaxe</x:v>
+        <x:v>Terminus</x:v>
       </x:c>
       <x:c r="C25" s="44" t="str">
-        <x:v>1H-Axt</x:v>
+        <x:v>1H-Schwert</x:v>
       </x:c>
       <x:c r="D25" s="44" t="str">
         <x:v>MM8</x:v>
       </x:c>
       <x:c r="E25" s="50" t="n">
         <x:f>ROUND(X25*Y25,0)</x:f>
-        <x:v>542</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="F25" s="51" t="n">
-        <x:f>ROUND(($B$5+N25*$H$5+W25)/(1-(AH25/2+(AA25+AB25+AC25+AD25+AE25+AF25)/16+AG25/8)),0)</x:f>
-        <x:v>3842</x:v>
+        <x:f>ROUND(($B$5+N25*$H$5+W25)/(1-(AH25/2+(AA25+AB25+AC25+AD25+AE25+AF25)/16+MIN(AA25:AF25)/8)),0)</x:f>
+        <x:v>3986</x:v>
       </x:c>
       <x:c r="G25" s="51" t="n">
         <x:f>F25-$B$8</x:f>
-        <x:v>0</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="H25" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I25" s="44" t="str">
-        <x:v>+100 Might vor Levelskalierung.</x:v>
+        <x:v>+100 Luftresistenz vor Levelskalierung.</x:v>
       </x:c>
       <x:c r="J25" s="44" t="str">
-        <x:v>Kälteschaden pro Treffer, Swift laut Itemtext; Swift-Auswirkung auf Recovery nicht separat bestätigt.</x:v>
+        <x:v>+7 Armsmaster (MAW Level 100 +9), steigert physischen Schaden und Angriffstempo.</x:v>
       </x:c>
       <x:c r="K25" s="44" t="str">
-        <x:v>Nur Minotauren (ExtraArtifacts).</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="L25" s="44" t="str">
-        <x:v>Kälte und Swift nicht in DPS.</x:v>
+        <x:v>Armsmaster berücksichtigt.</x:v>
       </x:c>
       <x:c r="M25" s="44" t="str">
         <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
@@ -2474,7 +2522,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q25" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="R25" s="54" t="n">
         <x:v>0</x:v>
@@ -2495,7 +2543,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X25" s="44" t="n">
-        <x:v>542</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="Y25" s="44" t="n">
         <x:v>1</x:v>
@@ -2509,7 +2557,7 @@
       </x:c>
       <x:c r="AB25" s="56" t="n">
         <x:f>IF($F$5+Q25&gt;=65000,1,1-1/(1+($F$5+Q25)/(60+$J$5*0.5)))</x:f>
-        <x:v>0.3125</x:v>
+        <x:v>0.6140350877192982</x:v>
       </x:c>
       <x:c r="AC25" s="56" t="n">
         <x:f>IF($F$5+R25&gt;=65000,1,1-1/(1+($F$5+R25)/(60+$J$5*0.5)))</x:f>
@@ -2536,31 +2584,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI25" s="44" t="str">
-        <x:v>Text + MAW-Stats</x:v>
+        <x:v>MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ25" s="44" t="str">
-        <x:v>8d6+16</x:v>
+        <x:v>3d4+17</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="49" customHeight="1">
+    <x:row r="26" ht="149" customHeight="1">
       <x:c r="A26" s="44" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="B26" s="44" t="str">
-        <x:v>Hell's Cleaver</x:v>
+        <x:v>Blade of Mercy</x:v>
       </x:c>
       <x:c r="C26" s="44" t="str">
-        <x:v>1H-Axt</x:v>
+        <x:v>Dolch</x:v>
       </x:c>
       <x:c r="D26" s="44" t="str">
         <x:v>MM8</x:v>
       </x:c>
       <x:c r="E26" s="50" t="n">
         <x:f>ROUND(X26*Y26,0)</x:f>
-        <x:v>542</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="F26" s="51" t="n">
-        <x:f>ROUND(($B$5+N26*$H$5+W26)/(1-(AH26/2+(AA26+AB26+AC26+AD26+AE26+AF26)/16+AG26/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N26*$H$5+W26)/(1-(AH26/2+(AA26+AB26+AC26+AD26+AE26+AF26)/16+MIN(AA26:AF26)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G26" s="51" t="n">
@@ -2571,19 +2619,21 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I26" s="44" t="str">
-        <x:v>+70 Might, +70 Accuracy, +50 Intellect/Personality im MAW-Code (Itemtext weicht bei Vorzeichen ab).</x:v>
+        <x:v>+100 Might, +100 Accuracy vor Levelskalierung (Code und Itemtext stimmen überein).</x:v>
       </x:c>
       <x:c r="J26" s="44" t="str">
-        <x:v>Hohe Might-/Accuracy-Boni statt direktem Trefferproc.</x:v>
+        <x:v>Elektrizitätsschaden 8–20 pro Treffer laut Itemtext (MM8-Engine/Itemtext, nicht in Lua), vermutlich wirkungslos, da zzMaw_Legendaries.lua:19 ItemAdditionalDamage am Tag 4.5 auf 0 setzt; hohe Might-/Accuracy-Boni im MAW-Code.</x:v>
       </x:c>
       <x:c r="K26" s="44" t="str">
-        <x:v>—</x:v>
+        <x:v>Nur Necromancer-/Lich-Klassen (ExtraArtifacts).</x:v>
       </x:c>
       <x:c r="L26" s="44" t="str">
-        <x:v>Keine externen Schadenseffekte enthalten.</x:v>
+        <x:v>Elektrizität nicht in DPS.</x:v>
       </x:c>
       <x:c r="M26" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N26" s="54" t="n">
         <x:v>0</x:v>
@@ -2616,7 +2666,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X26" s="44" t="n">
-        <x:v>542</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="Y26" s="44" t="n">
         <x:v>1</x:v>
@@ -2657,31 +2707,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI26" s="44" t="str">
-        <x:v>MAW-Stats; Textkonflikt</x:v>
+        <x:v>Skript + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ26" s="44" t="str">
-        <x:v>8d4+24</x:v>
+        <x:v>2d2+15</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="49" customHeight="1">
+    <x:row r="27" ht="149" customHeight="1">
       <x:c r="A27" s="44" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B27" s="44" t="str">
-        <x:v>Blade of Mercy</x:v>
+        <x:v>Iron Feather</x:v>
       </x:c>
       <x:c r="C27" s="44" t="str">
-        <x:v>Dolch</x:v>
+        <x:v>2H-Schwert</x:v>
       </x:c>
       <x:c r="D27" s="44" t="str">
-        <x:v>MM8</x:v>
+        <x:v>MM7</x:v>
       </x:c>
       <x:c r="E27" s="50" t="n">
         <x:f>ROUND(X27*Y27,0)</x:f>
-        <x:v>511</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="F27" s="51" t="n">
-        <x:f>ROUND(($B$5+N27*$H$5+W27)/(1-(AH27/2+(AA27+AB27+AC27+AD27+AE27+AF27)/16+AG27/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N27*$H$5+W27)/(1-(AH27/2+(AA27+AB27+AC27+AD27+AE27+AF27)/16+MIN(AA27:AF27)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G27" s="51" t="n">
@@ -2692,19 +2742,21 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I27" s="44" t="str">
-        <x:v>+100 Might, +100 Accuracy vor Skalierung; Itemtext weicht teils ab.</x:v>
+        <x:v>+80 Might vor Levelskalierung.</x:v>
       </x:c>
       <x:c r="J27" s="44" t="str">
-        <x:v>Elektrizitätsschaden pro Treffer; besonders hohe Might-/Accuracy-Boni im MAW-Code.</x:v>
+        <x:v>Geskripteter Luft-/Elektrizitätsschaden 15 Basis je Treffer (×2 bei Level 100); am Tag 4.5 von zzMaw_Legendaries.lua:19 (t.Result=0) wieder genullt.</x:v>
       </x:c>
       <x:c r="K27" s="44" t="str">
-        <x:v>Nur Necromancer-/Lich-Klassen (ExtraArtifacts).</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="L27" s="44" t="str">
-        <x:v>Elektrizität nicht in DPS.</x:v>
+        <x:v>Luftschaden nicht in DPS.</x:v>
       </x:c>
       <x:c r="M27" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N27" s="54" t="n">
         <x:v>0</x:v>
@@ -2737,7 +2789,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X27" s="44" t="n">
-        <x:v>511</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="Y27" s="44" t="n">
         <x:v>1</x:v>
@@ -2781,10 +2833,10 @@
         <x:v>Skript + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ27" s="44" t="str">
-        <x:v>8d3+15</x:v>
+        <x:v>4d5+14</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="49" customHeight="1">
+    <x:row r="28" ht="149" customHeight="1">
       <x:c r="A28" s="44" t="n">
         <x:v>17</x:v>
       </x:c>
@@ -2799,10 +2851,10 @@
       </x:c>
       <x:c r="E28" s="50" t="n">
         <x:f>ROUND(X28*Y28,0)</x:f>
-        <x:v>498</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="F28" s="51" t="n">
-        <x:f>ROUND(($B$5+N28*$H$5+W28)/(1-(AH28/2+(AA28+AB28+AC28+AD28+AE28+AF28)/16+AG28/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N28*$H$5+W28)/(1-(AH28/2+(AA28+AB28+AC28+AD28+AE28+AF28)/16+MIN(AA28:AF28)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G28" s="51" t="n">
@@ -2816,16 +2868,18 @@
         <x:v>+100 Might vor Levelskalierung; Bless nicht in Vitality.</x:v>
       </x:c>
       <x:c r="J28" s="44" t="str">
-        <x:v>Geskripteter zusätzlicher Trefferschaden (10 Basis); doppelter Schaden gegen Drachen; Bless-Buff.</x:v>
+        <x:v>Bless-Buff dauerhaft (ExtraArtifacts); geskripteter Zusatzschaden 10 Basis je Treffer (×2 bei Level 100), gegen Drachen verdoppelt – nur der Zusatzschaden, nicht der Waffentreffer; am Tag 4.5 von zzMaw_Legendaries.lua:19 (t.Result=0) wieder genullt.</x:v>
       </x:c>
       <x:c r="K28" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L28" s="44" t="str">
-        <x:v>Slayer, Trefferbonus und Bless nicht in DPS.</x:v>
+        <x:v>Slayer-Verdopplung und Bless-Buff nicht im DPS.</x:v>
       </x:c>
       <x:c r="M28" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N28" s="54" t="n">
         <x:v>0</x:v>
@@ -2858,7 +2912,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X28" s="44" t="n">
-        <x:v>498</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="Y28" s="44" t="n">
         <x:v>1</x:v>
@@ -2899,31 +2953,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI28" s="44" t="str">
-        <x:v>Skript</x:v>
+        <x:v>Skript + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ28" s="44" t="str">
-        <x:v>8d5+15</x:v>
+        <x:v>3d4+15</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="49" customHeight="1">
+    <x:row r="29" ht="199" customHeight="1">
       <x:c r="A29" s="44" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="B29" s="44" t="str">
-        <x:v>Mordred</x:v>
+        <x:v>Elderaxe</x:v>
       </x:c>
       <x:c r="C29" s="44" t="str">
-        <x:v>Dolch</x:v>
+        <x:v>1H-Axt</x:v>
       </x:c>
       <x:c r="D29" s="44" t="str">
-        <x:v>MM6</x:v>
+        <x:v>MM8</x:v>
       </x:c>
       <x:c r="E29" s="50" t="n">
         <x:f>ROUND(X29*Y29,0)</x:f>
-        <x:v>490</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="F29" s="51" t="n">
-        <x:f>ROUND(($B$5+N29*$H$5+W29)/(1-(AH29/2+(AA29+AB29+AC29+AD29+AE29+AF29)/16+AG29/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N29*$H$5+W29)/(1-(AH29/2+(AA29+AB29+AC29+AD29+AE29+AF29)/16+MIN(AA29:AF29)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G29" s="51" t="n">
@@ -2931,22 +2985,25 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H29" s="44" t="str">
-        <x:v>Ja: geskriptet</x:v>
+        <x:v>Nein</x:v>
       </x:c>
       <x:c r="I29" s="44" t="str">
-        <x:v>Potenzielle Selbstheilung; genaue Heilrate ohne konkreten Kampf nicht bestimmbar.</x:v>
+        <x:v>+100 Might vor Levelskalierung.</x:v>
       </x:c>
       <x:c r="J29" s="44" t="str">
-        <x:v>Vampiric in ExtraArtifacts explizit als On-Hit-Effekt aktiviert.</x:v>
+        <x:v>Kälteschaden 12–24 und Swift laut Itemtext (MM8-Engine/Itemtext, nicht in Lua); Kälteschaden vermutlich wirkungslos, da zzMaw_Legendaries.lua:19 ItemAdditionalDamage am Tag 4.5 auf 0 setzt; Swift vom MAW-Angriffstempo nicht berücksichtigt (zzMAW-Skills.lua:185 setzt t.Result neu, Swift nur über Enchant 41/59).</x:v>
       </x:c>
       <x:c r="K29" s="44" t="str">
-        <x:v>—</x:v>
+        <x:v>Nur Minotauren (ExtraArtifacts).</x:v>
       </x:c>
       <x:c r="L29" s="44" t="str">
-        <x:v>Lifeleech nicht in Vitality/DPS.</x:v>
+        <x:v>Kälte und Swift nicht in DPS.</x:v>
       </x:c>
       <x:c r="M29" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMAW-Skills.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N29" s="54" t="n">
         <x:v>0</x:v>
@@ -2979,7 +3036,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X29" s="44" t="n">
-        <x:v>490</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="Y29" s="44" t="n">
         <x:v>1</x:v>
@@ -3020,31 +3077,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI29" s="44" t="str">
-        <x:v>Skript</x:v>
+        <x:v>Text + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ29" s="44" t="str">
-        <x:v>8d5+20</x:v>
+        <x:v>4d2+16</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="49" customHeight="1">
+    <x:row r="30" ht="100" customHeight="1">
       <x:c r="A30" s="44" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="B30" s="44" t="str">
-        <x:v>Glomenthal</x:v>
+        <x:v>Puck</x:v>
       </x:c>
       <x:c r="C30" s="44" t="str">
         <x:v>1H-Schwert</x:v>
       </x:c>
       <x:c r="D30" s="44" t="str">
-        <x:v>MM8</x:v>
+        <x:v>MM7</x:v>
       </x:c>
       <x:c r="E30" s="50" t="n">
         <x:f>ROUND(X30*Y30,0)</x:f>
-        <x:v>489</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="F30" s="51" t="n">
-        <x:f>ROUND(($B$5+N30*$H$5+W30)/(1-(AH30/2+(AA30+AB30+AC30+AD30+AE30+AF30)/16+AG30/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N30*$H$5+W30)/(1-(AH30/2+(AA30+AB30+AC30+AD30+AE30+AF30)/16+MIN(AA30:AF30)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G30" s="51" t="n">
@@ -3055,19 +3112,20 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I30" s="44" t="str">
-        <x:v>+60 Might vor Levelskalierung.</x:v>
+        <x:v>+80 Speed vor Levelskalierung.</x:v>
       </x:c>
       <x:c r="J30" s="44" t="str">
-        <x:v>Dunkelschaden pro Treffer; effektiv gegen Gegner ohne Dunkelresistenz.</x:v>
+        <x:v>Swift im Itemtext; geskriptete Erholungsmodifikation −20, in ExtraArtifacts effektiv ca. −10 %.</x:v>
       </x:c>
       <x:c r="K30" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L30" s="44" t="str">
-        <x:v>Dunkelschaden nicht enthalten.</x:v>
+        <x:v>Angriffsverzögerung −20 (×0,9, ExtraArtifacts.lua:269) ist im Modell-DPS enthalten; Swift laut Itemtext nicht (wirkt am Tag 4.5 nicht).</x:v>
       </x:c>
       <x:c r="M30" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
       </x:c>
       <x:c r="N30" s="54" t="n">
         <x:v>0</x:v>
@@ -3100,7 +3158,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X30" s="44" t="n">
-        <x:v>489</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="Y30" s="44" t="n">
         <x:v>1</x:v>
@@ -3141,31 +3199,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI30" s="44" t="str">
-        <x:v>Text + MAW-Stats</x:v>
+        <x:v>Skript + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ30" s="44" t="str">
-        <x:v>8d4+20</x:v>
+        <x:v>3d3+17</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="49" customHeight="1">
+    <x:row r="31" ht="149" customHeight="1">
       <x:c r="A31" s="44" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="B31" s="44" t="str">
-        <x:v>Corsair</x:v>
+        <x:v>Elfbane</x:v>
       </x:c>
       <x:c r="C31" s="44" t="str">
-        <x:v>1H-Schwert</x:v>
+        <x:v>2H-Schwert</x:v>
       </x:c>
       <x:c r="D31" s="44" t="str">
         <x:v>MM7</x:v>
       </x:c>
       <x:c r="E31" s="50" t="n">
         <x:f>ROUND(X31*Y31,0)</x:f>
-        <x:v>472</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="F31" s="51" t="n">
-        <x:f>ROUND(($B$5+N31*$H$5+W31)/(1-(AH31/2+(AA31+AB31+AC31+AD31+AE31+AF31)/16+AG31/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N31*$H$5+W31)/(1-(AH31/2+(AA31+AB31+AC31+AD31+AE31+AF31)/16+MIN(AA31:AF31)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G31" s="51" t="n">
@@ -3176,19 +3234,21 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I31" s="44" t="str">
-        <x:v>+80 Luck vor Levelskalierung; begünstigt Kritchance.</x:v>
+        <x:v>+100 Speed vor Levelskalierung; Schutz-/Schildbonus nicht in Vitality-Modell enthalten.</x:v>
       </x:c>
       <x:c r="J31" s="44" t="str">
-        <x:v>Stealing/Disarm-Boni statt unmittelbarer Schadensprocs.</x:v>
+        <x:v>Elf Slaying: ExtraArtifacts verdoppelt nur den ItemAdditionalDamage-Wert (bei Elfbane 0, zudem am Tag 4.5 von zzMaw_Legendaries.lua:19 (t.Result=0) wieder genullt) – praktisch wirkungslos; dauerhafter Shield-Buff (Stufe 3) per ExtraArtifacts.</x:v>
       </x:c>
       <x:c r="K31" s="44" t="str">
-        <x:v>—</x:v>
+        <x:v>Nur Goblins (laut ExtraArtifacts).</x:v>
       </x:c>
       <x:c r="L31" s="44" t="str">
-        <x:v>Luck-Krit im Modell eingerechnet.</x:v>
+        <x:v>Elf-Slaying und Shielding nicht in DPS.</x:v>
       </x:c>
       <x:c r="M31" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N31" s="54" t="n">
         <x:v>0</x:v>
@@ -3221,7 +3281,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X31" s="44" t="n">
-        <x:v>472</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="Y31" s="44" t="n">
         <x:v>1</x:v>
@@ -3262,31 +3322,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI31" s="44" t="str">
-        <x:v>MAW-Stats</x:v>
+        <x:v>Skript + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ31" s="44" t="str">
-        <x:v>8d5+16</x:v>
+        <x:v>4d6+14</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="49" customHeight="1">
+    <x:row r="32" ht="50" customHeight="1">
       <x:c r="A32" s="44" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="B32" s="44" t="str">
-        <x:v>Elsenrail</x:v>
+        <x:v>Charele</x:v>
       </x:c>
       <x:c r="C32" s="44" t="str">
-        <x:v>1H-Schwert</x:v>
+        <x:v>Speer</x:v>
       </x:c>
       <x:c r="D32" s="44" t="str">
-        <x:v>MM8</x:v>
+        <x:v>MM7</x:v>
       </x:c>
       <x:c r="E32" s="50" t="n">
         <x:f>ROUND(X32*Y32,0)</x:f>
-        <x:v>469</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="F32" s="51" t="n">
-        <x:f>ROUND(($B$5+N32*$H$5+W32)/(1-(AH32/2+(AA32+AB32+AC32+AD32+AE32+AF32)/16+AG32/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N32*$H$5+W32)/(1-(AH32/2+(AA32+AB32+AC32+AD32+AE32+AF32)/16+MIN(AA32:AF32)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G32" s="51" t="n">
@@ -3297,16 +3357,16 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I32" s="44" t="str">
-        <x:v>+60 Accuracy vor Levelskalierung.</x:v>
+        <x:v>Keine spezifischen Defensivboni dokumentiert.</x:v>
       </x:c>
       <x:c r="J32" s="44" t="str">
-        <x:v>Lichtschaden pro Treffer; gegen manche Gegner sehr wirksam.</x:v>
+        <x:v>Hoher physischer Grundschaden ohne klaren Trefferproc.</x:v>
       </x:c>
       <x:c r="K32" s="44" t="str">
-        <x:v>—</x:v>
+        <x:v>1H/2H-fähig.</x:v>
       </x:c>
       <x:c r="L32" s="44" t="str">
-        <x:v>Lichtschaden nicht enthalten.</x:v>
+        <x:v>Keine besonderen Schadensprocs.</x:v>
       </x:c>
       <x:c r="M32" s="44" t="str">
         <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
@@ -3342,7 +3402,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X32" s="44" t="n">
-        <x:v>469</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="Y32" s="44" t="n">
         <x:v>1</x:v>
@@ -3383,31 +3443,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI32" s="44" t="str">
-        <x:v>Text + MAW-Stats</x:v>
+        <x:v>Itemdaten; Lua nur Upscaler-Liste (zzMaw-Items.lua:2451)</x:v>
       </x:c>
       <x:c r="AJ32" s="44" t="str">
-        <x:v>8d4+20</x:v>
+        <x:v>3d15+30</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="49" customHeight="1">
+    <x:row r="33" ht="50" customHeight="1">
       <x:c r="A33" s="44" t="n">
         <x:v>22</x:v>
       </x:c>
       <x:c r="B33" s="44" t="str">
-        <x:v>Hades</x:v>
+        <x:v>Hell's Cleaver</x:v>
       </x:c>
       <x:c r="C33" s="44" t="str">
-        <x:v>1H-Schwert</x:v>
+        <x:v>1H-Axt</x:v>
       </x:c>
       <x:c r="D33" s="44" t="str">
-        <x:v>MM6</x:v>
+        <x:v>MM8</x:v>
       </x:c>
       <x:c r="E33" s="50" t="n">
         <x:f>ROUND(X33*Y33,0)</x:f>
-        <x:v>467</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="F33" s="51" t="n">
-        <x:f>ROUND(($B$5+N33*$H$5+W33)/(1-(AH33/2+(AA33+AB33+AC33+AD33+AE33+AF33)/16+AG33/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N33*$H$5+W33)/(1-(AH33/2+(AA33+AB33+AC33+AD33+AE33+AF33)/16+MIN(AA33:AF33)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G33" s="51" t="n">
@@ -3418,19 +3478,19 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I33" s="44" t="str">
-        <x:v>+60 Luck; −3 HP-Regen (Schaden über Zeit für Träger).</x:v>
+        <x:v>+70 Might, +70 Accuracy, +50 Intellect/Personality im MAW-Code (Itemtext weicht bei Vorzeichen ab).</x:v>
       </x:c>
       <x:c r="J33" s="44" t="str">
-        <x:v>Geskripteter Wasserschaden (+20 Basis je Treffer) und zusätzlicher Zaubereffekt.</x:v>
+        <x:v>Hohe Might-/Accuracy-Boni statt direktem Trefferproc.</x:v>
       </x:c>
       <x:c r="K33" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L33" s="44" t="str">
-        <x:v>Zauber und zusätzlicher Wasserschaden nicht enthalten.</x:v>
+        <x:v>Keine externen Schadenseffekte enthalten.</x:v>
       </x:c>
       <x:c r="M33" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
       </x:c>
       <x:c r="N33" s="54" t="n">
         <x:v>0</x:v>
@@ -3463,13 +3523,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X33" s="44" t="n">
-        <x:v>467</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="Y33" s="44" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Z33" s="44" t="n">
-        <x:v>-3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AA33" s="56" t="n">
         <x:f>IF($F$5+P33&gt;=65000,1,1-1/(1+($F$5+P33)/(60+$J$5*0.5)))</x:f>
@@ -3504,18 +3564,18 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI33" s="44" t="str">
-        <x:v>Skript</x:v>
+        <x:v>MAW-Stats; Textkonflikt</x:v>
       </x:c>
       <x:c r="AJ33" s="44" t="str">
-        <x:v>6d6+18</x:v>
+        <x:v>4d2+14</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="49" customHeight="1">
+    <x:row r="34" ht="100" customHeight="1">
       <x:c r="A34" s="44" t="n">
         <x:v>23</x:v>
       </x:c>
       <x:c r="B34" s="44" t="str">
-        <x:v>Havoc</x:v>
+        <x:v>Glomenthal</x:v>
       </x:c>
       <x:c r="C34" s="44" t="str">
         <x:v>1H-Schwert</x:v>
@@ -3525,39 +3585,40 @@
       </x:c>
       <x:c r="E34" s="50" t="n">
         <x:f>ROUND(X34*Y34,0)</x:f>
-        <x:v>463</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="F34" s="51" t="n">
-        <x:f>ROUND(($B$5+N34*$H$5+W34)/(1-(AH34/2+(AA34+AB34+AC34+AD34+AE34+AF34)/16+AG34/8)),0)</x:f>
-        <x:v>3562</x:v>
+        <x:f>ROUND(($B$5+N34*$H$5+W34)/(1-(AH34/2+(AA34+AB34+AC34+AD34+AE34+AF34)/16+MIN(AA34:AF34)/8)),0)</x:f>
+        <x:v>3842</x:v>
       </x:c>
       <x:c r="G34" s="51" t="n">
         <x:f>F34-$B$8</x:f>
-        <x:v>-280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H34" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I34" s="44" t="str">
-        <x:v>+70 Speed, +70 Accuracy, −20 AC vor Levelskalierung.</x:v>
+        <x:v>+60 Might vor Levelskalierung.</x:v>
       </x:c>
       <x:c r="J34" s="44" t="str">
-        <x:v>Sehr hohe Speed-/Accuracy-Werte; kein eigener Trefferproc.</x:v>
+        <x:v>Dunkelschaden 20–40 pro Treffer laut Itemtext (MM8-Engine/Itemtext, nicht in Lua); vermutlich wirkungslos, da zzMaw_Legendaries.lua:19 ItemAdditionalDamage am Tag 4.5 auf 0 setzt.</x:v>
       </x:c>
       <x:c r="K34" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L34" s="44" t="str">
-        <x:v>Kein Zusatzproc.</x:v>
+        <x:v>Dunkelschaden nicht enthalten.</x:v>
       </x:c>
       <x:c r="M34" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N34" s="54" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O34" s="54" t="n">
-        <x:v>-25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="P34" s="54" t="n">
         <x:v>0</x:v>
@@ -3584,7 +3645,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X34" s="44" t="n">
-        <x:v>463</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="Y34" s="44" t="n">
         <x:v>1</x:v>
@@ -3622,54 +3683,54 @@
       </x:c>
       <x:c r="AH34" s="56" t="n">
         <x:f>1-((5+$J$5*2)/(10+$J$5*2+MAX(0,$D$5+O34)))*(1/(1+MAX(0,$D$5+O34)/(90+$J$5*0.25)))</x:f>
-        <x:v>0.5646352723915051</x:v>
+        <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI34" s="44" t="str">
-        <x:v>MAW-Stats</x:v>
+        <x:v>Text + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ34" s="44" t="str">
-        <x:v>10d3+18</x:v>
+        <x:v>3d3+17</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="49" customHeight="1">
+    <x:row r="35" ht="50" customHeight="1">
       <x:c r="A35" s="44" t="n">
         <x:v>24</x:v>
       </x:c>
       <x:c r="B35" s="44" t="str">
-        <x:v>Lightning Crossbow</x:v>
+        <x:v>Havoc</x:v>
       </x:c>
       <x:c r="C35" s="44" t="str">
-        <x:v>Armbrust</x:v>
+        <x:v>1H-Schwert</x:v>
       </x:c>
       <x:c r="D35" s="44" t="str">
         <x:v>MM8</x:v>
       </x:c>
       <x:c r="E35" s="50" t="n">
         <x:f>ROUND(X35*Y35,0)</x:f>
-        <x:v>460</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="F35" s="51" t="n">
-        <x:f>ROUND(($B$5+N35*$H$5+W35)/(1-(AH35/2+(AA35+AB35+AC35+AD35+AE35+AF35)/16+AG35/8)),0)</x:f>
-        <x:v>3842</x:v>
+        <x:f>ROUND(($B$5+N35*$H$5+W35)/(1-(AH35/2+(AA35+AB35+AC35+AD35+AE35+AF35)/16+MIN(AA35:AF35)/8)),0)</x:f>
+        <x:v>3562</x:v>
       </x:c>
       <x:c r="G35" s="51" t="n">
         <x:f>F35-$B$8</x:f>
-        <x:v>0</x:v>
+        <x:v>-280</x:v>
       </x:c>
       <x:c r="H35" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I35" s="44" t="str">
-        <x:v>+60 Might und Speed vor Skalierung.</x:v>
+        <x:v>+70 Speed, +70 Accuracy, −20 AC vor Levelskalierung.</x:v>
       </x:c>
       <x:c r="J35" s="44" t="str">
-        <x:v>Swift laut Itemtext; besonders für Bogen-/Armbrustnutzer.</x:v>
+        <x:v>Sehr hohe Speed-/Accuracy-Werte; kein eigener Trefferproc.</x:v>
       </x:c>
       <x:c r="K35" s="44" t="str">
-        <x:v>Nur Elfen/Dunkelelfen (ExtraArtifacts).</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="L35" s="44" t="str">
-        <x:v>Swift-Auswirkung nicht in DPS.</x:v>
+        <x:v>Kein Zusatzproc.</x:v>
       </x:c>
       <x:c r="M35" s="44" t="str">
         <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
@@ -3678,7 +3739,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O35" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>-25</x:v>
       </x:c>
       <x:c r="P35" s="54" t="n">
         <x:v>0</x:v>
@@ -3705,7 +3766,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X35" s="44" t="n">
-        <x:v>460</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="Y35" s="44" t="n">
         <x:v>1</x:v>
@@ -3743,34 +3804,34 @@
       </x:c>
       <x:c r="AH35" s="56" t="n">
         <x:f>1-((5+$J$5*2)/(10+$J$5*2+MAX(0,$D$5+O35)))*(1/(1+MAX(0,$D$5+O35)/(90+$J$5*0.25)))</x:f>
-        <x:v>0.6462865716429107</x:v>
+        <x:v>0.5646352723915051</x:v>
       </x:c>
       <x:c r="AI35" s="44" t="str">
-        <x:v>Itemtext + MAW-Stats</x:v>
+        <x:v>MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ35" s="44" t="str">
-        <x:v>20d3+15</x:v>
+        <x:v>3d3+18</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="49" customHeight="1">
+    <x:row r="36" ht="149" customHeight="1">
       <x:c r="A36" s="44" t="n">
         <x:v>25</x:v>
       </x:c>
       <x:c r="B36" s="44" t="str">
-        <x:v>Puck</x:v>
+        <x:v>Lightning Crossbow</x:v>
       </x:c>
       <x:c r="C36" s="44" t="str">
-        <x:v>1H-Schwert</x:v>
+        <x:v>Armbrust</x:v>
       </x:c>
       <x:c r="D36" s="44" t="str">
-        <x:v>MM7</x:v>
+        <x:v>MM8</x:v>
       </x:c>
       <x:c r="E36" s="50" t="n">
         <x:f>ROUND(X36*Y36,0)</x:f>
-        <x:v>460</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="F36" s="51" t="n">
-        <x:f>ROUND(($B$5+N36*$H$5+W36)/(1-(AH36/2+(AA36+AB36+AC36+AD36+AE36+AF36)/16+AG36/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N36*$H$5+W36)/(1-(AH36/2+(AA36+AB36+AC36+AD36+AE36+AF36)/16+MIN(AA36:AF36)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G36" s="51" t="n">
@@ -3781,19 +3842,21 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I36" s="44" t="str">
-        <x:v>+80 Speed vor Levelskalierung.</x:v>
+        <x:v>+60 Might und Speed vor Skalierung.</x:v>
       </x:c>
       <x:c r="J36" s="44" t="str">
-        <x:v>Swift im Itemtext; geskriptete Erholungsmodifikation −20, in ExtraArtifacts effektiv ca. −10 %.</x:v>
+        <x:v>Swift laut Itemtext (MM8-Engine/Itemtext, nicht in Lua), vom MAW-Angriffstempo nicht berücksichtigt (zzMAW-Skills.lua:185 setzt t.Result neu, Swift nur über Enchant 41/59); hohe Might-/Speed-Boni.</x:v>
       </x:c>
       <x:c r="K36" s="44" t="str">
-        <x:v>—</x:v>
+        <x:v>Nur Elfen/Dunkelelfen (ExtraArtifacts).</x:v>
       </x:c>
       <x:c r="L36" s="44" t="str">
-        <x:v>Besondere Recovery nicht in Tabellen-DPS.</x:v>
+        <x:v>Swift nicht in DPS (wirkt am Tag 4.5 nicht).</x:v>
       </x:c>
       <x:c r="M36" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMAW-Skills.lua</x:v>
       </x:c>
       <x:c r="N36" s="54" t="n">
         <x:v>0</x:v>
@@ -3826,7 +3889,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X36" s="44" t="n">
-        <x:v>460</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="Y36" s="44" t="n">
         <x:v>1</x:v>
@@ -3867,54 +3930,56 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI36" s="44" t="str">
-        <x:v>Skript + MAW-Stats</x:v>
+        <x:v>Itemtext + MAW-Stats + Skript (Tragbedingung)</x:v>
       </x:c>
       <x:c r="AJ36" s="44" t="str">
-        <x:v>6d6+17</x:v>
+        <x:v>5d2+15</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="49" customHeight="1">
+    <x:row r="37" ht="149" customHeight="1">
       <x:c r="A37" s="44" t="n">
         <x:v>26</x:v>
       </x:c>
       <x:c r="B37" s="44" t="str">
-        <x:v>Snake</x:v>
+        <x:v>Hades</x:v>
       </x:c>
       <x:c r="C37" s="44" t="str">
         <x:v>1H-Schwert</x:v>
       </x:c>
       <x:c r="D37" s="44" t="str">
-        <x:v>MM8</x:v>
+        <x:v>MM6</x:v>
       </x:c>
       <x:c r="E37" s="50" t="n">
         <x:f>ROUND(X37*Y37,0)</x:f>
-        <x:v>442</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="F37" s="51" t="n">
-        <x:f>ROUND(($B$5+N37*$H$5+W37)/(1-(AH37/2+(AA37+AB37+AC37+AD37+AE37+AF37)/16+AG37/8)),0)</x:f>
-        <x:v>3649</x:v>
+        <x:f>ROUND(($B$5+N37*$H$5+W37)/(1-(AH37/2+(AA37+AB37+AC37+AD37+AE37+AF37)/16+MIN(AA37:AF37)/8)),0)</x:f>
+        <x:v>3842</x:v>
       </x:c>
       <x:c r="G37" s="51" t="n">
         <x:f>F37-$B$8</x:f>
-        <x:v>-193</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H37" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I37" s="44" t="str">
-        <x:v>+100 Speed, −50 Wasserresistenz, −15 Personality vor Skalierung.</x:v>
+        <x:v>+60 Luck; −3 HP-Regen (Schaden über Zeit für Träger).</x:v>
       </x:c>
       <x:c r="J37" s="44" t="str">
-        <x:v>Verlangsamt das Ziel bei Treffer (Slow).</x:v>
+        <x:v>Geskripteter Wasserschaden 20 Basis je Treffer (×2 bei Level 100; Itemtext: Gift) und Acid Burst (Zauber 29) bei Treffer; Disarm Traps +10 vor Levelskalierung (Level 100: +13); Wasserschaden am Tag 4.5 von zzMaw_Legendaries.lua:19 (t.Result=0) wieder genullt.</x:v>
       </x:c>
       <x:c r="K37" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L37" s="44" t="str">
-        <x:v>Verlangsamung nicht in DPS.</x:v>
+        <x:v>Zauber und zusätzlicher Wasserschaden nicht enthalten.</x:v>
       </x:c>
       <x:c r="M37" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N37" s="54" t="n">
         <x:v>0</x:v>
@@ -3929,7 +3994,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="R37" s="54" t="n">
-        <x:v>-62.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="S37" s="54" t="n">
         <x:v>0</x:v>
@@ -3947,13 +4012,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X37" s="44" t="n">
-        <x:v>442</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="Y37" s="44" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Z37" s="44" t="n">
-        <x:v>0</x:v>
+        <x:v>-3</x:v>
       </x:c>
       <x:c r="AA37" s="56" t="n">
         <x:f>IF($F$5+P37&gt;=65000,1,1-1/(1+($F$5+P37)/(60+$J$5*0.5)))</x:f>
@@ -3965,7 +4030,7 @@
       </x:c>
       <x:c r="AC37" s="56" t="n">
         <x:f>IF($F$5+R37&gt;=65000,1,1-1/(1+($F$5+R37)/(60+$J$5*0.5)))</x:f>
-        <x:v>-0.1282051282051282</x:v>
+        <x:v>0.3125</x:v>
       </x:c>
       <x:c r="AD37" s="56" t="n">
         <x:f>IF($F$5+S37&gt;=65000,1,1-1/(1+($F$5+S37)/(60+$J$5*0.5)))</x:f>
@@ -3988,54 +4053,54 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI37" s="44" t="str">
-        <x:v>Text + MAW-Stats</x:v>
+        <x:v>Skript + MAW-Stats/Skills; Z: −3 HP je Regen-Tick (ExtraArtifacts.lua:194-199, 760)</x:v>
       </x:c>
       <x:c r="AJ37" s="44" t="str">
-        <x:v>8d4+15</x:v>
+        <x:v>3d3+18</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="49" customHeight="1">
+    <x:row r="38" ht="50" customHeight="1">
       <x:c r="A38" s="44" t="n">
         <x:v>27</x:v>
       </x:c>
       <x:c r="B38" s="44" t="str">
-        <x:v>Foulfang</x:v>
+        <x:v>Snake</x:v>
       </x:c>
       <x:c r="C38" s="44" t="str">
-        <x:v>Dolch</x:v>
+        <x:v>1H-Schwert</x:v>
       </x:c>
       <x:c r="D38" s="44" t="str">
         <x:v>MM8</x:v>
       </x:c>
       <x:c r="E38" s="50" t="n">
         <x:f>ROUND(X38*Y38,0)</x:f>
-        <x:v>429</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="F38" s="51" t="n">
-        <x:f>ROUND(($B$5+N38*$H$5+W38)/(1-(AH38/2+(AA38+AB38+AC38+AD38+AE38+AF38)/16+AG38/8)),0)</x:f>
-        <x:v>3842</x:v>
+        <x:f>ROUND(($B$5+N38*$H$5+W38)/(1-(AH38/2+(AA38+AB38+AC38+AD38+AE38+AF38)/16+MIN(AA38:AF38)/8)),0)</x:f>
+        <x:v>3315</x:v>
       </x:c>
       <x:c r="G38" s="51" t="n">
         <x:f>F38-$B$8</x:f>
-        <x:v>0</x:v>
+        <x:v>-527</x:v>
       </x:c>
       <x:c r="H38" s="44" t="str">
-        <x:v>Ja: Gegenstandstext</x:v>
+        <x:v>Nein</x:v>
       </x:c>
       <x:c r="I38" s="44" t="str">
-        <x:v>Potenzielle Selbstheilung, nicht in der Stats-Menü-Vitality.</x:v>
+        <x:v>+100 Speed, −50 Wasserresistenz, −15 Personality vor Skalierung.</x:v>
       </x:c>
       <x:c r="J38" s="44" t="str">
-        <x:v>Vampiric und Giftschaden laut Itemtext.</x:v>
+        <x:v>Verlangsamt das Ziel bei Treffer (Slow) laut Itemtext (MM8-Engine/Itemtext, nicht in Lua).</x:v>
       </x:c>
       <x:c r="K38" s="44" t="str">
-        <x:v>Nur Vampire (ExtraArtifacts).</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="L38" s="44" t="str">
-        <x:v>Gift und Lifesteal nicht in DPS.</x:v>
+        <x:v>Verlangsamung nicht in DPS.</x:v>
       </x:c>
       <x:c r="M38" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
       </x:c>
       <x:c r="N38" s="54" t="n">
         <x:v>0</x:v>
@@ -4050,7 +4115,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="R38" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>-62.5</x:v>
       </x:c>
       <x:c r="S38" s="54" t="n">
         <x:v>0</x:v>
@@ -4068,7 +4133,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X38" s="44" t="n">
-        <x:v>429</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="Y38" s="44" t="n">
         <x:v>1</x:v>
@@ -4086,7 +4151,7 @@
       </x:c>
       <x:c r="AC38" s="56" t="n">
         <x:f>IF($F$5+R38&gt;=65000,1,1-1/(1+($F$5+R38)/(60+$J$5*0.5)))</x:f>
-        <x:v>0.3125</x:v>
+        <x:v>-0.1282051282051282</x:v>
       </x:c>
       <x:c r="AD38" s="56" t="n">
         <x:f>IF($F$5+S38&gt;=65000,1,1-1/(1+($F$5+S38)/(60+$J$5*0.5)))</x:f>
@@ -4109,31 +4174,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI38" s="44" t="str">
-        <x:v>Itemtext; Script-Verbindung offen</x:v>
+        <x:v>Text + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ38" s="44" t="str">
-        <x:v>12d3+12</x:v>
+        <x:v>3d4+15</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="49" customHeight="1">
+    <x:row r="39" ht="100" customHeight="1">
       <x:c r="A39" s="44" t="n">
         <x:v>28</x:v>
       </x:c>
       <x:c r="B39" s="44" t="str">
-        <x:v>Old Nick</x:v>
+        <x:v>Elsenrail</x:v>
       </x:c>
       <x:c r="C39" s="44" t="str">
-        <x:v>Dolch</x:v>
+        <x:v>1H-Schwert</x:v>
       </x:c>
       <x:c r="D39" s="44" t="str">
-        <x:v>MM7</x:v>
+        <x:v>MM8</x:v>
       </x:c>
       <x:c r="E39" s="50" t="n">
         <x:f>ROUND(X39*Y39,0)</x:f>
-        <x:v>418</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="F39" s="51" t="n">
-        <x:f>ROUND(($B$5+N39*$H$5+W39)/(1-(AH39/2+(AA39+AB39+AC39+AD39+AE39+AF39)/16+AG39/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N39*$H$5+W39)/(1-(AH39/2+(AA39+AB39+AC39+AD39+AE39+AF39)/16+MIN(AA39:AF39)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G39" s="51" t="n">
@@ -4144,19 +4209,20 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I39" s="44" t="str">
-        <x:v>Disarm-Skillbonus; kein direkter Vitality-Effekt.</x:v>
+        <x:v>+60 Accuracy vor Levelskalierung.</x:v>
       </x:c>
       <x:c r="J39" s="44" t="str">
-        <x:v>Geskripteter zusätzlicher Wasserschaden (36 Basis); doppelter Trefferschaden gegen Elfen.</x:v>
+        <x:v>Lichtschaden 20–40 pro Treffer laut Itemtext (MM8-Engine/Itemtext, nicht in Lua); vermutlich wirkungslos, da zzMaw_Legendaries.lua:19 ItemAdditionalDamage am Tag 4.5 auf 0 setzt.</x:v>
       </x:c>
       <x:c r="K39" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L39" s="44" t="str">
-        <x:v>Wasser und Elf-Slaying nicht in DPS.</x:v>
+        <x:v>Lichtschaden nicht enthalten.</x:v>
       </x:c>
       <x:c r="M39" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N39" s="54" t="n">
         <x:v>0</x:v>
@@ -4189,7 +4255,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X39" s="44" t="n">
-        <x:v>418</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="Y39" s="44" t="n">
         <x:v>1</x:v>
@@ -4230,57 +4296,58 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI39" s="44" t="str">
-        <x:v>Skript</x:v>
+        <x:v>Text + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ39" s="44" t="str">
-        <x:v>8d5+10</x:v>
+        <x:v>3d3+17</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="49" customHeight="1">
+    <x:row r="40" ht="100" customHeight="1">
       <x:c r="A40" s="44" t="n">
         <x:v>29</x:v>
       </x:c>
       <x:c r="B40" s="44" t="str">
-        <x:v>Judicious Measure</x:v>
+        <x:v>Gibbet</x:v>
       </x:c>
       <x:c r="C40" s="44" t="str">
-        <x:v>1H-Schwert</x:v>
+        <x:v>Speer</x:v>
       </x:c>
       <x:c r="D40" s="44" t="str">
-        <x:v>MM8</x:v>
+        <x:v>MM7</x:v>
       </x:c>
       <x:c r="E40" s="50" t="n">
         <x:f>ROUND(X40*Y40,0)</x:f>
-        <x:v>416</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="F40" s="51" t="n">
-        <x:f>ROUND(($B$5+N40*$H$5+W40)/(1-(AH40/2+(AA40+AB40+AC40+AD40+AE40+AF40)/16+AG40/8)),0)</x:f>
-        <x:v>4322</x:v>
+        <x:f>ROUND(($B$5+N40*$H$5+W40)/(1-(AH40/2+(AA40+AB40+AC40+AD40+AE40+AF40)/16+MIN(AA40:AF40)/8)),0)</x:f>
+        <x:v>3842</x:v>
       </x:c>
       <x:c r="G40" s="51" t="n">
         <x:f>F40-$B$8</x:f>
-        <x:v>480</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H40" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I40" s="44" t="str">
-        <x:v>+40 Endurance und +40 Luck vor Levelskalierung.</x:v>
+        <x:v>Keine direkten Attribute; hoher situativer Offensivnutzen.</x:v>
       </x:c>
       <x:c r="J40" s="44" t="str">
-        <x:v>Ogre Slaying: situationsabhängiger Bonus gegen Oger.</x:v>
+        <x:v>Geskripteter Feuerschaden 15 Basis je Treffer (×2 bei Level 100), gegen Drachen, Dämonen und Untote verdoppelt – nur der Zusatzschaden, nicht der Waffentreffer; am Tag 4.5 von zzMaw_Legendaries.lua:19 (t.Result=0) wieder genullt.</x:v>
       </x:c>
       <x:c r="K40" s="44" t="str">
-        <x:v>—</x:v>
+        <x:v>1H/2H-fähig.</x:v>
       </x:c>
       <x:c r="L40" s="44" t="str">
-        <x:v>Ogre Slaying nicht in DPS.</x:v>
+        <x:v>Slayer und Feuerschaden nicht enthalten.</x:v>
       </x:c>
       <x:c r="M40" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N40" s="54" t="n">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="O40" s="54" t="n">
         <x:v>0</x:v>
@@ -4310,7 +4377,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X40" s="44" t="n">
-        <x:v>416</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="Y40" s="44" t="n">
         <x:v>1</x:v>
@@ -4351,60 +4418,60 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI40" s="44" t="str">
-        <x:v>Text + MAW-Stats</x:v>
+        <x:v>Skript</x:v>
       </x:c>
       <x:c r="AJ40" s="44" t="str">
-        <x:v>6d5+16</x:v>
+        <x:v>3d9+30</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="49" customHeight="1">
+    <x:row r="41" ht="50" customHeight="1">
       <x:c r="A41" s="44" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="B41" s="44" t="str">
-        <x:v>Poseidon</x:v>
+        <x:v>Corsair</x:v>
       </x:c>
       <x:c r="C41" s="44" t="str">
-        <x:v>Speer</x:v>
+        <x:v>1H-Schwert</x:v>
       </x:c>
       <x:c r="D41" s="44" t="str">
-        <x:v>MM6</x:v>
+        <x:v>MM7</x:v>
       </x:c>
       <x:c r="E41" s="50" t="n">
         <x:f>ROUND(X41*Y41,0)</x:f>
-        <x:v>413</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="F41" s="51" t="n">
-        <x:f>ROUND(($B$5+N41*$H$5+W41)/(1-(AH41/2+(AA41+AB41+AC41+AD41+AE41+AF41)/16+AG41/8)),0)</x:f>
-        <x:v>4171</x:v>
+        <x:f>ROUND(($B$5+N41*$H$5+W41)/(1-(AH41/2+(AA41+AB41+AC41+AD41+AE41+AF41)/16+MIN(AA41:AF41)/8)),0)</x:f>
+        <x:v>3842</x:v>
       </x:c>
       <x:c r="G41" s="51" t="n">
         <x:f>F41-$B$8</x:f>
-        <x:v>329</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H41" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I41" s="44" t="str">
-        <x:v>+40 Might, Endurance, Accuracy; −10 Speed und −10 AC vor Skalierung.</x:v>
+        <x:v>+80 Luck vor Levelskalierung; begünstigt Kritchance.</x:v>
       </x:c>
       <x:c r="J41" s="44" t="str">
-        <x:v>Hoher Grundschaden; Speer-GM-Resistenzsenkung kann Folgeangriffe verstärken.</x:v>
+        <x:v>Disarm Traps +10 vor Levelskalierung (Level 100: +13); Itemtext nennt Stealing +5/Disarm +5, Stealing ist in Lua nicht umgesetzt; keine Schadensprocs.</x:v>
       </x:c>
       <x:c r="K41" s="44" t="str">
-        <x:v>1H/2H-fähig.</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="L41" s="44" t="str">
-        <x:v>Speer-GM-Debuff nicht in Basis-DPS.</x:v>
+        <x:v>Luck-Krit im Modell eingerechnet.</x:v>
       </x:c>
       <x:c r="M41" s="44" t="str">
         <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
       </x:c>
       <x:c r="N41" s="54" t="n">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="O41" s="54" t="n">
-        <x:v>-12.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="P41" s="54" t="n">
         <x:v>0</x:v>
@@ -4431,7 +4498,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X41" s="44" t="n">
-        <x:v>413</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="Y41" s="44" t="n">
         <x:v>1</x:v>
@@ -4469,60 +4536,60 @@
       </x:c>
       <x:c r="AH41" s="56" t="n">
         <x:f>1-((5+$J$5*2)/(10+$J$5*2+MAX(0,$D$5+O41)))*(1/(1+MAX(0,$D$5+O41)/(90+$J$5*0.25)))</x:f>
-        <x:v>0.6086730988691773</x:v>
+        <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI41" s="44" t="str">
-        <x:v>MAW-Stats</x:v>
+        <x:v>MAW-Stats + MAW-Skills</x:v>
       </x:c>
       <x:c r="AJ41" s="44" t="str">
-        <x:v>9d9+19</x:v>
+        <x:v>2d4+16</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" ht="49" customHeight="1">
+    <x:row r="42" ht="50" customHeight="1">
       <x:c r="A42" s="44" t="n">
         <x:v>31</x:v>
       </x:c>
       <x:c r="B42" s="44" t="str">
-        <x:v>Cronos</x:v>
+        <x:v>Mordred</x:v>
       </x:c>
       <x:c r="C42" s="44" t="str">
-        <x:v>1H-Axt</x:v>
+        <x:v>Dolch</x:v>
       </x:c>
       <x:c r="D42" s="44" t="str">
         <x:v>MM6</x:v>
       </x:c>
       <x:c r="E42" s="50" t="n">
         <x:f>ROUND(X42*Y42,0)</x:f>
-        <x:v>385</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="F42" s="51" t="n">
-        <x:f>ROUND(($B$5+N42*$H$5+W42)/(1-(AH42/2+(AA42+AB42+AC42+AD42+AE42+AF42)/16+AG42/8)),0)</x:f>
-        <x:v>5282</x:v>
+        <x:f>ROUND(($B$5+N42*$H$5+W42)/(1-(AH42/2+(AA42+AB42+AC42+AD42+AE42+AF42)/16+MIN(AA42:AF42)/8)),0)</x:f>
+        <x:v>3842</x:v>
       </x:c>
       <x:c r="G42" s="51" t="n">
         <x:f>F42-$B$8</x:f>
-        <x:v>1440</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H42" s="44" t="str">
-        <x:v>Nein</x:v>
+        <x:v>Ja: geskriptet</x:v>
       </x:c>
       <x:c r="I42" s="44" t="str">
-        <x:v>+120 Endurance, −60 Luck vor Levelskalierung.</x:v>
+        <x:v>Potenzielle Selbstheilung; genaue Heilrate ohne konkreten Kampf nicht bestimmbar.</x:v>
       </x:c>
       <x:c r="J42" s="44" t="str">
-        <x:v>Keine zusätzliche Schadenswirkung im MAW-Skript nachgewiesen.</x:v>
+        <x:v>Vampiric in ExtraArtifacts explizit als On-Hit-Effekt aktiviert.</x:v>
       </x:c>
       <x:c r="K42" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L42" s="44" t="str">
-        <x:v>Keine separaten Procs.</x:v>
+        <x:v>Lifeleech nicht in Vitality/DPS.</x:v>
       </x:c>
       <x:c r="M42" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
       </x:c>
       <x:c r="N42" s="54" t="n">
-        <x:v>150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="O42" s="54" t="n">
         <x:v>0</x:v>
@@ -4552,7 +4619,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X42" s="44" t="n">
-        <x:v>385</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="Y42" s="44" t="n">
         <x:v>1</x:v>
@@ -4593,57 +4660,57 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI42" s="44" t="str">
-        <x:v>MAW-Stats</x:v>
+        <x:v>Skript</x:v>
       </x:c>
       <x:c r="AJ42" s="44" t="str">
-        <x:v>8d4+16</x:v>
+        <x:v>2d6+15</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" ht="49" customHeight="1">
+    <x:row r="43" ht="50" customHeight="1">
       <x:c r="A43" s="44" t="n">
         <x:v>32</x:v>
       </x:c>
       <x:c r="B43" s="44" t="str">
-        <x:v>Charele</x:v>
+        <x:v>Judicious Measure</x:v>
       </x:c>
       <x:c r="C43" s="44" t="str">
-        <x:v>Speer</x:v>
+        <x:v>1H-Schwert</x:v>
       </x:c>
       <x:c r="D43" s="44" t="str">
-        <x:v>MM7</x:v>
+        <x:v>MM8</x:v>
       </x:c>
       <x:c r="E43" s="50" t="n">
         <x:f>ROUND(X43*Y43,0)</x:f>
-        <x:v>383</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="F43" s="51" t="n">
-        <x:f>ROUND(($B$5+N43*$H$5+W43)/(1-(AH43/2+(AA43+AB43+AC43+AD43+AE43+AF43)/16+AG43/8)),0)</x:f>
-        <x:v>3842</x:v>
+        <x:f>ROUND(($B$5+N43*$H$5+W43)/(1-(AH43/2+(AA43+AB43+AC43+AD43+AE43+AF43)/16+MIN(AA43:AF43)/8)),0)</x:f>
+        <x:v>4322</x:v>
       </x:c>
       <x:c r="G43" s="51" t="n">
         <x:f>F43-$B$8</x:f>
-        <x:v>0</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="H43" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I43" s="44" t="str">
-        <x:v>Keine spezifischen Defensivboni dokumentiert.</x:v>
+        <x:v>+40 Endurance und +40 Luck vor Levelskalierung.</x:v>
       </x:c>
       <x:c r="J43" s="44" t="str">
-        <x:v>Hoher physischer Grundschaden ohne klaren Trefferproc.</x:v>
+        <x:v>Ogre Slaying laut Itemtext (MM8-Engine/Itemtext, nicht in Lua): situationsabhängiger Bonus gegen Oger.</x:v>
       </x:c>
       <x:c r="K43" s="44" t="str">
-        <x:v>1H/2H-fähig.</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="L43" s="44" t="str">
-        <x:v>Keine besonderen Schadensprocs.</x:v>
+        <x:v>Ogre Slaying nicht in DPS.</x:v>
       </x:c>
       <x:c r="M43" s="44" t="str">
         <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
       </x:c>
       <x:c r="N43" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="O43" s="54" t="n">
         <x:v>0</x:v>
@@ -4673,7 +4740,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X43" s="44" t="n">
-        <x:v>383</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="Y43" s="44" t="n">
         <x:v>1</x:v>
@@ -4714,63 +4781,65 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI43" s="44" t="str">
-        <x:v>Itemdaten</x:v>
+        <x:v>Text + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ43" s="44" t="str">
-        <x:v>9d9+18</x:v>
+        <x:v>2d4+16</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" ht="49" customHeight="1">
+    <x:row r="44" ht="149" customHeight="1">
       <x:c r="A44" s="44" t="n">
         <x:v>33</x:v>
       </x:c>
       <x:c r="B44" s="44" t="str">
-        <x:v>Tournament Bow</x:v>
+        <x:v>Splitter</x:v>
       </x:c>
       <x:c r="C44" s="44" t="str">
-        <x:v>Bogen</x:v>
+        <x:v>1H-Axt</x:v>
       </x:c>
       <x:c r="D44" s="44" t="str">
-        <x:v>MM8</x:v>
+        <x:v>MM7</x:v>
       </x:c>
       <x:c r="E44" s="50" t="n">
         <x:f>ROUND(X44*Y44,0)</x:f>
-        <x:v>382</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="F44" s="51" t="n">
-        <x:f>ROUND(($B$5+N44*$H$5+W44)/(1-(AH44/2+(AA44+AB44+AC44+AD44+AE44+AF44)/16+AG44/8)),0)</x:f>
-        <x:v>3562</x:v>
+        <x:f>ROUND(($B$5+N44*$H$5+W44)/(1-(AH44/2+(AA44+AB44+AC44+AD44+AE44+AF44)/16+MIN(AA44:AF44)/8)),0)</x:f>
+        <x:v>4187</x:v>
       </x:c>
       <x:c r="G44" s="51" t="n">
         <x:f>F44-$B$8</x:f>
-        <x:v>-280</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="H44" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I44" s="44" t="str">
-        <x:v>+100 Accuracy, −20 AC laut Itemtext; AC-Code nicht separat eingetragen.</x:v>
+        <x:v>Extrem hohe Feuerresistenz (+65000), im MAW-Modell praktisch Feuerimmunität.</x:v>
       </x:c>
       <x:c r="J44" s="44" t="str">
-        <x:v>Bow-Skillbonus (+4 MAW-Code) und hohe Accuracy; kein zusätzlicher Trefferproc.</x:v>
+        <x:v>Bei Treffer Wing Buffet (Zauber 125) und Fireball (Zauber 6) am Ziel; zusätzlich geskripteter Feuerschaden 10 Basis (×2 bei Level 100), am Tag 4.5 von zzMaw_Legendaries.lua:19 (t.Result=0) wieder genullt.</x:v>
       </x:c>
       <x:c r="K44" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L44" s="44" t="str">
-        <x:v>Skillbonus in Modell-DPS.</x:v>
+        <x:v>Explosion/Fläche nicht in DPS.</x:v>
       </x:c>
       <x:c r="M44" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N44" s="54" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O44" s="54" t="n">
-        <x:v>-25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="P44" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>81250</x:v>
       </x:c>
       <x:c r="Q44" s="54" t="n">
         <x:v>0</x:v>
@@ -4794,7 +4863,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X44" s="44" t="n">
-        <x:v>382</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="Y44" s="44" t="n">
         <x:v>1</x:v>
@@ -4804,7 +4873,7 @@
       </x:c>
       <x:c r="AA44" s="56" t="n">
         <x:f>IF($F$5+P44&gt;=65000,1,1-1/(1+($F$5+P44)/(60+$J$5*0.5)))</x:f>
-        <x:v>0.3125</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AB44" s="56" t="n">
         <x:f>IF($F$5+Q44&gt;=65000,1,1-1/(1+($F$5+Q44)/(60+$J$5*0.5)))</x:f>
@@ -4832,60 +4901,60 @@
       </x:c>
       <x:c r="AH44" s="56" t="n">
         <x:f>1-((5+$J$5*2)/(10+$J$5*2+MAX(0,$D$5+O44)))*(1/(1+MAX(0,$D$5+O44)/(90+$J$5*0.25)))</x:f>
-        <x:v>0.5646352723915051</x:v>
+        <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI44" s="44" t="str">
-        <x:v>Skript + Text</x:v>
+        <x:v>Skript + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ44" s="44" t="str">
-        <x:v>12d3+14</x:v>
+        <x:v>4d2+13</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" ht="49" customHeight="1">
+    <x:row r="45" ht="50" customHeight="1">
       <x:c r="A45" s="44" t="n">
         <x:v>34</x:v>
       </x:c>
       <x:c r="B45" s="44" t="str">
-        <x:v>Mash</x:v>
+        <x:v>Cronos</x:v>
       </x:c>
       <x:c r="C45" s="44" t="str">
-        <x:v>Mace</x:v>
+        <x:v>1H-Axt</x:v>
       </x:c>
       <x:c r="D45" s="44" t="str">
-        <x:v>MM7</x:v>
+        <x:v>MM6</x:v>
       </x:c>
       <x:c r="E45" s="50" t="n">
         <x:f>ROUND(X45*Y45,0)</x:f>
-        <x:v>357</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="F45" s="51" t="n">
-        <x:f>ROUND(($B$5+N45*$H$5+W45)/(1-(AH45/2+(AA45+AB45+AC45+AD45+AE45+AF45)/16+AG45/8)),0)</x:f>
-        <x:v>3842</x:v>
+        <x:f>ROUND(($B$5+N45*$H$5+W45)/(1-(AH45/2+(AA45+AB45+AC45+AD45+AE45+AF45)/16+MIN(AA45:AF45)/8)),0)</x:f>
+        <x:v>5282</x:v>
       </x:c>
       <x:c r="G45" s="51" t="n">
         <x:f>F45-$B$8</x:f>
-        <x:v>0</x:v>
+        <x:v>1440</x:v>
       </x:c>
       <x:c r="H45" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I45" s="44" t="str">
-        <x:v>+150 Might, −40 Speed/Intellect/Personality vor Skalierung.</x:v>
+        <x:v>+120 Endurance, −60 Luck vor Levelskalierung.</x:v>
       </x:c>
       <x:c r="J45" s="44" t="str">
-        <x:v>Großer Might-Bonus; etwas langsamer durch Speed-Malus.</x:v>
+        <x:v>Keine zusätzliche Schadenswirkung im MAW-Skript nachgewiesen.</x:v>
       </x:c>
       <x:c r="K45" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L45" s="44" t="str">
-        <x:v>Attributboni sind in DPS berücksichtigt.</x:v>
+        <x:v>Keine separaten Procs.</x:v>
       </x:c>
       <x:c r="M45" s="44" t="str">
         <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
       </x:c>
       <x:c r="N45" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="O45" s="54" t="n">
         <x:v>0</x:v>
@@ -4915,7 +4984,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X45" s="44" t="n">
-        <x:v>357</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="Y45" s="44" t="n">
         <x:v>1</x:v>
@@ -4959,28 +5028,28 @@
         <x:v>MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ45" s="44" t="str">
-        <x:v>6d6+15</x:v>
+        <x:v>4d2+16</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="49" customHeight="1">
+    <x:row r="46" ht="50" customHeight="1">
       <x:c r="A46" s="44" t="n">
         <x:v>35</x:v>
       </x:c>
       <x:c r="B46" s="44" t="str">
-        <x:v>Percival</x:v>
+        <x:v>Justice</x:v>
       </x:c>
       <x:c r="C46" s="44" t="str">
-        <x:v>Bogen</x:v>
+        <x:v>Mace</x:v>
       </x:c>
       <x:c r="D46" s="44" t="str">
-        <x:v>MM6</x:v>
+        <x:v>MM7</x:v>
       </x:c>
       <x:c r="E46" s="50" t="n">
         <x:f>ROUND(X46*Y46,0)</x:f>
-        <x:v>355</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="F46" s="51" t="n">
-        <x:f>ROUND(($B$5+N46*$H$5+W46)/(1-(AH46/2+(AA46+AB46+AC46+AD46+AE46+AF46)/16+AG46/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N46*$H$5+W46)/(1-(AH46/2+(AA46+AB46+AC46+AD46+AE46+AF46)/16+MIN(AA46:AF46)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G46" s="51" t="n">
@@ -4991,19 +5060,19 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I46" s="44" t="str">
-        <x:v>+40 Speed vor Skalierung; Bonus-Erholung reduziert Schaden nicht direkt.</x:v>
+        <x:v>−40 Speed vor Skalierung.</x:v>
       </x:c>
       <x:c r="J46" s="44" t="str">
-        <x:v>Feuerexplosion beim Pfeileinschlag (geskriptet), besonders gegen Gruppen; geringere Erholungszeit.</x:v>
+        <x:v>Undead Slaying nur laut Itemtext (nicht in Lua); Mind- und Body-Magie je +50 % des Basis-Skills (artifactSpellBonus).</x:v>
       </x:c>
       <x:c r="K46" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L46" s="44" t="str">
-        <x:v>Explosion und Recovery-Bonus nicht in Modell-DPS.</x:v>
+        <x:v>Slayer/Zauber-Boni nicht in DPS.</x:v>
       </x:c>
       <x:c r="M46" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
       </x:c>
       <x:c r="N46" s="54" t="n">
         <x:v>0</x:v>
@@ -5036,7 +5105,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X46" s="44" t="n">
-        <x:v>355</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="Y46" s="44" t="n">
         <x:v>1</x:v>
@@ -5077,31 +5146,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI46" s="44" t="str">
-        <x:v>Skript</x:v>
+        <x:v>Text + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ46" s="44" t="str">
-        <x:v>6d2+13</x:v>
+        <x:v>2d8+24</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" ht="49" customHeight="1">
+    <x:row r="47" ht="149" customHeight="1">
       <x:c r="A47" s="44" t="n">
         <x:v>36</x:v>
       </x:c>
       <x:c r="B47" s="44" t="str">
-        <x:v>Staff of the Swamp</x:v>
+        <x:v>Foulfang</x:v>
       </x:c>
       <x:c r="C47" s="44" t="str">
-        <x:v>Staff</x:v>
+        <x:v>Dolch</x:v>
       </x:c>
       <x:c r="D47" s="44" t="str">
         <x:v>MM8</x:v>
       </x:c>
       <x:c r="E47" s="50" t="n">
         <x:f>ROUND(X47*Y47,0)</x:f>
-        <x:v>352</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="F47" s="51" t="n">
-        <x:f>ROUND(($B$5+N47*$H$5+W47)/(1-(AH47/2+(AA47+AB47+AC47+AD47+AE47+AF47)/16+AG47/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N47*$H$5+W47)/(1-(AH47/2+(AA47+AB47+AC47+AD47+AE47+AF47)/16+MIN(AA47:AF47)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G47" s="51" t="n">
@@ -5109,22 +5178,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H47" s="44" t="str">
-        <x:v>Nein</x:v>
+        <x:v>Laut Itemtext (nicht in Lua)</x:v>
       </x:c>
       <x:c r="I47" s="44" t="str">
-        <x:v>Immunität gegen Krankheit, Paralyse und Gift laut Itemdaten; Wert nicht in Vitality.</x:v>
+        <x:v>Potenzielle Selbstheilung, nicht in der Stats-Menü-Vitality.</x:v>
       </x:c>
       <x:c r="J47" s="44" t="str">
-        <x:v>Schutzstab ohne direkten Schadensproc; Shielding laut Text.</x:v>
+        <x:v>Vampiric und 20 Giftschaden laut Itemtext (MM8-Engine/Itemtext, nicht in Lua); MAW-Leech (zzMaw-Items.lua:3722) erfasst nur Enchant 16/41; Giftschaden vermutlich wirkungslos, da zzMaw_Legendaries.lua:19 ItemAdditionalDamage am Tag 4.5 auf 0 setzt.</x:v>
       </x:c>
       <x:c r="K47" s="44" t="str">
-        <x:v>—</x:v>
+        <x:v>Nur Vampire (ExtraArtifacts).</x:v>
       </x:c>
       <x:c r="L47" s="44" t="str">
-        <x:v>Immunitäten nicht als DPS.</x:v>
+        <x:v>Gift und Lifesteal nicht in DPS.</x:v>
       </x:c>
       <x:c r="M47" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N47" s="54" t="n">
         <x:v>0</x:v>
@@ -5157,7 +5228,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X47" s="44" t="n">
-        <x:v>352</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="Y47" s="44" t="n">
         <x:v>1</x:v>
@@ -5198,31 +5269,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI47" s="44" t="str">
-        <x:v>Itemtext</x:v>
+        <x:v>Itemtext; Lua nur Tragbedingung (Vampire), kein Leech-Eintrag</x:v>
       </x:c>
       <x:c r="AJ47" s="44" t="str">
-        <x:v>8d4+11</x:v>
+        <x:v>2d3+12</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" ht="49" customHeight="1">
+    <x:row r="48" ht="50" customHeight="1">
       <x:c r="A48" s="44" t="n">
         <x:v>37</x:v>
       </x:c>
       <x:c r="B48" s="44" t="str">
-        <x:v>Merlin</x:v>
+        <x:v>Mash</x:v>
       </x:c>
       <x:c r="C48" s="44" t="str">
-        <x:v>Staff</x:v>
+        <x:v>Mace</x:v>
       </x:c>
       <x:c r="D48" s="44" t="str">
-        <x:v>MM6</x:v>
+        <x:v>MM7</x:v>
       </x:c>
       <x:c r="E48" s="50" t="n">
         <x:f>ROUND(X48*Y48,0)</x:f>
-        <x:v>350</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="F48" s="51" t="n">
-        <x:f>ROUND(($B$5+N48*$H$5+W48)/(1-(AH48/2+(AA48+AB48+AC48+AD48+AE48+AF48)/16+AG48/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N48*$H$5+W48)/(1-(AH48/2+(AA48+AB48+AC48+AD48+AE48+AF48)/16+MIN(AA48:AF48)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G48" s="51" t="n">
@@ -5233,19 +5304,19 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I48" s="44" t="str">
-        <x:v>+120 Intellect und Personality, +200 SP, SP-Regeneration; ohne Mana Shield kein Vitality-Bonus.</x:v>
+        <x:v>+150 Might, −40 Speed/Intellect/Personality vor Skalierung.</x:v>
       </x:c>
       <x:c r="J48" s="44" t="str">
-        <x:v>Angriffserholungsbonus −20 (effektiv ca. −10 %) im Skript; als Caster-Waffe interessant.</x:v>
+        <x:v>Großer Might-Bonus; etwas langsamer durch Speed-Malus.</x:v>
       </x:c>
       <x:c r="K48" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L48" s="44" t="str">
-        <x:v>Erholungseffekt nicht in Modell-DPS.</x:v>
+        <x:v>Attributboni sind in DPS berücksichtigt.</x:v>
       </x:c>
       <x:c r="M48" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
       </x:c>
       <x:c r="N48" s="54" t="n">
         <x:v>0</x:v>
@@ -5278,7 +5349,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X48" s="44" t="n">
-        <x:v>350</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="Y48" s="44" t="n">
         <x:v>1</x:v>
@@ -5319,57 +5390,59 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI48" s="44" t="str">
-        <x:v>Skript</x:v>
+        <x:v>MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ48" s="44" t="str">
-        <x:v>6d6+10</x:v>
+        <x:v>1d3+15</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" ht="49" customHeight="1">
+    <x:row r="49" ht="149" customHeight="1">
       <x:c r="A49" s="44" t="n">
         <x:v>38</x:v>
       </x:c>
       <x:c r="B49" s="44" t="str">
-        <x:v>Thor</x:v>
+        <x:v>Guardian</x:v>
       </x:c>
       <x:c r="C49" s="44" t="str">
-        <x:v>Mace</x:v>
+        <x:v>Speer</x:v>
       </x:c>
       <x:c r="D49" s="44" t="str">
-        <x:v>MM6</x:v>
+        <x:v>MM8</x:v>
       </x:c>
       <x:c r="E49" s="50" t="n">
         <x:f>ROUND(X49*Y49,0)</x:f>
-        <x:v>338</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="F49" s="51" t="n">
-        <x:f>ROUND(($B$5+N49*$H$5+W49)/(1-(AH49/2+(AA49+AB49+AC49+AD49+AE49+AF49)/16+AG49/8)),0)</x:f>
-        <x:v>3842</x:v>
+        <x:f>ROUND(($B$5+N49*$H$5+W49)/(1-(AH49/2+(AA49+AB49+AC49+AD49+AE49+AF49)/16+MIN(AA49:AF49)/8)),0)</x:f>
+        <x:v>4082</x:v>
       </x:c>
       <x:c r="G49" s="51" t="n">
         <x:f>F49-$B$8</x:f>
-        <x:v>0</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="H49" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I49" s="44" t="str">
-        <x:v>+75 Might vor Levelskalierung.</x:v>
+        <x:v>+20 auf alle Attribute vor Levelskalierung; Endurance/Speed enthalten.</x:v>
       </x:c>
       <x:c r="J49" s="44" t="str">
-        <x:v>Geskripteter zusätzlicher Treffer-Schaden (10 Basis) und Spezialzauber beim Treffer.</x:v>
+        <x:v>Körperschaden 20–40 pro Treffer laut Itemtext (MM8-Engine/Itemtext, nicht in Lua), vermutlich wirkungslos, da zzMaw_Legendaries.lua:19 ItemAdditionalDamage am Tag 4.5 auf 0 setzt; +20 auf alle Hauptattribute; als 2H-Hellebarde Speer-GM-Debuff ×1,5.</x:v>
       </x:c>
       <x:c r="K49" s="44" t="str">
-        <x:v>—</x:v>
+        <x:v>Nur zweihändig (MAW stellt Hellebarden auf 2H um).</x:v>
       </x:c>
       <x:c r="L49" s="44" t="str">
-        <x:v>Zauber und Bonus-Hit nicht in DPS.</x:v>
+        <x:v>Körperschaden und Speer-GM-Debuff nicht in DPS.</x:v>
       </x:c>
       <x:c r="M49" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Stats.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N49" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="O49" s="54" t="n">
         <x:v>0</x:v>
@@ -5399,7 +5472,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X49" s="44" t="n">
-        <x:v>338</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="Y49" s="44" t="n">
         <x:v>1</x:v>
@@ -5440,54 +5513,54 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI49" s="44" t="str">
-        <x:v>Skript</x:v>
+        <x:v>Text + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ49" s="44" t="str">
-        <x:v>8d5+14</x:v>
+        <x:v>3d6+18</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" ht="49" customHeight="1">
+    <x:row r="50" ht="50" customHeight="1">
       <x:c r="A50" s="44" t="n">
         <x:v>39</x:v>
       </x:c>
       <x:c r="B50" s="44" t="str">
-        <x:v>Spiritslayer</x:v>
+        <x:v>Mekorig's Hammer</x:v>
       </x:c>
       <x:c r="C50" s="44" t="str">
-        <x:v>Speer</x:v>
+        <x:v>Mace</x:v>
       </x:c>
       <x:c r="D50" s="44" t="str">
-        <x:v>MM8</x:v>
+        <x:v>MM7</x:v>
       </x:c>
       <x:c r="E50" s="50" t="n">
         <x:f>ROUND(X50*Y50,0)</x:f>
-        <x:v>309</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="F50" s="51" t="n">
-        <x:f>ROUND(($B$5+N50*$H$5+W50)/(1-(AH50/2+(AA50+AB50+AC50+AD50+AE50+AF50)/16+AG50/8)),0)</x:f>
-        <x:v>3842</x:v>
+        <x:f>ROUND(($B$5+N50*$H$5+W50)/(1-(AH50/2+(AA50+AB50+AC50+AD50+AE50+AF50)/16+MIN(AA50:AF50)/8)),0)</x:f>
+        <x:v>2039</x:v>
       </x:c>
       <x:c r="G50" s="51" t="n">
         <x:f>F50-$B$8</x:f>
-        <x:v>0</x:v>
+        <x:v>-1803</x:v>
       </x:c>
       <x:c r="H50" s="44" t="str">
-        <x:v>Ja: Gegenstandstext</x:v>
+        <x:v>Nein</x:v>
       </x:c>
       <x:c r="I50" s="44" t="str">
-        <x:v>+80 Might, −40 Luck vor Skalierung; Lebensraub separat.</x:v>
+        <x:v>+75 Might, −100 Luftresistenz vor Levelskalierung.</x:v>
       </x:c>
       <x:c r="J50" s="44" t="str">
-        <x:v>Vampiric laut Itemtext: heilt potenziell beim Treffer; Umsetzung im MAW-Leech-Code nicht vollständig nachgewiesen.</x:v>
+        <x:v>Spirit-Magie +50 % des Basis-Skills (artifactSpellBonus); primär Hybrid-Zauberwaffe.</x:v>
       </x:c>
       <x:c r="K50" s="44" t="str">
-        <x:v>1H/2H-fähig.</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="L50" s="44" t="str">
-        <x:v>Lifesteal nicht in Vitality oder DPS.</x:v>
+        <x:v>Magiebonus nicht als Angriffsschaden eingerechnet.</x:v>
       </x:c>
       <x:c r="M50" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
       </x:c>
       <x:c r="N50" s="54" t="n">
         <x:v>0</x:v>
@@ -5499,7 +5572,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q50" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>-125</x:v>
       </x:c>
       <x:c r="R50" s="54" t="n">
         <x:v>0</x:v>
@@ -5520,7 +5593,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X50" s="44" t="n">
-        <x:v>309</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="Y50" s="44" t="n">
         <x:v>1</x:v>
@@ -5534,7 +5607,7 @@
       </x:c>
       <x:c r="AB50" s="56" t="n">
         <x:f>IF($F$5+Q50&gt;=65000,1,1-1/(1+($F$5+Q50)/(60+$J$5*0.5)))</x:f>
-        <x:v>0.3125</x:v>
+        <x:v>-2.1428571428571423</x:v>
       </x:c>
       <x:c r="AC50" s="56" t="n">
         <x:f>IF($F$5+R50&gt;=65000,1,1-1/(1+($F$5+R50)/(60+$J$5*0.5)))</x:f>
@@ -5561,63 +5634,63 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI50" s="44" t="str">
-        <x:v>Itemtext, Lifeleech ungeprüft</x:v>
+        <x:v>MAW-Stats + MAW-Zauberbonus</x:v>
       </x:c>
       <x:c r="AJ50" s="44" t="str">
-        <x:v>5d9+16</x:v>
+        <x:v>2d5+15</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" ht="49" customHeight="1">
+    <x:row r="51" ht="50" customHeight="1">
       <x:c r="A51" s="44" t="n">
         <x:v>40</x:v>
       </x:c>
       <x:c r="B51" s="44" t="str">
-        <x:v>Ares</x:v>
+        <x:v>Poseidon</x:v>
       </x:c>
       <x:c r="C51" s="44" t="str">
-        <x:v>Mace</x:v>
+        <x:v>Speer</x:v>
       </x:c>
       <x:c r="D51" s="44" t="str">
         <x:v>MM6</x:v>
       </x:c>
       <x:c r="E51" s="50" t="n">
         <x:f>ROUND(X51*Y51,0)</x:f>
-        <x:v>303</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="F51" s="51" t="n">
-        <x:f>ROUND(($B$5+N51*$H$5+W51)/(1-(AH51/2+(AA51+AB51+AC51+AD51+AE51+AF51)/16+AG51/8)),0)</x:f>
-        <x:v>3986</x:v>
+        <x:f>ROUND(($B$5+N51*$H$5+W51)/(1-(AH51/2+(AA51+AB51+AC51+AD51+AE51+AF51)/16+MIN(AA51:AF51)/8)),0)</x:f>
+        <x:v>4171</x:v>
       </x:c>
       <x:c r="G51" s="51" t="n">
         <x:f>F51-$B$8</x:f>
-        <x:v>144</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="H51" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I51" s="44" t="str">
-        <x:v>+100 Feuerresistenz vor Skalierung.</x:v>
+        <x:v>+40 Might, Endurance, Accuracy; −10 Speed und −10 AC vor Skalierung.</x:v>
       </x:c>
       <x:c r="J51" s="44" t="str">
-        <x:v>Geskripteter Feuerschaden (+30 Basis je Treffer).</x:v>
+        <x:v>Hoher Grundschaden; Speer-GM-Resistenzsenkung kann Folgeangriffe verstärken.</x:v>
       </x:c>
       <x:c r="K51" s="44" t="str">
-        <x:v>—</x:v>
+        <x:v>1H/2H-fähig.</x:v>
       </x:c>
       <x:c r="L51" s="44" t="str">
-        <x:v>Feuerschaden nicht in phys. DPS.</x:v>
+        <x:v>Speer-GM-Debuff nicht in Basis-DPS.</x:v>
       </x:c>
       <x:c r="M51" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
       </x:c>
       <x:c r="N51" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="O51" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>-12.5</x:v>
       </x:c>
       <x:c r="P51" s="54" t="n">
-        <x:v>125</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Q51" s="54" t="n">
         <x:v>0</x:v>
@@ -5641,7 +5714,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X51" s="44" t="n">
-        <x:v>303</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="Y51" s="44" t="n">
         <x:v>1</x:v>
@@ -5651,7 +5724,7 @@
       </x:c>
       <x:c r="AA51" s="56" t="n">
         <x:f>IF($F$5+P51&gt;=65000,1,1-1/(1+($F$5+P51)/(60+$J$5*0.5)))</x:f>
-        <x:v>0.6140350877192982</x:v>
+        <x:v>0.3125</x:v>
       </x:c>
       <x:c r="AB51" s="56" t="n">
         <x:f>IF($F$5+Q51&gt;=65000,1,1-1/(1+($F$5+Q51)/(60+$J$5*0.5)))</x:f>
@@ -5679,34 +5752,34 @@
       </x:c>
       <x:c r="AH51" s="56" t="n">
         <x:f>1-((5+$J$5*2)/(10+$J$5*2+MAX(0,$D$5+O51)))*(1/(1+MAX(0,$D$5+O51)/(90+$J$5*0.25)))</x:f>
-        <x:v>0.6462865716429107</x:v>
+        <x:v>0.6086730988691773</x:v>
       </x:c>
       <x:c r="AI51" s="44" t="str">
-        <x:v>Skript + MAW-Stats</x:v>
+        <x:v>MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ51" s="44" t="str">
-        <x:v>8d4+16</x:v>
+        <x:v>2d6+19</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" ht="49" customHeight="1">
+    <x:row r="52" ht="149" customHeight="1">
       <x:c r="A52" s="44" t="n">
         <x:v>41</x:v>
       </x:c>
       <x:c r="B52" s="44" t="str">
-        <x:v>Scepter of Kings</x:v>
+        <x:v>Thor</x:v>
       </x:c>
       <x:c r="C52" s="44" t="str">
         <x:v>Mace</x:v>
       </x:c>
       <x:c r="D52" s="44" t="str">
-        <x:v>MM8</x:v>
+        <x:v>MM6</x:v>
       </x:c>
       <x:c r="E52" s="50" t="n">
         <x:f>ROUND(X52*Y52,0)</x:f>
-        <x:v>303</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="F52" s="51" t="n">
-        <x:f>ROUND(($B$5+N52*$H$5+W52)/(1-(AH52/2+(AA52+AB52+AC52+AD52+AE52+AF52)/16+AG52/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N52*$H$5+W52)/(1-(AH52/2+(AA52+AB52+AC52+AD52+AE52+AF52)/16+MIN(AA52:AF52)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G52" s="51" t="n">
@@ -5717,19 +5790,21 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I52" s="44" t="str">
-        <x:v>+80 Personality vor Skalierung; HP-Regeneration ist nicht Teil des Vitality-Werts.</x:v>
+        <x:v>+75 Might vor Levelskalierung.</x:v>
       </x:c>
       <x:c r="J52" s="44" t="str">
-        <x:v>Kein zusätzlicher Trefferproc; HP-Regeneration während des Tragens.</x:v>
+        <x:v>Geskripteter Zusatzschaden 10 Basis je Treffer (×2 bei Level 100); bei Treffer Wing Buffet (Rückstoß, Zauber 125) und Lightning Bolt (Zauber 18), falls das Ziel überlebt; Zusatzschaden am Tag 4.5 von zzMaw_Legendaries.lua:19 (t.Result=0) wieder genullt.</x:v>
       </x:c>
       <x:c r="K52" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L52" s="44" t="str">
-        <x:v>Heilung/Regeneration nicht in DPS.</x:v>
+        <x:v>Zauber und Bonus-Hit nicht in DPS.</x:v>
       </x:c>
       <x:c r="M52" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N52" s="54" t="n">
         <x:v>0</x:v>
@@ -5762,13 +5837,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X52" s="44" t="n">
-        <x:v>303</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="Y52" s="44" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Z52" s="44" t="n">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AA52" s="56" t="n">
         <x:f>IF($F$5+P52&gt;=65000,1,1-1/(1+($F$5+P52)/(60+$J$5*0.5)))</x:f>
@@ -5806,51 +5881,53 @@
         <x:v>Skript + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ52" s="44" t="str">
-        <x:v>8d4+16</x:v>
+        <x:v>2d5+14</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" ht="49" customHeight="1">
+    <x:row r="53" ht="149" customHeight="1">
       <x:c r="A53" s="44" t="n">
         <x:v>42</x:v>
       </x:c>
       <x:c r="B53" s="44" t="str">
-        <x:v>Splitter</x:v>
+        <x:v>Old Nick</x:v>
       </x:c>
       <x:c r="C53" s="44" t="str">
-        <x:v>1H-Axt</x:v>
+        <x:v>Dolch</x:v>
       </x:c>
       <x:c r="D53" s="44" t="str">
         <x:v>MM7</x:v>
       </x:c>
       <x:c r="E53" s="50" t="n">
         <x:f>ROUND(X53*Y53,0)</x:f>
-        <x:v>303</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="F53" s="51" t="n">
-        <x:f>ROUND(($B$5+N53*$H$5+W53)/(1-(AH53/2+(AA53+AB53+AC53+AD53+AE53+AF53)/16+AG53/8)),0)</x:f>
-        <x:v>4187</x:v>
+        <x:f>ROUND(($B$5+N53*$H$5+W53)/(1-(AH53/2+(AA53+AB53+AC53+AD53+AE53+AF53)/16+MIN(AA53:AF53)/8)),0)</x:f>
+        <x:v>3842</x:v>
       </x:c>
       <x:c r="G53" s="51" t="n">
         <x:f>F53-$B$8</x:f>
-        <x:v>345</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H53" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I53" s="44" t="str">
-        <x:v>Extrem hohe Feuerresistenz (+65000), im MAW-Modell praktisch Feuerimmunität.</x:v>
+        <x:v>+5 Disarm Traps vor Levelskalierung (Level 100: +6); kein direkter Vitality-Effekt.</x:v>
       </x:c>
       <x:c r="J53" s="44" t="str">
-        <x:v>Explosive Feuerwirkung bei Treffern; zusätzlich Feuer-Zusatzschaden (10 Basis).</x:v>
+        <x:v>Geskripteter Wasserschaden 36 Basis je Treffer (×2 bei Level 100; Itemtext: 54 Gift), gegen Elfen verdoppelt – nur der Zusatzschaden, nicht der Waffentreffer; am Tag 4.5 von zzMaw_Legendaries.lua:19 (t.Result=0) wieder genullt.</x:v>
       </x:c>
       <x:c r="K53" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L53" s="44" t="str">
-        <x:v>Explosion/Fläche nicht in DPS.</x:v>
+        <x:v>Wasser und Elf-Slaying nicht in DPS.</x:v>
       </x:c>
       <x:c r="M53" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N53" s="54" t="n">
         <x:v>0</x:v>
@@ -5859,7 +5936,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="P53" s="54" t="n">
-        <x:v>81250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Q53" s="54" t="n">
         <x:v>0</x:v>
@@ -5883,7 +5960,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X53" s="44" t="n">
-        <x:v>303</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="Y53" s="44" t="n">
         <x:v>1</x:v>
@@ -5893,7 +5970,7 @@
       </x:c>
       <x:c r="AA53" s="56" t="n">
         <x:f>IF($F$5+P53&gt;=65000,1,1-1/(1+($F$5+P53)/(60+$J$5*0.5)))</x:f>
-        <x:v>1</x:v>
+        <x:v>0.3125</x:v>
       </x:c>
       <x:c r="AB53" s="56" t="n">
         <x:f>IF($F$5+Q53&gt;=65000,1,1-1/(1+($F$5+Q53)/(60+$J$5*0.5)))</x:f>
@@ -5924,18 +6001,18 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI53" s="44" t="str">
-        <x:v>Skript + MAW-Stats</x:v>
+        <x:v>Skript + MAW-Skills</x:v>
       </x:c>
       <x:c r="AJ53" s="44" t="str">
-        <x:v>4d2+13</x:v>
+        <x:v>2d2+10</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" ht="49" customHeight="1">
+    <x:row r="54" ht="50" customHeight="1">
       <x:c r="A54" s="44" t="n">
         <x:v>43</x:v>
       </x:c>
       <x:c r="B54" s="44" t="str">
-        <x:v>Guardian</x:v>
+        <x:v>Spiritslayer</x:v>
       </x:c>
       <x:c r="C54" s="44" t="str">
         <x:v>Speer</x:v>
@@ -5945,36 +6022,36 @@
       </x:c>
       <x:c r="E54" s="50" t="n">
         <x:f>ROUND(X54*Y54,0)</x:f>
-        <x:v>301</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="F54" s="51" t="n">
-        <x:f>ROUND(($B$5+N54*$H$5+W54)/(1-(AH54/2+(AA54+AB54+AC54+AD54+AE54+AF54)/16+AG54/8)),0)</x:f>
-        <x:v>4082</x:v>
+        <x:f>ROUND(($B$5+N54*$H$5+W54)/(1-(AH54/2+(AA54+AB54+AC54+AD54+AE54+AF54)/16+MIN(AA54:AF54)/8)),0)</x:f>
+        <x:v>3842</x:v>
       </x:c>
       <x:c r="G54" s="51" t="n">
         <x:f>F54-$B$8</x:f>
-        <x:v>240</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H54" s="44" t="str">
-        <x:v>Nein</x:v>
+        <x:v>Laut Itemtext (nicht in Lua)</x:v>
       </x:c>
       <x:c r="I54" s="44" t="str">
-        <x:v>+20 auf alle Attribute vor Levelskalierung; Endurance/Speed enthalten.</x:v>
+        <x:v>+80 Might, −40 Luck vor Skalierung; Lebensraub separat.</x:v>
       </x:c>
       <x:c r="J54" s="44" t="str">
-        <x:v>Körperschaden pro Treffer; zusätzlich kleine Boni auf alle Hauptattribute.</x:v>
+        <x:v>Vampiric laut Itemtext (MM8-Engine/Itemtext, nicht in Lua): heilt potenziell beim Treffer; MAW-Leech (zzMaw-Items.lua:3722) erfasst nur Enchant 16/41.</x:v>
       </x:c>
       <x:c r="K54" s="44" t="str">
-        <x:v>1H/2H-fähig (Hellebarde).</x:v>
+        <x:v>1H/2H-fähig.</x:v>
       </x:c>
       <x:c r="L54" s="44" t="str">
-        <x:v>Körperschaden nicht in DPS.</x:v>
+        <x:v>Lifesteal nicht in Vitality oder DPS.</x:v>
       </x:c>
       <x:c r="M54" s="44" t="str">
         <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
       </x:c>
       <x:c r="N54" s="54" t="n">
-        <x:v>25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="O54" s="54" t="n">
         <x:v>0</x:v>
@@ -6004,7 +6081,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X54" s="44" t="n">
-        <x:v>301</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="Y54" s="44" t="n">
         <x:v>1</x:v>
@@ -6045,63 +6122,65 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI54" s="44" t="str">
-        <x:v>Text + MAW-Stats</x:v>
+        <x:v>MAW-Stats + Itemtext; Vampiric nicht in Lua</x:v>
       </x:c>
       <x:c r="AJ54" s="44" t="str">
-        <x:v>6d6+18</x:v>
+        <x:v>1d9+16</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" ht="49" customHeight="1">
+    <x:row r="55" ht="149" customHeight="1">
       <x:c r="A55" s="44" t="n">
         <x:v>44</x:v>
       </x:c>
       <x:c r="B55" s="44" t="str">
-        <x:v>Wyrm Spitter</x:v>
+        <x:v>Ares</x:v>
       </x:c>
       <x:c r="C55" s="44" t="str">
-        <x:v>Speer</x:v>
+        <x:v>Mace</x:v>
       </x:c>
       <x:c r="D55" s="44" t="str">
-        <x:v>MM8</x:v>
+        <x:v>MM6</x:v>
       </x:c>
       <x:c r="E55" s="50" t="n">
         <x:f>ROUND(X55*Y55,0)</x:f>
-        <x:v>293</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="F55" s="51" t="n">
-        <x:f>ROUND(($B$5+N55*$H$5+W55)/(1-(AH55/2+(AA55+AB55+AC55+AD55+AE55+AF55)/16+AG55/8)),0)</x:f>
-        <x:v>4562</x:v>
+        <x:f>ROUND(($B$5+N55*$H$5+W55)/(1-(AH55/2+(AA55+AB55+AC55+AD55+AE55+AF55)/16+MIN(AA55:AF55)/8)),0)</x:f>
+        <x:v>3986</x:v>
       </x:c>
       <x:c r="G55" s="51" t="n">
         <x:f>F55-$B$8</x:f>
-        <x:v>720</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="H55" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I55" s="44" t="str">
-        <x:v>+60 Endurance vor Levelskalierung.</x:v>
+        <x:v>+100 Feuerresistenz vor Skalierung.</x:v>
       </x:c>
       <x:c r="J55" s="44" t="str">
-        <x:v>Dragon Slaying und Swift laut Itemtext; gegen Drachen deutlich besser.</x:v>
+        <x:v>Geskripteter Feuerschaden 30 Basis je Treffer (×2 bei Level 100); am Tag 4.5 von zzMaw_Legendaries.lua:19 (t.Result=0) wieder genullt.</x:v>
       </x:c>
       <x:c r="K55" s="44" t="str">
-        <x:v>1H/2H-fähig.</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="L55" s="44" t="str">
-        <x:v>Slayer und Swift nicht eingerechnet.</x:v>
+        <x:v>Feuerschaden nicht in phys. DPS.</x:v>
       </x:c>
       <x:c r="M55" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N55" s="54" t="n">
-        <x:v>75</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="O55" s="54" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="P55" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="Q55" s="54" t="n">
         <x:v>0</x:v>
@@ -6125,7 +6204,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X55" s="44" t="n">
-        <x:v>293</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="Y55" s="44" t="n">
         <x:v>1</x:v>
@@ -6135,7 +6214,7 @@
       </x:c>
       <x:c r="AA55" s="56" t="n">
         <x:f>IF($F$5+P55&gt;=65000,1,1-1/(1+($F$5+P55)/(60+$J$5*0.5)))</x:f>
-        <x:v>0.3125</x:v>
+        <x:v>0.6140350877192982</x:v>
       </x:c>
       <x:c r="AB55" s="56" t="n">
         <x:f>IF($F$5+Q55&gt;=65000,1,1-1/(1+($F$5+Q55)/(60+$J$5*0.5)))</x:f>
@@ -6166,18 +6245,18 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI55" s="44" t="str">
-        <x:v>Text + MAW-Stats</x:v>
+        <x:v>Skript + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ55" s="44" t="str">
-        <x:v>5d9+17</x:v>
+        <x:v>2d4+16</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" ht="49" customHeight="1">
+    <x:row r="56" ht="100" customHeight="1">
       <x:c r="A56" s="44" t="n">
         <x:v>45</x:v>
       </x:c>
       <x:c r="B56" s="44" t="str">
-        <x:v>Breaker</x:v>
+        <x:v>Scepter of Kings</x:v>
       </x:c>
       <x:c r="C56" s="44" t="str">
         <x:v>Mace</x:v>
@@ -6187,36 +6266,37 @@
       </x:c>
       <x:c r="E56" s="50" t="n">
         <x:f>ROUND(X56*Y56,0)</x:f>
-        <x:v>287</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="F56" s="51" t="n">
-        <x:f>ROUND(($B$5+N56*$H$5+W56)/(1-(AH56/2+(AA56+AB56+AC56+AD56+AE56+AF56)/16+AG56/8)),0)</x:f>
-        <x:v>4202</x:v>
+        <x:f>ROUND(($B$5+N56*$H$5+W56)/(1-(AH56/2+(AA56+AB56+AC56+AD56+AE56+AF56)/16+MIN(AA56:AF56)/8)),0)</x:f>
+        <x:v>3842</x:v>
       </x:c>
       <x:c r="G56" s="51" t="n">
         <x:f>F56-$B$8</x:f>
-        <x:v>360</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H56" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I56" s="44" t="str">
-        <x:v>+30 Might, +30 Endurance vor Levelskalierung.</x:v>
+        <x:v>+80 Personality vor Skalierung; HP-Regeneration ist nicht Teil des Vitality-Werts.</x:v>
       </x:c>
       <x:c r="J56" s="44" t="str">
-        <x:v>Körperschaden je Treffer und erhöhte Might.</x:v>
+        <x:v>Kein zusätzlicher Trefferproc; HP-Regeneration 0,2 % der max. HP pro Sekunde (artifactHpRegen; ×2 nach 20 s ohne Schaden, ×4 ohne Gegner in Sicht).</x:v>
       </x:c>
       <x:c r="K56" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L56" s="44" t="str">
-        <x:v>Körperschaden nicht in DPS.</x:v>
+        <x:v>Heilung/Regeneration nicht in DPS.</x:v>
       </x:c>
       <x:c r="M56" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMAW-Skills.lua</x:v>
       </x:c>
       <x:c r="N56" s="54" t="n">
-        <x:v>37.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="O56" s="54" t="n">
         <x:v>0</x:v>
@@ -6246,13 +6326,14 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X56" s="44" t="n">
-        <x:v>287</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="Y56" s="44" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Z56" s="44" t="n">
-        <x:v>0</x:v>
+        <x:f>0.002*($B$5+N56*$H$5+W56)</x:f>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AA56" s="56" t="n">
         <x:f>IF($F$5+P56&gt;=65000,1,1-1/(1+($F$5+P56)/(60+$J$5*0.5)))</x:f>
@@ -6287,57 +6368,58 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI56" s="44" t="str">
-        <x:v>Text + MAW-Stats</x:v>
+        <x:v>MAW-Stats + MAW-Regeneration; Z: 0,2 % der Modell-HP pro Sekunde (HP/s, zzMAW-Skills.lua:1180)</x:v>
       </x:c>
       <x:c r="AJ56" s="44" t="str">
-        <x:v>10d3+12</x:v>
+        <x:v>2d4+16</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" ht="49" customHeight="1">
+    <x:row r="57" ht="100" customHeight="1">
       <x:c r="A57" s="44" t="n">
         <x:v>46</x:v>
       </x:c>
       <x:c r="B57" s="44" t="str">
-        <x:v>Gibbet</x:v>
+        <x:v>Breaker</x:v>
       </x:c>
       <x:c r="C57" s="44" t="str">
-        <x:v>Speer</x:v>
+        <x:v>Mace</x:v>
       </x:c>
       <x:c r="D57" s="44" t="str">
-        <x:v>MM7</x:v>
+        <x:v>MM8</x:v>
       </x:c>
       <x:c r="E57" s="50" t="n">
         <x:f>ROUND(X57*Y57,0)</x:f>
-        <x:v>281</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="F57" s="51" t="n">
-        <x:f>ROUND(($B$5+N57*$H$5+W57)/(1-(AH57/2+(AA57+AB57+AC57+AD57+AE57+AF57)/16+AG57/8)),0)</x:f>
-        <x:v>3842</x:v>
+        <x:f>ROUND(($B$5+N57*$H$5+W57)/(1-(AH57/2+(AA57+AB57+AC57+AD57+AE57+AF57)/16+MIN(AA57:AF57)/8)),0)</x:f>
+        <x:v>4202</x:v>
       </x:c>
       <x:c r="G57" s="51" t="n">
         <x:f>F57-$B$8</x:f>
-        <x:v>0</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="H57" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I57" s="44" t="str">
-        <x:v>Keine direkten Attribute; hoher situativer Offensivnutzen.</x:v>
+        <x:v>+30 Might, +30 Endurance vor Levelskalierung.</x:v>
       </x:c>
       <x:c r="J57" s="44" t="str">
-        <x:v>Geskripteter doppelter Trefferschaden gegen Drachen, Dämonen und Untote; zusätzlicher Feuerschaden (15 Basis).</x:v>
+        <x:v>Körperschaden 20–40 je Treffer laut Itemtext (MM8-Engine/Itemtext, nicht in Lua), vermutlich wirkungslos, da zzMaw_Legendaries.lua:19 ItemAdditionalDamage am Tag 4.5 auf 0 setzt; erhöhte Might.</x:v>
       </x:c>
       <x:c r="K57" s="44" t="str">
-        <x:v>1H/2H-fähig.</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="L57" s="44" t="str">
-        <x:v>Slayer und Feuerschaden nicht enthalten.</x:v>
+        <x:v>Körperschaden nicht in DPS.</x:v>
       </x:c>
       <x:c r="M57" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N57" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>37.5</x:v>
       </x:c>
       <x:c r="O57" s="54" t="n">
         <x:v>0</x:v>
@@ -6367,7 +6449,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X57" s="44" t="n">
-        <x:v>281</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="Y57" s="44" t="n">
         <x:v>1</x:v>
@@ -6408,13 +6490,13 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI57" s="44" t="str">
-        <x:v>Skript</x:v>
+        <x:v>Text + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ57" s="44" t="str">
-        <x:v>6d6+18</x:v>
+        <x:v>3d3+12</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" ht="49" customHeight="1">
+    <x:row r="58" ht="50" customHeight="1">
       <x:c r="A58" s="44" t="n">
         <x:v>47</x:v>
       </x:c>
@@ -6429,15 +6511,15 @@
       </x:c>
       <x:c r="E58" s="50" t="n">
         <x:f>ROUND(X58*Y58,0)</x:f>
-        <x:v>272</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="F58" s="51" t="n">
-        <x:f>ROUND(($B$5+N58*$H$5+W58)/(1-(AH58/2+(AA58+AB58+AC58+AD58+AE58+AF58)/16+AG58/8)),0)</x:f>
-        <x:v>3863</x:v>
+        <x:f>ROUND(($B$5+N58*$H$5+W58)/(1-(AH58/2+(AA58+AB58+AC58+AD58+AE58+AF58)/16+MIN(AA58:AF58)/8)),0)</x:f>
+        <x:v>3592</x:v>
       </x:c>
       <x:c r="G58" s="51" t="n">
         <x:f>F58-$B$8</x:f>
-        <x:v>21</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="H58" s="44" t="str">
         <x:v>Nein</x:v>
@@ -6446,7 +6528,7 @@
         <x:v>+140 Wasserresistenz, −40 Feuerresistenz vor Skalierung.</x:v>
       </x:c>
       <x:c r="J58" s="44" t="str">
-        <x:v>Water Breathing; offensiver Grundschaden ohne Zusatzproc.</x:v>
+        <x:v>Water Breathing laut Itemtext (MM8-Engine/Itemtext, nicht in Lua); offensiver Grundschaden ohne Zusatzproc.</x:v>
       </x:c>
       <x:c r="K58" s="44" t="str">
         <x:v>1H/2H-fähig.</x:v>
@@ -6488,7 +6570,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X58" s="44" t="n">
-        <x:v>272</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="Y58" s="44" t="n">
         <x:v>1</x:v>
@@ -6532,54 +6614,55 @@
         <x:v>MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ58" s="44" t="str">
-        <x:v>6d6+16</x:v>
+        <x:v>2d6+16</x:v>
       </x:c>
     </x:row>
-    <x:row r="59" ht="49" customHeight="1">
+    <x:row r="59" ht="100" customHeight="1">
       <x:c r="A59" s="44" t="n">
         <x:v>48</x:v>
       </x:c>
       <x:c r="B59" s="44" t="str">
-        <x:v>Mekorig's Hammer</x:v>
+        <x:v>Wyrm Spitter</x:v>
       </x:c>
       <x:c r="C59" s="44" t="str">
-        <x:v>Mace</x:v>
+        <x:v>Speer</x:v>
       </x:c>
       <x:c r="D59" s="44" t="str">
-        <x:v>MM7</x:v>
+        <x:v>MM8</x:v>
       </x:c>
       <x:c r="E59" s="50" t="n">
         <x:f>ROUND(X59*Y59,0)</x:f>
-        <x:v>250</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="F59" s="51" t="n">
-        <x:f>ROUND(($B$5+N59*$H$5+W59)/(1-(AH59/2+(AA59+AB59+AC59+AD59+AE59+AF59)/16+AG59/8)),0)</x:f>
-        <x:v>2967</x:v>
+        <x:f>ROUND(($B$5+N59*$H$5+W59)/(1-(AH59/2+(AA59+AB59+AC59+AD59+AE59+AF59)/16+MIN(AA59:AF59)/8)),0)</x:f>
+        <x:v>4562</x:v>
       </x:c>
       <x:c r="G59" s="51" t="n">
         <x:f>F59-$B$8</x:f>
-        <x:v>-875</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="H59" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I59" s="44" t="str">
-        <x:v>+75 Might, −100 Luftresistenz vor Levelskalierung.</x:v>
+        <x:v>+60 Endurance vor Levelskalierung.</x:v>
       </x:c>
       <x:c r="J59" s="44" t="str">
-        <x:v>Spirit-Magic-Bonus; primär Hybrid-Zauberwaffe.</x:v>
+        <x:v>Dragon Slaying und Swift laut Itemtext (MM8-Engine/Itemtext, nicht in Lua); Swift vom MAW-Angriffstempo nicht berücksichtigt (zzMAW-Skills.lua:185 setzt t.Result neu, Swift nur über Enchant 41/59).</x:v>
       </x:c>
       <x:c r="K59" s="44" t="str">
-        <x:v>—</x:v>
+        <x:v>1H/2H-fähig.</x:v>
       </x:c>
       <x:c r="L59" s="44" t="str">
-        <x:v>Magiebonus nicht als Angriffsschaden eingerechnet.</x:v>
+        <x:v>Slayer und Swift nicht eingerechnet.</x:v>
       </x:c>
       <x:c r="M59" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMAW-Skills.lua</x:v>
       </x:c>
       <x:c r="N59" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="O59" s="54" t="n">
         <x:v>0</x:v>
@@ -6588,7 +6671,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q59" s="54" t="n">
-        <x:v>-125</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="R59" s="54" t="n">
         <x:v>0</x:v>
@@ -6609,7 +6692,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X59" s="44" t="n">
-        <x:v>250</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="Y59" s="44" t="n">
         <x:v>1</x:v>
@@ -6623,7 +6706,7 @@
       </x:c>
       <x:c r="AB59" s="56" t="n">
         <x:f>IF($F$5+Q59&gt;=65000,1,1-1/(1+($F$5+Q59)/(60+$J$5*0.5)))</x:f>
-        <x:v>-2.1428571428571423</x:v>
+        <x:v>0.3125</x:v>
       </x:c>
       <x:c r="AC59" s="56" t="n">
         <x:f>IF($F$5+R59&gt;=65000,1,1-1/(1+($F$5+R59)/(60+$J$5*0.5)))</x:f>
@@ -6650,31 +6733,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI59" s="44" t="str">
-        <x:v>MAW-Stats</x:v>
+        <x:v>Text + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ59" s="44" t="str">
-        <x:v>2d5+15</x:v>
+        <x:v>1d9+17</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" ht="49" customHeight="1">
+    <x:row r="60" ht="50" customHeight="1">
       <x:c r="A60" s="44" t="n">
         <x:v>49</x:v>
       </x:c>
       <x:c r="B60" s="44" t="str">
-        <x:v>Justice</x:v>
+        <x:v>Staff of the Swamp</x:v>
       </x:c>
       <x:c r="C60" s="44" t="str">
-        <x:v>Mace</x:v>
+        <x:v>Staff</x:v>
       </x:c>
       <x:c r="D60" s="44" t="str">
-        <x:v>MM7</x:v>
+        <x:v>MM8</x:v>
       </x:c>
       <x:c r="E60" s="50" t="n">
         <x:f>ROUND(X60*Y60,0)</x:f>
-        <x:v>219</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="F60" s="51" t="n">
-        <x:f>ROUND(($B$5+N60*$H$5+W60)/(1-(AH60/2+(AA60+AB60+AC60+AD60+AE60+AF60)/16+AG60/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N60*$H$5+W60)/(1-(AH60/2+(AA60+AB60+AC60+AD60+AE60+AF60)/16+MIN(AA60:AF60)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G60" s="51" t="n">
@@ -6685,16 +6768,16 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I60" s="44" t="str">
-        <x:v>−40 Speed vor Skalierung.</x:v>
+        <x:v>Immunität gegen Krankheit, Paralyse und Gift laut Itemtext (MM8-Engine/Itemtext, nicht in Lua); nicht in Vitality.</x:v>
       </x:c>
       <x:c r="J60" s="44" t="str">
-        <x:v>Undead Slaying; Boni auf Mind-/Body-Magic.</x:v>
+        <x:v>Schutzstab ohne direkten Schadensproc; Shielding laut Itemtext (MM8-Engine/Itemtext, nicht in Lua).</x:v>
       </x:c>
       <x:c r="K60" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L60" s="44" t="str">
-        <x:v>Slayer/Zauber-Boni nicht in DPS.</x:v>
+        <x:v>Immunitäten nicht als DPS.</x:v>
       </x:c>
       <x:c r="M60" s="44" t="str">
         <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
@@ -6730,7 +6813,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X60" s="44" t="n">
-        <x:v>219</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="Y60" s="44" t="n">
         <x:v>1</x:v>
@@ -6771,60 +6854,61 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI60" s="44" t="str">
-        <x:v>Text + MAW-Stats</x:v>
+        <x:v>Itemtext; Lua nur Upscaler-Liste (zzMaw-Items.lua:2452)</x:v>
       </x:c>
       <x:c r="AJ60" s="44" t="str">
-        <x:v>2d4+16</x:v>
+        <x:v>3d4+11</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" ht="49" customHeight="1">
+    <x:row r="61" ht="100" customHeight="1">
       <x:c r="A61" s="44" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="B61" s="44" t="str">
-        <x:v>Staff of Elements</x:v>
+        <x:v>Merlin</x:v>
       </x:c>
       <x:c r="C61" s="44" t="str">
         <x:v>Staff</x:v>
       </x:c>
       <x:c r="D61" s="44" t="str">
-        <x:v>MM8</x:v>
+        <x:v>MM6</x:v>
       </x:c>
       <x:c r="E61" s="50" t="n">
         <x:f>ROUND(X61*Y61,0)</x:f>
-        <x:v>188</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="F61" s="51" t="n">
-        <x:f>ROUND(($B$5+N61*$H$5+W61)/(1-(AH61/2+(AA61+AB61+AC61+AD61+AE61+AF61)/16+AG61/8)),0)</x:f>
-        <x:v>3234</x:v>
+        <x:f>ROUND(($B$5+N61*$H$5+W61)/(1-(AH61/2+(AA61+AB61+AC61+AD61+AE61+AF61)/16+MIN(AA61:AF61)/8)),0)</x:f>
+        <x:v>3842</x:v>
       </x:c>
       <x:c r="G61" s="51" t="n">
         <x:f>F61-$B$8</x:f>
-        <x:v>-608</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H61" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I61" s="44" t="str">
-        <x:v>−40 AC vor Levelskalierung, macht anfälliger.</x:v>
+        <x:v>+120 Intellect und Personality, +200 SP, SP-Regeneration; ohne Mana Shield kein Vitality-Bonus.</x:v>
       </x:c>
       <x:c r="J61" s="44" t="str">
-        <x:v>Verstärkt vier Elementarmagieschulen; für Zauberschaden wertvoll, nicht für Stab-DPS.</x:v>
+        <x:v>Angriffserholungsbonus −20 (effektiv ca. −10 %) im Skript; als Caster-Waffe interessant.</x:v>
       </x:c>
       <x:c r="K61" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L61" s="44" t="str">
-        <x:v>Zauberboni nicht in physischen DPS.</x:v>
+        <x:v>Angriffsverzögerung −20 (×0,9, ExtraArtifacts.lua:269) ist im Modell-DPS enthalten; Zauberboni (Intellect/Personality, SP, SP-Regeneration) nicht.</x:v>
       </x:c>
       <x:c r="M61" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
       </x:c>
       <x:c r="N61" s="54" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O61" s="54" t="n">
-        <x:v>-50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="P61" s="54" t="n">
         <x:v>0</x:v>
@@ -6851,7 +6935,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X61" s="44" t="n">
-        <x:v>188</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="Y61" s="44" t="n">
         <x:v>1</x:v>
@@ -6889,54 +6973,54 @@
       </x:c>
       <x:c r="AH61" s="56" t="n">
         <x:f>1-((5+$J$5*2)/(10+$J$5*2+MAX(0,$D$5+O61)))*(1/(1+MAX(0,$D$5+O61)/(90+$J$5*0.25)))</x:f>
-        <x:v>0.45046620046620045</x:v>
+        <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI61" s="44" t="str">
-        <x:v>MAW-Stats</x:v>
+        <x:v>Skript + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ61" s="44" t="str">
-        <x:v>2d4+4</x:v>
+        <x:v>2d4+10</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" ht="49" customHeight="1">
+    <x:row r="62" ht="50" customHeight="1">
       <x:c r="A62" s="44" t="n">
         <x:v>51</x:v>
       </x:c>
       <x:c r="B62" s="44" t="str">
-        <x:v>Ethric's Staff</x:v>
+        <x:v>Staff of Elements</x:v>
       </x:c>
       <x:c r="C62" s="44" t="str">
         <x:v>Staff</x:v>
       </x:c>
       <x:c r="D62" s="44" t="str">
-        <x:v>MM7</x:v>
+        <x:v>MM8</x:v>
       </x:c>
       <x:c r="E62" s="50" t="n">
         <x:f>ROUND(X62*Y62,0)</x:f>
-        <x:v>153</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F62" s="51" t="n">
-        <x:f>ROUND(($B$5+N62*$H$5+W62)/(1-(AH62/2+(AA62+AB62+AC62+AD62+AE62+AF62)/16+AG62/8)),0)</x:f>
-        <x:v>3842</x:v>
+        <x:f>ROUND(($B$5+N62*$H$5+W62)/(1-(AH62/2+(AA62+AB62+AC62+AD62+AE62+AF62)/16+MIN(AA62:AF62)/8)),0)</x:f>
+        <x:v>3234</x:v>
       </x:c>
       <x:c r="G62" s="51" t="n">
         <x:f>F62-$B$8</x:f>
-        <x:v>0</x:v>
+        <x:v>-608</x:v>
       </x:c>
       <x:c r="H62" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I62" s="44" t="str">
-        <x:v>Verliert als Nicht-Lich fortlaufend HP (Skript); negativer Defensiveffekt.</x:v>
+        <x:v>−40 AC vor Levelskalierung, macht anfälliger.</x:v>
       </x:c>
       <x:c r="J62" s="44" t="str">
-        <x:v>Dark-Magic- und Meditation-Bonus für Zauberwirker.</x:v>
+        <x:v>Feuer-, Luft-, Wasser- und Erdmagie je +50 % des Basis-Skills (artifactSpellBonus); für Zauberschaden wertvoll, nicht für Stab-DPS.</x:v>
       </x:c>
       <x:c r="K62" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L62" s="44" t="str">
-        <x:v>Magische Vorteile nicht als physische DPS gerechnet.</x:v>
+        <x:v>Zauberboni nicht in physischen DPS.</x:v>
       </x:c>
       <x:c r="M62" s="44" t="str">
         <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
@@ -6945,7 +7029,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O62" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>-50</x:v>
       </x:c>
       <x:c r="P62" s="54" t="n">
         <x:v>0</x:v>
@@ -6972,13 +7056,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X62" s="44" t="n">
-        <x:v>153</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Y62" s="44" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Z62" s="44" t="n">
-        <x:v>-3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AA62" s="56" t="n">
         <x:f>IF($F$5+P62&gt;=65000,1,1-1/(1+($F$5+P62)/(60+$J$5*0.5)))</x:f>
@@ -7010,12 +7094,134 @@
       </x:c>
       <x:c r="AH62" s="56" t="n">
         <x:f>1-((5+$J$5*2)/(10+$J$5*2+MAX(0,$D$5+O62)))*(1/(1+MAX(0,$D$5+O62)/(90+$J$5*0.25)))</x:f>
+        <x:v>0.45046620046620045</x:v>
+      </x:c>
+      <x:c r="AI62" s="44" t="str">
+        <x:v>MAW-Stats</x:v>
+      </x:c>
+      <x:c r="AJ62" s="44" t="str">
+        <x:v>2d4+4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="100" customHeight="1">
+      <x:c r="A63" s="44" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B63" s="44" t="str">
+        <x:v>Ethric's Staff</x:v>
+      </x:c>
+      <x:c r="C63" s="44" t="str">
+        <x:v>Staff</x:v>
+      </x:c>
+      <x:c r="D63" s="44" t="str">
+        <x:v>MM7</x:v>
+      </x:c>
+      <x:c r="E63" s="50" t="n">
+        <x:f>ROUND(X63*Y63,0)</x:f>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F63" s="51" t="n">
+        <x:f>ROUND(($B$5+N63*$H$5+W63)/(1-(AH63/2+(AA63+AB63+AC63+AD63+AE63+AF63)/16+MIN(AA63:AF63)/8)),0)</x:f>
+        <x:v>3842</x:v>
+      </x:c>
+      <x:c r="G63" s="51" t="n">
+        <x:f>F63-$B$8</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H63" s="44" t="str">
+        <x:v>Nein</x:v>
+      </x:c>
+      <x:c r="I63" s="44" t="str">
+        <x:v>Verliert als Nicht-Lich fortlaufend HP (Skript); negativer Defensiveffekt.</x:v>
+      </x:c>
+      <x:c r="J63" s="44" t="str">
+        <x:v>Dark-Magie +50 % des Basis-Skills (artifactSpellBonus) und Meditation +8 vor Levelskalierung (Level 100: +10) für Zauberwirker.</x:v>
+      </x:c>
+      <x:c r="K63" s="44" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="L63" s="44" t="str">
+        <x:v>Magische Vorteile nicht als physische DPS gerechnet.</x:v>
+      </x:c>
+      <x:c r="M63" s="44" t="str">
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+      </x:c>
+      <x:c r="N63" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O63" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P63" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q63" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R63" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S63" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T63" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U63" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V63" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W63" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X63" s="44" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="Y63" s="44" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z63" s="44" t="n">
+        <x:v>-3</x:v>
+      </x:c>
+      <x:c r="AA63" s="56" t="n">
+        <x:f>IF($F$5+P63&gt;=65000,1,1-1/(1+($F$5+P63)/(60+$J$5*0.5)))</x:f>
+        <x:v>0.3125</x:v>
+      </x:c>
+      <x:c r="AB63" s="56" t="n">
+        <x:f>IF($F$5+Q63&gt;=65000,1,1-1/(1+($F$5+Q63)/(60+$J$5*0.5)))</x:f>
+        <x:v>0.3125</x:v>
+      </x:c>
+      <x:c r="AC63" s="56" t="n">
+        <x:f>IF($F$5+R63&gt;=65000,1,1-1/(1+($F$5+R63)/(60+$J$5*0.5)))</x:f>
+        <x:v>0.3125</x:v>
+      </x:c>
+      <x:c r="AD63" s="56" t="n">
+        <x:f>IF($F$5+S63&gt;=65000,1,1-1/(1+($F$5+S63)/(60+$J$5*0.5)))</x:f>
+        <x:v>0.3125</x:v>
+      </x:c>
+      <x:c r="AE63" s="56" t="n">
+        <x:f>IF($F$5+T63&gt;=65000,1,1-1/(1+($F$5+T63)/(60+$J$5*0.5)))</x:f>
+        <x:v>0.3125</x:v>
+      </x:c>
+      <x:c r="AF63" s="56" t="n">
+        <x:f>IF($F$5+U63&gt;=65000,1,1-1/(1+($F$5+U63)/(60+$J$5*0.5)))</x:f>
+        <x:v>0.3125</x:v>
+      </x:c>
+      <x:c r="AG63" s="56" t="n">
+        <x:f>IF($F$5+V63&gt;=65000,1,1-1/(1+($F$5+V63)/(60+$J$5*0.5)))</x:f>
+        <x:v>0.3125</x:v>
+      </x:c>
+      <x:c r="AH63" s="56" t="n">
+        <x:f>1-((5+$J$5*2)/(10+$J$5*2+MAX(0,$D$5+O63)))*(1/(1+MAX(0,$D$5+O63)/(90+$J$5*0.25)))</x:f>
         <x:v>0.6462865716429107</x:v>
       </x:c>
-      <x:c r="AI62" s="44" t="str">
-        <x:v>Skript</x:v>
-      </x:c>
-      <x:c r="AJ62" s="44" t="str">
+      <x:c r="AI63" s="44" t="str">
+        <x:v>Skript + MAW-Skills; Z: −3 HP je Regen-Tick (ExtraArtifacts.lua:194-199, 787)</x:v>
+      </x:c>
+      <x:c r="AJ63" s="44" t="str">
         <x:v>2d4+11</x:v>
       </x:c>
     </x:row>
@@ -7024,11 +7230,13 @@
     <x:mergeCell ref="A1:M1"/>
     <x:mergeCell ref="A2:M2"/>
     <x:mergeCell ref="A3:M3"/>
+    <x:mergeCell ref="A4:M4"/>
     <x:mergeCell ref="A7:M7"/>
     <x:mergeCell ref="C8:M8"/>
     <x:mergeCell ref="A9:M9"/>
+    <x:mergeCell ref="A10:M10"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="E12:E62">
+  <x:conditionalFormatting sqref="E12:E63">
     <x:cfRule type="dataBar" priority="1">
       <x:dataBar>
         <x:cfvo type="min"/>
@@ -7042,7 +7250,7 @@
       </x:extLst>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="G12:G62">
+  <x:conditionalFormatting sqref="G12:G63">
     <x:cfRule type="colorScale" priority="2">
       <x:colorScale>
         <x:cfvo type="min"/>
@@ -7069,7 +7277,7 @@
               <x14:fillColor rgb="FF7AB6DE"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>E12:E62</xm:sqref>
+          <xm:sqref>E12:E63</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </x:ext>
@@ -7121,7 +7329,7 @@
   <x:sheetData>
     <x:row r="1" ht="37" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>MAW 4.5  |  BEST OF SURVIVAL / DEF</x:v>
+        <x:v>MAW 4.5  |  BEST OF SURVIVAL / DEF · Stand: Release-Tag 4.5</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -7138,7 +7346,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="9" t="str">
-        <x:v>51 Artefakt-/Reliktwaffen · MM6/7/8 Merge · 2H/1H, Speere, Maces, Staffs, Dolche, Bögen und Armbrust</x:v>
+        <x:v>52 Artefakt-/Reliktwaffen · MM6/7/8 Merge · 2H/1H, Speere, Maces, Staffs, Dolche, Bögen und Armbrüste</x:v>
       </x:c>
       <x:c r="B2" s="9"/>
       <x:c r="C2" s="9"/>
@@ -7170,6 +7378,23 @@
       <x:c r="L3" s="13"/>
       <x:c r="M3" s="13"/>
     </x:row>
+    <x:row r="4" ht="33" customHeight="1">
+      <x:c r="A4" s="58" t="str">
+        <x:v>Stand: Werte, Formeln und Quellenlinks beziehen sich auf den Release-Tag 4.5 von MAW. Im aktuellen main ist das Artefaktsystem umgebaut (Scripts/Modules/MawCore/Artifacts.lua) – dort gelten andere Werte. Korrektur 24.10.2026: Der Resistenzterm mit Gewicht 1/8 ist die schwächste der sechs Resistenzen (zzMaw-Stats.lua, Damage-Kind 12), nicht Spirit. Korrektur 24.10.2026 (2): DPS neu nach Lua-Modell, Texte gegen Lua geprüft, Ania Selving ergänzt.</x:v>
+      </x:c>
+      <x:c r="B4" s="58"/>
+      <x:c r="C4" s="58"/>
+      <x:c r="D4" s="58"/>
+      <x:c r="E4" s="58"/>
+      <x:c r="F4" s="58"/>
+      <x:c r="G4" s="58"/>
+      <x:c r="H4" s="58"/>
+      <x:c r="I4" s="58"/>
+      <x:c r="J4" s="58"/>
+      <x:c r="K4" s="58"/>
+      <x:c r="L4" s="58"/>
+      <x:c r="M4" s="58"/>
+    </x:row>
     <x:row r="5" ht="22" customHeight="1">
       <x:c r="A5" s="16" t="str">
         <x:v>Basis-HP</x:v>
@@ -7236,7 +7461,7 @@
     </x:row>
     <x:row r="7" ht="29" customHeight="1">
       <x:c r="A7" s="23" t="str">
-        <x:v>* Nur Vitality-Parameter (grün) sind editierbar gedacht. HP/Endurance = 5 ist ein transparenter Szenario-Annahmewert, KEINE bestätigte Spielkonstante. DPS bleibt Benchmark (Lv100 / 20 GM).</x:v>
+        <x:v>* Nur die grünen Parameter sind zum Ändern gedacht. HP je Endurance = 5 ist eine Annahme: Im Code gilt HP = HPFactor·⌊End/5⌋ + maxHP·End/1000 (×Bodybuilding), also klassenabhängig (zzMaw-Items.lua:3549-3570, Tag 4.5).</x:v>
       </x:c>
       <x:c r="B7" s="23"/>
       <x:c r="C7" s="23"/>
@@ -7290,6 +7515,23 @@
       <x:c r="L9" s="36"/>
       <x:c r="M9" s="36"/>
     </x:row>
+    <x:row r="10" ht="33" customHeight="1">
+      <x:c r="A10" s="58" t="str">
+        <x:v>DPS-Modell: Nachbildung der MAW-Tooltip-DPS (calcPowerVitality, zzMaw-Stats.lua, Tag 4.5) für eine Modellfigur Lv 100, Waffen-Skill GM 20, Armsmaster GM 20, Basiswerte 100, Mensch ohne Klassenboni, eine Waffe ohne Schild, Monster-Lv 100. Ohne Element-/Zusatzschaden (am Tag 4.5 genullt), ohne Speer-Shred und Buffs. Rassengebundene Waffen (Elderaxe, Elfbane, Lightning Crossbow) ohne Rassenbonus. Engine-Annahmen: Might- und Accuracy-Grundeffekt, Bow-Skill-Addition. Artefakte ohne Ladungen angenommen (MaxCharges = 0, zzMaw-Items.lua:3220-3235). ModAttackDelay (Puck/Merlin/Percival) enthalten.</x:v>
+      </x:c>
+      <x:c r="B10" s="58"/>
+      <x:c r="C10" s="58"/>
+      <x:c r="D10" s="58"/>
+      <x:c r="E10" s="58"/>
+      <x:c r="F10" s="58"/>
+      <x:c r="G10" s="58"/>
+      <x:c r="H10" s="58"/>
+      <x:c r="I10" s="58"/>
+      <x:c r="J10" s="58"/>
+      <x:c r="K10" s="58"/>
+      <x:c r="L10" s="58"/>
+      <x:c r="M10" s="58"/>
+    </x:row>
     <x:row r="11" ht="34" customHeight="1">
       <x:c r="A11" s="40" t="str">
         <x:v>Rang</x:v>
@@ -7400,7 +7642,7 @@
         <x:v>Originalschaden</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="49" customHeight="1">
+    <x:row r="12" ht="50" customHeight="1">
       <x:c r="A12" s="44" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -7415,10 +7657,10 @@
       </x:c>
       <x:c r="E12" s="50" t="n">
         <x:f>ROUND(X12*Y12,0)</x:f>
-        <x:v>385</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="F12" s="51" t="n">
-        <x:f>ROUND(($B$5+N12*$H$5+W12)/(1-(AH12/2+(AA12+AB12+AC12+AD12+AE12+AF12)/16+AG12/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N12*$H$5+W12)/(1-(AH12/2+(AA12+AB12+AC12+AD12+AE12+AF12)/16+MIN(AA12:AF12)/8)),0)</x:f>
         <x:v>5282</x:v>
       </x:c>
       <x:c r="G12" s="51" t="n">
@@ -7474,7 +7716,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X12" s="44" t="n">
-        <x:v>385</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="Y12" s="44" t="n">
         <x:v>1</x:v>
@@ -7518,10 +7760,10 @@
         <x:v>MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ12" s="44" t="str">
-        <x:v>8d4+16</x:v>
+        <x:v>4d2+16</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="49" customHeight="1">
+    <x:row r="13" ht="50" customHeight="1">
       <x:c r="A13" s="44" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -7536,10 +7778,10 @@
       </x:c>
       <x:c r="E13" s="50" t="n">
         <x:f>ROUND(X13*Y13,0)</x:f>
-        <x:v>851</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="F13" s="51" t="n">
-        <x:f>ROUND(($B$5+N13*$H$5+W13)/(1-(AH13/2+(AA13+AB13+AC13+AD13+AE13+AF13)/16+AG13/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N13*$H$5+W13)/(1-(AH13/2+(AA13+AB13+AC13+AD13+AE13+AF13)/16+MIN(AA13:AF13)/8)),0)</x:f>
         <x:v>4773</x:v>
       </x:c>
       <x:c r="G13" s="51" t="n">
@@ -7595,7 +7837,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X13" s="44" t="n">
-        <x:v>851</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="Y13" s="44" t="n">
         <x:v>1</x:v>
@@ -7639,10 +7881,10 @@
         <x:v>MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ13" s="44" t="str">
-        <x:v>8d9+16</x:v>
+        <x:v>3d7+15</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="49" customHeight="1">
+    <x:row r="14" ht="50" customHeight="1">
       <x:c r="A14" s="44" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -7657,10 +7899,10 @@
       </x:c>
       <x:c r="E14" s="50" t="n">
         <x:f>ROUND(X14*Y14,0)</x:f>
-        <x:v>885</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="F14" s="51" t="n">
-        <x:f>ROUND(($B$5+N14*$H$5+W14)/(1-(AH14/2+(AA14+AB14+AC14+AD14+AE14+AF14)/16+AG14/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N14*$H$5+W14)/(1-(AH14/2+(AA14+AB14+AC14+AD14+AE14+AF14)/16+MIN(AA14:AF14)/8)),0)</x:f>
         <x:v>4562</x:v>
       </x:c>
       <x:c r="G14" s="51" t="n">
@@ -7716,7 +7958,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X14" s="44" t="n">
-        <x:v>885</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="Y14" s="44" t="n">
         <x:v>1</x:v>
@@ -7760,10 +8002,10 @@
         <x:v>MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ14" s="44" t="str">
-        <x:v>6d12+20</x:v>
+        <x:v>4d5+16</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="49" customHeight="1">
+    <x:row r="15" ht="100" customHeight="1">
       <x:c r="A15" s="44" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -7778,10 +8020,10 @@
       </x:c>
       <x:c r="E15" s="50" t="n">
         <x:f>ROUND(X15*Y15,0)</x:f>
-        <x:v>293</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="F15" s="51" t="n">
-        <x:f>ROUND(($B$5+N15*$H$5+W15)/(1-(AH15/2+(AA15+AB15+AC15+AD15+AE15+AF15)/16+AG15/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N15*$H$5+W15)/(1-(AH15/2+(AA15+AB15+AC15+AD15+AE15+AF15)/16+MIN(AA15:AF15)/8)),0)</x:f>
         <x:v>4562</x:v>
       </x:c>
       <x:c r="G15" s="51" t="n">
@@ -7795,7 +8037,7 @@
         <x:v>+60 Endurance vor Levelskalierung.</x:v>
       </x:c>
       <x:c r="J15" s="44" t="str">
-        <x:v>Dragon Slaying und Swift laut Itemtext; gegen Drachen deutlich besser.</x:v>
+        <x:v>Dragon Slaying und Swift laut Itemtext (MM8-Engine/Itemtext, nicht in Lua); Swift vom MAW-Angriffstempo nicht berücksichtigt (zzMAW-Skills.lua:185 setzt t.Result neu, Swift nur über Enchant 41/59).</x:v>
       </x:c>
       <x:c r="K15" s="44" t="str">
         <x:v>1H/2H-fähig.</x:v>
@@ -7804,7 +8046,8 @@
         <x:v>Slayer und Swift nicht eingerechnet.</x:v>
       </x:c>
       <x:c r="M15" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMAW-Skills.lua</x:v>
       </x:c>
       <x:c r="N15" s="54" t="n">
         <x:v>75</x:v>
@@ -7837,7 +8080,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X15" s="44" t="n">
-        <x:v>293</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="Y15" s="44" t="n">
         <x:v>1</x:v>
@@ -7881,10 +8124,10 @@
         <x:v>Text + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ15" s="44" t="str">
-        <x:v>5d9+17</x:v>
+        <x:v>1d9+17</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="49" customHeight="1">
+    <x:row r="16" ht="50" customHeight="1">
       <x:c r="A16" s="44" t="n">
         <x:v>5</x:v>
       </x:c>
@@ -7899,10 +8142,10 @@
       </x:c>
       <x:c r="E16" s="50" t="n">
         <x:f>ROUND(X16*Y16,0)</x:f>
-        <x:v>416</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="F16" s="51" t="n">
-        <x:f>ROUND(($B$5+N16*$H$5+W16)/(1-(AH16/2+(AA16+AB16+AC16+AD16+AE16+AF16)/16+AG16/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N16*$H$5+W16)/(1-(AH16/2+(AA16+AB16+AC16+AD16+AE16+AF16)/16+MIN(AA16:AF16)/8)),0)</x:f>
         <x:v>4322</x:v>
       </x:c>
       <x:c r="G16" s="51" t="n">
@@ -7916,7 +8159,7 @@
         <x:v>+40 Endurance und +40 Luck vor Levelskalierung.</x:v>
       </x:c>
       <x:c r="J16" s="44" t="str">
-        <x:v>Ogre Slaying: situationsabhängiger Bonus gegen Oger.</x:v>
+        <x:v>Ogre Slaying laut Itemtext (MM8-Engine/Itemtext, nicht in Lua): situationsabhängiger Bonus gegen Oger.</x:v>
       </x:c>
       <x:c r="K16" s="44" t="str">
         <x:v>—</x:v>
@@ -7958,7 +8201,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X16" s="44" t="n">
-        <x:v>416</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="Y16" s="44" t="n">
         <x:v>1</x:v>
@@ -8002,10 +8245,10 @@
         <x:v>Text + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ16" s="44" t="str">
-        <x:v>6d5+16</x:v>
+        <x:v>2d4+16</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="49" customHeight="1">
+    <x:row r="17" ht="100" customHeight="1">
       <x:c r="A17" s="44" t="n">
         <x:v>6</x:v>
       </x:c>
@@ -8020,10 +8263,10 @@
       </x:c>
       <x:c r="E17" s="50" t="n">
         <x:f>ROUND(X17*Y17,0)</x:f>
-        <x:v>287</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="F17" s="51" t="n">
-        <x:f>ROUND(($B$5+N17*$H$5+W17)/(1-(AH17/2+(AA17+AB17+AC17+AD17+AE17+AF17)/16+AG17/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N17*$H$5+W17)/(1-(AH17/2+(AA17+AB17+AC17+AD17+AE17+AF17)/16+MIN(AA17:AF17)/8)),0)</x:f>
         <x:v>4202</x:v>
       </x:c>
       <x:c r="G17" s="51" t="n">
@@ -8037,7 +8280,7 @@
         <x:v>+30 Might, +30 Endurance vor Levelskalierung.</x:v>
       </x:c>
       <x:c r="J17" s="44" t="str">
-        <x:v>Körperschaden je Treffer und erhöhte Might.</x:v>
+        <x:v>Körperschaden 20–40 je Treffer laut Itemtext (MM8-Engine/Itemtext, nicht in Lua), vermutlich wirkungslos, da zzMaw_Legendaries.lua:19 ItemAdditionalDamage am Tag 4.5 auf 0 setzt; erhöhte Might.</x:v>
       </x:c>
       <x:c r="K17" s="44" t="str">
         <x:v>—</x:v>
@@ -8046,7 +8289,8 @@
         <x:v>Körperschaden nicht in DPS.</x:v>
       </x:c>
       <x:c r="M17" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N17" s="54" t="n">
         <x:v>37.5</x:v>
@@ -8079,7 +8323,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X17" s="44" t="n">
-        <x:v>287</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="Y17" s="44" t="n">
         <x:v>1</x:v>
@@ -8123,10 +8367,10 @@
         <x:v>Text + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ17" s="44" t="str">
-        <x:v>10d3+12</x:v>
+        <x:v>3d3+12</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="49" customHeight="1">
+    <x:row r="18" ht="149" customHeight="1">
       <x:c r="A18" s="44" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -8141,10 +8385,10 @@
       </x:c>
       <x:c r="E18" s="50" t="n">
         <x:f>ROUND(X18*Y18,0)</x:f>
-        <x:v>303</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="F18" s="51" t="n">
-        <x:f>ROUND(($B$5+N18*$H$5+W18)/(1-(AH18/2+(AA18+AB18+AC18+AD18+AE18+AF18)/16+AG18/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N18*$H$5+W18)/(1-(AH18/2+(AA18+AB18+AC18+AD18+AE18+AF18)/16+MIN(AA18:AF18)/8)),0)</x:f>
         <x:v>4187</x:v>
       </x:c>
       <x:c r="G18" s="51" t="n">
@@ -8158,7 +8402,7 @@
         <x:v>Extrem hohe Feuerresistenz (+65000), im MAW-Modell praktisch Feuerimmunität.</x:v>
       </x:c>
       <x:c r="J18" s="44" t="str">
-        <x:v>Explosive Feuerwirkung bei Treffern; zusätzlich Feuer-Zusatzschaden (10 Basis).</x:v>
+        <x:v>Bei Treffer Wing Buffet (Zauber 125) und Fireball (Zauber 6) am Ziel; zusätzlich geskripteter Feuerschaden 10 Basis (×2 bei Level 100), am Tag 4.5 von zzMaw_Legendaries.lua:19 (t.Result=0) wieder genullt.</x:v>
       </x:c>
       <x:c r="K18" s="44" t="str">
         <x:v>—</x:v>
@@ -8167,7 +8411,9 @@
         <x:v>Explosion/Fläche nicht in DPS.</x:v>
       </x:c>
       <x:c r="M18" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N18" s="54" t="n">
         <x:v>0</x:v>
@@ -8200,7 +8446,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X18" s="44" t="n">
-        <x:v>303</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="Y18" s="44" t="n">
         <x:v>1</x:v>
@@ -8247,7 +8493,7 @@
         <x:v>4d2+13</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="49" customHeight="1">
+    <x:row r="19" ht="50" customHeight="1">
       <x:c r="A19" s="44" t="n">
         <x:v>8</x:v>
       </x:c>
@@ -8262,10 +8508,10 @@
       </x:c>
       <x:c r="E19" s="50" t="n">
         <x:f>ROUND(X19*Y19,0)</x:f>
-        <x:v>413</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="F19" s="51" t="n">
-        <x:f>ROUND(($B$5+N19*$H$5+W19)/(1-(AH19/2+(AA19+AB19+AC19+AD19+AE19+AF19)/16+AG19/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N19*$H$5+W19)/(1-(AH19/2+(AA19+AB19+AC19+AD19+AE19+AF19)/16+MIN(AA19:AF19)/8)),0)</x:f>
         <x:v>4171</x:v>
       </x:c>
       <x:c r="G19" s="51" t="n">
@@ -8321,7 +8567,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X19" s="44" t="n">
-        <x:v>413</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="Y19" s="44" t="n">
         <x:v>1</x:v>
@@ -8365,10 +8611,10 @@
         <x:v>MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ19" s="44" t="str">
-        <x:v>9d9+19</x:v>
+        <x:v>2d6+19</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="49" customHeight="1">
+    <x:row r="20" ht="149" customHeight="1">
       <x:c r="A20" s="44" t="n">
         <x:v>9</x:v>
       </x:c>
@@ -8383,10 +8629,10 @@
       </x:c>
       <x:c r="E20" s="50" t="n">
         <x:f>ROUND(X20*Y20,0)</x:f>
-        <x:v>301</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="F20" s="51" t="n">
-        <x:f>ROUND(($B$5+N20*$H$5+W20)/(1-(AH20/2+(AA20+AB20+AC20+AD20+AE20+AF20)/16+AG20/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N20*$H$5+W20)/(1-(AH20/2+(AA20+AB20+AC20+AD20+AE20+AF20)/16+MIN(AA20:AF20)/8)),0)</x:f>
         <x:v>4082</x:v>
       </x:c>
       <x:c r="G20" s="51" t="n">
@@ -8400,16 +8646,18 @@
         <x:v>+20 auf alle Attribute vor Levelskalierung; Endurance/Speed enthalten.</x:v>
       </x:c>
       <x:c r="J20" s="44" t="str">
-        <x:v>Körperschaden pro Treffer; zusätzlich kleine Boni auf alle Hauptattribute.</x:v>
+        <x:v>Körperschaden 20–40 pro Treffer laut Itemtext (MM8-Engine/Itemtext, nicht in Lua), vermutlich wirkungslos, da zzMaw_Legendaries.lua:19 ItemAdditionalDamage am Tag 4.5 auf 0 setzt; +20 auf alle Hauptattribute; als 2H-Hellebarde Speer-GM-Debuff ×1,5.</x:v>
       </x:c>
       <x:c r="K20" s="44" t="str">
-        <x:v>1H/2H-fähig (Hellebarde).</x:v>
+        <x:v>Nur zweihändig (MAW stellt Hellebarden auf 2H um).</x:v>
       </x:c>
       <x:c r="L20" s="44" t="str">
-        <x:v>Körperschaden nicht in DPS.</x:v>
+        <x:v>Körperschaden und Speer-GM-Debuff nicht in DPS.</x:v>
       </x:c>
       <x:c r="M20" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Stats.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N20" s="54" t="n">
         <x:v>25</x:v>
@@ -8442,7 +8690,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X20" s="44" t="n">
-        <x:v>301</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="Y20" s="44" t="n">
         <x:v>1</x:v>
@@ -8486,10 +8734,10 @@
         <x:v>Text + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ20" s="44" t="str">
-        <x:v>6d6+18</x:v>
+        <x:v>3d6+18</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="49" customHeight="1">
+    <x:row r="21" ht="100" customHeight="1">
       <x:c r="A21" s="44" t="n">
         <x:v>10</x:v>
       </x:c>
@@ -8504,10 +8752,10 @@
       </x:c>
       <x:c r="E21" s="50" t="n">
         <x:f>ROUND(X21*Y21,0)</x:f>
-        <x:v>891</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="F21" s="51" t="n">
-        <x:f>ROUND(($B$5+N21*$H$5+W21)/(1-(AH21/2+(AA21+AB21+AC21+AD21+AE21+AF21)/16+AG21/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N21*$H$5+W21)/(1-(AH21/2+(AA21+AB21+AC21+AD21+AE21+AF21)/16+MIN(AA21:AF21)/8)),0)</x:f>
         <x:v>3986</x:v>
       </x:c>
       <x:c r="G21" s="51" t="n">
@@ -8521,7 +8769,7 @@
         <x:v>+100 Feuerresistenz vor Skalierung; bei Level 100 +125.</x:v>
       </x:c>
       <x:c r="J21" s="44" t="str">
-        <x:v>Feuer-Zusatzschaden pro Treffer; besser bei Gegnern mit niedriger Feuerresistenz.</x:v>
+        <x:v>Feuerschaden 20–40 pro Treffer laut Itemtext (MM8-Engine/Itemtext, nicht in Lua); vermutlich wirkungslos, da zzMaw_Legendaries.lua:19 ItemAdditionalDamage am Tag 4.5 auf 0 setzt.</x:v>
       </x:c>
       <x:c r="K21" s="44" t="str">
         <x:v>—</x:v>
@@ -8530,7 +8778,8 @@
         <x:v>Elementarschaden nicht eingerechnet.</x:v>
       </x:c>
       <x:c r="M21" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N21" s="54" t="n">
         <x:v>0</x:v>
@@ -8563,7 +8812,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X21" s="44" t="n">
-        <x:v>891</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="Y21" s="44" t="n">
         <x:v>1</x:v>
@@ -8607,10 +8856,10 @@
         <x:v>Text + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ21" s="44" t="str">
-        <x:v>10d8+25</x:v>
+        <x:v>3d7+19</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="49" customHeight="1">
+    <x:row r="22" ht="50" customHeight="1">
       <x:c r="A22" s="44" t="n">
         <x:v>11</x:v>
       </x:c>
@@ -8625,10 +8874,10 @@
       </x:c>
       <x:c r="E22" s="50" t="n">
         <x:f>ROUND(X22*Y22,0)</x:f>
-        <x:v>574</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="F22" s="51" t="n">
-        <x:f>ROUND(($B$5+N22*$H$5+W22)/(1-(AH22/2+(AA22+AB22+AC22+AD22+AE22+AF22)/16+AG22/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N22*$H$5+W22)/(1-(AH22/2+(AA22+AB22+AC22+AD22+AE22+AF22)/16+MIN(AA22:AF22)/8)),0)</x:f>
         <x:v>3986</x:v>
       </x:c>
       <x:c r="G22" s="51" t="n">
@@ -8684,7 +8933,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X22" s="44" t="n">
-        <x:v>574</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="Y22" s="44" t="n">
         <x:v>1</x:v>
@@ -8728,10 +8977,10 @@
         <x:v>MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ22" s="44" t="str">
-        <x:v>8d4+20</x:v>
+        <x:v>3d4+17</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="49" customHeight="1">
+    <x:row r="23" ht="149" customHeight="1">
       <x:c r="A23" s="44" t="n">
         <x:v>12</x:v>
       </x:c>
@@ -8746,10 +8995,10 @@
       </x:c>
       <x:c r="E23" s="50" t="n">
         <x:f>ROUND(X23*Y23,0)</x:f>
-        <x:v>303</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="F23" s="51" t="n">
-        <x:f>ROUND(($B$5+N23*$H$5+W23)/(1-(AH23/2+(AA23+AB23+AC23+AD23+AE23+AF23)/16+AG23/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N23*$H$5+W23)/(1-(AH23/2+(AA23+AB23+AC23+AD23+AE23+AF23)/16+MIN(AA23:AF23)/8)),0)</x:f>
         <x:v>3986</x:v>
       </x:c>
       <x:c r="G23" s="51" t="n">
@@ -8763,7 +9012,7 @@
         <x:v>+100 Feuerresistenz vor Skalierung.</x:v>
       </x:c>
       <x:c r="J23" s="44" t="str">
-        <x:v>Geskripteter Feuerschaden (+30 Basis je Treffer).</x:v>
+        <x:v>Geskripteter Feuerschaden 30 Basis je Treffer (×2 bei Level 100); am Tag 4.5 von zzMaw_Legendaries.lua:19 (t.Result=0) wieder genullt.</x:v>
       </x:c>
       <x:c r="K23" s="44" t="str">
         <x:v>—</x:v>
@@ -8772,7 +9021,9 @@
         <x:v>Feuerschaden nicht in phys. DPS.</x:v>
       </x:c>
       <x:c r="M23" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N23" s="54" t="n">
         <x:v>0</x:v>
@@ -8805,7 +9056,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X23" s="44" t="n">
-        <x:v>303</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="Y23" s="44" t="n">
         <x:v>1</x:v>
@@ -8849,51 +9100,52 @@
         <x:v>Skript + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ23" s="44" t="str">
-        <x:v>8d4+16</x:v>
+        <x:v>2d4+16</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="49" customHeight="1">
+    <x:row r="24" ht="100" customHeight="1">
       <x:c r="A24" s="44" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B24" s="44" t="str">
-        <x:v>Trident of Rulership</x:v>
+        <x:v>Scepter of Kings</x:v>
       </x:c>
       <x:c r="C24" s="44" t="str">
-        <x:v>Speer</x:v>
+        <x:v>Mace</x:v>
       </x:c>
       <x:c r="D24" s="44" t="str">
         <x:v>MM8</x:v>
       </x:c>
       <x:c r="E24" s="50" t="n">
         <x:f>ROUND(X24*Y24,0)</x:f>
-        <x:v>272</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="F24" s="51" t="n">
-        <x:f>ROUND(($B$5+N24*$H$5+W24)/(1-(AH24/2+(AA24+AB24+AC24+AD24+AE24+AF24)/16+AG24/8)),0)</x:f>
-        <x:v>3863</x:v>
+        <x:f>ROUND(($B$5+N24*$H$5+W24)/(1-(AH24/2+(AA24+AB24+AC24+AD24+AE24+AF24)/16+MIN(AA24:AF24)/8)),0)</x:f>
+        <x:v>3842</x:v>
       </x:c>
       <x:c r="G24" s="51" t="n">
         <x:f>F24-$B$8</x:f>
-        <x:v>21</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H24" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I24" s="44" t="str">
-        <x:v>+140 Wasserresistenz, −40 Feuerresistenz vor Skalierung.</x:v>
+        <x:v>+80 Personality vor Skalierung; HP-Regeneration ist nicht Teil des Vitality-Werts.</x:v>
       </x:c>
       <x:c r="J24" s="44" t="str">
-        <x:v>Water Breathing; offensiver Grundschaden ohne Zusatzproc.</x:v>
+        <x:v>Kein zusätzlicher Trefferproc; HP-Regeneration 0,2 % der max. HP pro Sekunde (artifactHpRegen; ×2 nach 20 s ohne Schaden, ×4 ohne Gegner in Sicht).</x:v>
       </x:c>
       <x:c r="K24" s="44" t="str">
-        <x:v>1H/2H-fähig.</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="L24" s="44" t="str">
-        <x:v>Kein zusätzlicher DPS-Proc.</x:v>
+        <x:v>Heilung/Regeneration nicht in DPS.</x:v>
       </x:c>
       <x:c r="M24" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMAW-Skills.lua</x:v>
       </x:c>
       <x:c r="N24" s="54" t="n">
         <x:v>0</x:v>
@@ -8902,13 +9154,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="P24" s="54" t="n">
-        <x:v>-50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Q24" s="54" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R24" s="54" t="n">
-        <x:v>175</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="S24" s="54" t="n">
         <x:v>0</x:v>
@@ -8926,17 +9178,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X24" s="44" t="n">
-        <x:v>272</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="Y24" s="44" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Z24" s="44" t="n">
-        <x:v>0</x:v>
+        <x:f>0.002*($B$5+N24*$H$5+W24)</x:f>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AA24" s="56" t="n">
         <x:f>IF($F$5+P24&gt;=65000,1,1-1/(1+($F$5+P24)/(60+$J$5*0.5)))</x:f>
-        <x:v>0</x:v>
+        <x:v>0.3125</x:v>
       </x:c>
       <x:c r="AB24" s="56" t="n">
         <x:f>IF($F$5+Q24&gt;=65000,1,1-1/(1+($F$5+Q24)/(60+$J$5*0.5)))</x:f>
@@ -8944,7 +9197,7 @@
       </x:c>
       <x:c r="AC24" s="56" t="n">
         <x:f>IF($F$5+R24&gt;=65000,1,1-1/(1+($F$5+R24)/(60+$J$5*0.5)))</x:f>
-        <x:v>0.6716417910447761</x:v>
+        <x:v>0.3125</x:v>
       </x:c>
       <x:c r="AD24" s="56" t="n">
         <x:f>IF($F$5+S24&gt;=65000,1,1-1/(1+($F$5+S24)/(60+$J$5*0.5)))</x:f>
@@ -8967,31 +9220,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI24" s="44" t="str">
-        <x:v>MAW-Stats</x:v>
+        <x:v>MAW-Stats + MAW-Regeneration; Z: 0,2 % der Modell-HP pro Sekunde (HP/s, zzMAW-Skills.lua:1180)</x:v>
       </x:c>
       <x:c r="AJ24" s="44" t="str">
-        <x:v>6d6+16</x:v>
+        <x:v>2d4+16</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="49" customHeight="1">
+    <x:row r="25" ht="50" customHeight="1">
       <x:c r="A25" s="44" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="B25" s="44" t="str">
-        <x:v>Scepter of Kings</x:v>
+        <x:v>Mordred</x:v>
       </x:c>
       <x:c r="C25" s="44" t="str">
-        <x:v>Mace</x:v>
+        <x:v>Dolch</x:v>
       </x:c>
       <x:c r="D25" s="44" t="str">
-        <x:v>MM8</x:v>
+        <x:v>MM6</x:v>
       </x:c>
       <x:c r="E25" s="50" t="n">
         <x:f>ROUND(X25*Y25,0)</x:f>
-        <x:v>303</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="F25" s="51" t="n">
-        <x:f>ROUND(($B$5+N25*$H$5+W25)/(1-(AH25/2+(AA25+AB25+AC25+AD25+AE25+AF25)/16+AG25/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N25*$H$5+W25)/(1-(AH25/2+(AA25+AB25+AC25+AD25+AE25+AF25)/16+MIN(AA25:AF25)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G25" s="51" t="n">
@@ -8999,22 +9252,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H25" s="44" t="str">
-        <x:v>Nein</x:v>
+        <x:v>Ja: geskriptet</x:v>
       </x:c>
       <x:c r="I25" s="44" t="str">
-        <x:v>+80 Personality vor Skalierung; HP-Regeneration ist nicht Teil des Vitality-Werts.</x:v>
+        <x:v>Potenzielle Selbstheilung; genaue Heilrate ohne konkreten Kampf nicht bestimmbar.</x:v>
       </x:c>
       <x:c r="J25" s="44" t="str">
-        <x:v>Kein zusätzlicher Trefferproc; HP-Regeneration während des Tragens.</x:v>
+        <x:v>Vampiric in ExtraArtifacts explizit als On-Hit-Effekt aktiviert.</x:v>
       </x:c>
       <x:c r="K25" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L25" s="44" t="str">
-        <x:v>Heilung/Regeneration nicht in DPS.</x:v>
+        <x:v>Lifeleech nicht in Vitality/DPS.</x:v>
       </x:c>
       <x:c r="M25" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
       </x:c>
       <x:c r="N25" s="54" t="n">
         <x:v>0</x:v>
@@ -9047,13 +9300,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X25" s="44" t="n">
-        <x:v>303</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="Y25" s="44" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Z25" s="44" t="n">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AA25" s="56" t="n">
         <x:f>IF($F$5+P25&gt;=65000,1,1-1/(1+($F$5+P25)/(60+$J$5*0.5)))</x:f>
@@ -9088,31 +9341,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI25" s="44" t="str">
-        <x:v>Skript + MAW-Stats</x:v>
+        <x:v>Skript</x:v>
       </x:c>
       <x:c r="AJ25" s="44" t="str">
-        <x:v>8d4+16</x:v>
+        <x:v>2d6+15</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="49" customHeight="1">
+    <x:row r="26" ht="100" customHeight="1">
       <x:c r="A26" s="44" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="B26" s="44" t="str">
-        <x:v>Mordred</x:v>
+        <x:v>Longseeker</x:v>
       </x:c>
       <x:c r="C26" s="44" t="str">
-        <x:v>Dolch</x:v>
+        <x:v>Bogen</x:v>
       </x:c>
       <x:c r="D26" s="44" t="str">
-        <x:v>MM6</x:v>
+        <x:v>MM8</x:v>
       </x:c>
       <x:c r="E26" s="50" t="n">
         <x:f>ROUND(X26*Y26,0)</x:f>
-        <x:v>490</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="F26" s="51" t="n">
-        <x:f>ROUND(($B$5+N26*$H$5+W26)/(1-(AH26/2+(AA26+AB26+AC26+AD26+AE26+AF26)/16+AG26/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N26*$H$5+W26)/(1-(AH26/2+(AA26+AB26+AC26+AD26+AE26+AF26)/16+MIN(AA26:AF26)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G26" s="51" t="n">
@@ -9120,22 +9373,23 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H26" s="44" t="str">
-        <x:v>Ja: geskriptet</x:v>
+        <x:v>Nein</x:v>
       </x:c>
       <x:c r="I26" s="44" t="str">
-        <x:v>Potenzielle Selbstheilung; genaue Heilrate ohne konkreten Kampf nicht bestimmbar.</x:v>
+        <x:v>+50 Accuracy vor Skalierung; kein defensiver Stat.</x:v>
       </x:c>
       <x:c r="J26" s="44" t="str">
-        <x:v>Vampiric in ExtraArtifacts explizit als On-Hit-Effekt aktiviert.</x:v>
+        <x:v>Swift laut Itemtext (MM8-Engine/Itemtext, nicht in Lua), vom MAW-Angriffstempo nicht berücksichtigt (zzMAW-Skills.lua:185 setzt t.Result neu, Swift nur über Enchant 41/59); Bow-Skill +4 vor Levelskalierung (Level 100: +5).</x:v>
       </x:c>
       <x:c r="K26" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L26" s="44" t="str">
-        <x:v>Lifeleech nicht in Vitality/DPS.</x:v>
+        <x:v>Swift nicht in DPS (wirkt am Tag 4.5 nicht).</x:v>
       </x:c>
       <x:c r="M26" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMAW-Skills.lua</x:v>
       </x:c>
       <x:c r="N26" s="54" t="n">
         <x:v>0</x:v>
@@ -9168,7 +9422,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X26" s="44" t="n">
-        <x:v>490</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="Y26" s="44" t="n">
         <x:v>1</x:v>
@@ -9209,31 +9463,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI26" s="44" t="str">
-        <x:v>Skript</x:v>
+        <x:v>Itemtext + MAW-Skills</x:v>
       </x:c>
       <x:c r="AJ26" s="44" t="str">
-        <x:v>8d5+20</x:v>
+        <x:v>6d2+14</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="49" customHeight="1">
+    <x:row r="27" ht="100" customHeight="1">
       <x:c r="A27" s="44" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B27" s="44" t="str">
-        <x:v>Foulfang</x:v>
+        <x:v>Ghoulsbane</x:v>
       </x:c>
       <x:c r="C27" s="44" t="str">
-        <x:v>Dolch</x:v>
+        <x:v>2H-Axt</x:v>
       </x:c>
       <x:c r="D27" s="44" t="str">
-        <x:v>MM8</x:v>
+        <x:v>MM7</x:v>
       </x:c>
       <x:c r="E27" s="50" t="n">
         <x:f>ROUND(X27*Y27,0)</x:f>
-        <x:v>429</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="F27" s="51" t="n">
-        <x:f>ROUND(($B$5+N27*$H$5+W27)/(1-(AH27/2+(AA27+AB27+AC27+AD27+AE27+AF27)/16+AG27/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N27*$H$5+W27)/(1-(AH27/2+(AA27+AB27+AC27+AD27+AE27+AF27)/16+MIN(AA27:AF27)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G27" s="51" t="n">
@@ -9241,22 +9495,23 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H27" s="44" t="str">
-        <x:v>Ja: Gegenstandstext</x:v>
+        <x:v>Nein</x:v>
       </x:c>
       <x:c r="I27" s="44" t="str">
-        <x:v>Potenzielle Selbstheilung, nicht in der Stats-Menü-Vitality.</x:v>
+        <x:v>Immunität gegen Paralyse laut ExtraArtifacts.</x:v>
       </x:c>
       <x:c r="J27" s="44" t="str">
-        <x:v>Vampiric und Giftschaden laut Itemtext.</x:v>
+        <x:v>Geskripteter Feuerschaden 15 Basis je Treffer (×2 bei Level 100), gegen Untote verdoppelt – nur der Zusatzschaden, nicht der Waffentreffer; am Tag 4.5 von zzMaw_Legendaries.lua:19 (t.Result=0) wieder genullt.</x:v>
       </x:c>
       <x:c r="K27" s="44" t="str">
-        <x:v>Nur Vampire (ExtraArtifacts).</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="L27" s="44" t="str">
-        <x:v>Gift und Lifesteal nicht in DPS.</x:v>
+        <x:v>Undead-Slaying und Feuerschaden nicht enthalten.</x:v>
       </x:c>
       <x:c r="M27" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N27" s="54" t="n">
         <x:v>0</x:v>
@@ -9289,7 +9544,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X27" s="44" t="n">
-        <x:v>429</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="Y27" s="44" t="n">
         <x:v>1</x:v>
@@ -9330,31 +9585,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI27" s="44" t="str">
-        <x:v>Itemtext; Script-Verbindung offen</x:v>
+        <x:v>Skript</x:v>
       </x:c>
       <x:c r="AJ27" s="44" t="str">
-        <x:v>12d3+12</x:v>
+        <x:v>1d18+30</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="49" customHeight="1">
+    <x:row r="28" ht="100" customHeight="1">
       <x:c r="A28" s="44" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="B28" s="44" t="str">
-        <x:v>Spiritslayer</x:v>
+        <x:v>Percival</x:v>
       </x:c>
       <x:c r="C28" s="44" t="str">
-        <x:v>Speer</x:v>
+        <x:v>Bogen</x:v>
       </x:c>
       <x:c r="D28" s="44" t="str">
-        <x:v>MM8</x:v>
+        <x:v>MM6</x:v>
       </x:c>
       <x:c r="E28" s="50" t="n">
         <x:f>ROUND(X28*Y28,0)</x:f>
-        <x:v>309</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="F28" s="51" t="n">
-        <x:f>ROUND(($B$5+N28*$H$5+W28)/(1-(AH28/2+(AA28+AB28+AC28+AD28+AE28+AF28)/16+AG28/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N28*$H$5+W28)/(1-(AH28/2+(AA28+AB28+AC28+AD28+AE28+AF28)/16+MIN(AA28:AF28)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G28" s="51" t="n">
@@ -9362,22 +9617,23 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H28" s="44" t="str">
-        <x:v>Ja: Gegenstandstext</x:v>
+        <x:v>Nein</x:v>
       </x:c>
       <x:c r="I28" s="44" t="str">
-        <x:v>+80 Might, −40 Luck vor Skalierung; Lebensraub separat.</x:v>
+        <x:v>+40 Speed vor Skalierung; Bonus-Erholung reduziert Schaden nicht direkt.</x:v>
       </x:c>
       <x:c r="J28" s="44" t="str">
-        <x:v>Vampiric laut Itemtext: heilt potenziell beim Treffer; Umsetzung im MAW-Leech-Code nicht vollständig nachgewiesen.</x:v>
+        <x:v>Fireball (Zauber 6) beim Pfeiltreffer (geskriptet), besonders gegen Gruppen; Angriffsverzögerung −20 (ExtraArtifacts), effektiv ca. −10 %.</x:v>
       </x:c>
       <x:c r="K28" s="44" t="str">
-        <x:v>1H/2H-fähig.</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="L28" s="44" t="str">
-        <x:v>Lifesteal nicht in Vitality oder DPS.</x:v>
+        <x:v>Angriffsverzögerung −20 (×0,9, ExtraArtifacts.lua:269) ist im Modell-DPS enthalten; Fireball-Explosion beim Pfeiltreffer nicht.</x:v>
       </x:c>
       <x:c r="M28" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
       </x:c>
       <x:c r="N28" s="54" t="n">
         <x:v>0</x:v>
@@ -9410,7 +9666,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X28" s="44" t="n">
-        <x:v>309</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="Y28" s="44" t="n">
         <x:v>1</x:v>
@@ -9451,31 +9707,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI28" s="44" t="str">
-        <x:v>Itemtext, Lifeleech ungeprüft</x:v>
+        <x:v>Skript + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ28" s="44" t="str">
-        <x:v>5d9+16</x:v>
+        <x:v>6d2+13</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="49" customHeight="1">
+    <x:row r="29" ht="100" customHeight="1">
       <x:c r="A29" s="44" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="B29" s="44" t="str">
-        <x:v>Conan</x:v>
+        <x:v>Finality</x:v>
       </x:c>
       <x:c r="C29" s="44" t="str">
-        <x:v>2H-Axt</x:v>
+        <x:v>2H-Schwert</x:v>
       </x:c>
       <x:c r="D29" s="44" t="str">
-        <x:v>MM6</x:v>
+        <x:v>MM8</x:v>
       </x:c>
       <x:c r="E29" s="50" t="n">
         <x:f>ROUND(X29*Y29,0)</x:f>
-        <x:v>1016</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="F29" s="51" t="n">
-        <x:f>ROUND(($B$5+N29*$H$5+W29)/(1-(AH29/2+(AA29+AB29+AC29+AD29+AE29+AF29)/16+AG29/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N29*$H$5+W29)/(1-(AH29/2+(AA29+AB29+AC29+AD29+AE29+AF29)/16+MIN(AA29:AF29)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G29" s="51" t="n">
@@ -9486,19 +9742,20 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I29" s="44" t="str">
-        <x:v>+150 Accuracy (MAW, auf Level 100: +187,5); verbessert Treffer und Kritschaden.</x:v>
+        <x:v>+120 Accuracy, −20 Speed vor Levelskalierung.</x:v>
       </x:c>
       <x:c r="J29" s="44" t="str">
-        <x:v>Verdoppelt Treffer gegen Drachen und Dämonen; geskripteter zusätzlicher Treffer-Schaden von 10, skaliert mit Level.</x:v>
+        <x:v>Feuerschaden 20–40 und Slow (verlangsamt das Ziel) laut Itemtext (MM8-Engine/Itemtext, nicht in Lua); Feuerschaden vermutlich wirkungslos, da zzMaw_Legendaries.lua:19 ItemAdditionalDamage am Tag 4.5 auf 0 setzt.</x:v>
       </x:c>
       <x:c r="K29" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L29" s="44" t="str">
-        <x:v>Slayer ×2 und geskripteter Zusatzschaden nicht im phys. DPS enthalten.</x:v>
+        <x:v>Feuer und Slow nicht in DPS.</x:v>
       </x:c>
       <x:c r="M29" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N29" s="54" t="n">
         <x:v>0</x:v>
@@ -9531,7 +9788,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X29" s="44" t="n">
-        <x:v>1016</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="Y29" s="44" t="n">
         <x:v>1</x:v>
@@ -9572,31 +9829,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI29" s="44" t="str">
-        <x:v>Skript + Text</x:v>
+        <x:v>Text + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ29" s="44" t="str">
-        <x:v>10d10+20</x:v>
+        <x:v>4d5+19</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="49" customHeight="1">
+    <x:row r="30" ht="149" customHeight="1">
       <x:c r="A30" s="44" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="B30" s="44" t="str">
-        <x:v>Finality</x:v>
+        <x:v>Ullyses</x:v>
       </x:c>
       <x:c r="C30" s="44" t="str">
-        <x:v>2H-Schwert</x:v>
+        <x:v>Bogen</x:v>
       </x:c>
       <x:c r="D30" s="44" t="str">
-        <x:v>MM8</x:v>
+        <x:v>MM7</x:v>
       </x:c>
       <x:c r="E30" s="50" t="n">
         <x:f>ROUND(X30*Y30,0)</x:f>
-        <x:v>851</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="F30" s="51" t="n">
-        <x:f>ROUND(($B$5+N30*$H$5+W30)/(1-(AH30/2+(AA30+AB30+AC30+AD30+AE30+AF30)/16+AG30/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N30*$H$5+W30)/(1-(AH30/2+(AA30+AB30+AC30+AD30+AE30+AF30)/16+MIN(AA30:AF30)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G30" s="51" t="n">
@@ -9607,19 +9864,21 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I30" s="44" t="str">
-        <x:v>+120 Accuracy, −20 Speed vor Levelskalierung.</x:v>
+        <x:v>+80 Accuracy vor Skalierung.</x:v>
       </x:c>
       <x:c r="J30" s="44" t="str">
-        <x:v>Feuerschaden pro Treffer und Slow (verlangsamt das Ziel).</x:v>
+        <x:v>Geskripteter Wasserschaden 15 Basis je Treffer (×2 bei Level 100), Eisgeschoss als Projektil; am Tag 4.5 von zzMaw_Legendaries.lua:19 (t.Result=0) wieder genullt.</x:v>
       </x:c>
       <x:c r="K30" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L30" s="44" t="str">
-        <x:v>Feuer und Slow nicht in DPS.</x:v>
+        <x:v>Wasserschaden nicht in DPS.</x:v>
       </x:c>
       <x:c r="M30" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N30" s="54" t="n">
         <x:v>0</x:v>
@@ -9652,7 +9911,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X30" s="44" t="n">
-        <x:v>851</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="Y30" s="44" t="n">
         <x:v>1</x:v>
@@ -9693,31 +9952,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI30" s="44" t="str">
-        <x:v>Text + MAW-Stats</x:v>
+        <x:v>Skript + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ30" s="44" t="str">
-        <x:v>8d8+25</x:v>
+        <x:v>6d2+14</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="49" customHeight="1">
+    <x:row r="31" ht="149" customHeight="1">
       <x:c r="A31" s="44" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="B31" s="44" t="str">
-        <x:v>Iron Feather</x:v>
+        <x:v>Conan</x:v>
       </x:c>
       <x:c r="C31" s="44" t="str">
-        <x:v>2H-Schwert</x:v>
+        <x:v>2H-Axt</x:v>
       </x:c>
       <x:c r="D31" s="44" t="str">
-        <x:v>MM7</x:v>
+        <x:v>MM6</x:v>
       </x:c>
       <x:c r="E31" s="50" t="n">
         <x:f>ROUND(X31*Y31,0)</x:f>
-        <x:v>766</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F31" s="51" t="n">
-        <x:f>ROUND(($B$5+N31*$H$5+W31)/(1-(AH31/2+(AA31+AB31+AC31+AD31+AE31+AF31)/16+AG31/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N31*$H$5+W31)/(1-(AH31/2+(AA31+AB31+AC31+AD31+AE31+AF31)/16+MIN(AA31:AF31)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G31" s="51" t="n">
@@ -9728,19 +9987,21 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I31" s="44" t="str">
-        <x:v>+80 Might vor Levelskalierung.</x:v>
+        <x:v>+150 Accuracy (MAW, auf Level 100: +187,5); verbessert Treffer und Kritschaden.</x:v>
       </x:c>
       <x:c r="J31" s="44" t="str">
-        <x:v>Geskripteter zusätzlicher Luft-/Elektrizitätsschaden von 15 Basis je Treffer.</x:v>
+        <x:v>Geskripteter Zusatzschaden 10 Basis je Treffer (×2 bei Level 100), gegen Drachen/Dämonen verdoppelt – nur der Zusatzschaden, nicht der Waffentreffer; am Tag 4.5 von zzMaw_Legendaries.lua:19 (t.Result=0) wieder genullt.</x:v>
       </x:c>
       <x:c r="K31" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L31" s="44" t="str">
-        <x:v>Luftschaden nicht in DPS.</x:v>
+        <x:v>Zusatzschaden inkl. Slayer-Verdopplung nicht im phys. DPS (am Tag 4.5 ohnehin genullt).</x:v>
       </x:c>
       <x:c r="M31" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N31" s="54" t="n">
         <x:v>0</x:v>
@@ -9773,7 +10034,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X31" s="44" t="n">
-        <x:v>766</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="Y31" s="44" t="n">
         <x:v>1</x:v>
@@ -9814,31 +10075,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI31" s="44" t="str">
-        <x:v>Skript</x:v>
+        <x:v>Skript + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ31" s="44" t="str">
-        <x:v>9d10+25</x:v>
+        <x:v>3d7+14</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="49" customHeight="1">
+    <x:row r="32" ht="50" customHeight="1">
       <x:c r="A32" s="44" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="B32" s="44" t="str">
-        <x:v>Longseeker</x:v>
+        <x:v>Wallace</x:v>
       </x:c>
       <x:c r="C32" s="44" t="str">
-        <x:v>Bogen</x:v>
+        <x:v>1H-Schwert</x:v>
       </x:c>
       <x:c r="D32" s="44" t="str">
-        <x:v>MM8</x:v>
+        <x:v>MM7</x:v>
       </x:c>
       <x:c r="E32" s="50" t="n">
         <x:f>ROUND(X32*Y32,0)</x:f>
-        <x:v>736</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="F32" s="51" t="n">
-        <x:f>ROUND(($B$5+N32*$H$5+W32)/(1-(AH32/2+(AA32+AB32+AC32+AD32+AE32+AF32)/16+AG32/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N32*$H$5+W32)/(1-(AH32/2+(AA32+AB32+AC32+AD32+AE32+AF32)/16+MIN(AA32:AF32)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G32" s="51" t="n">
@@ -9849,16 +10110,16 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I32" s="44" t="str">
-        <x:v>+50 Accuracy vor Skalierung; kein defensiver Stat.</x:v>
+        <x:v>+40 Personality vor Levelskalierung, kaum direkter Vitality-Effekt.</x:v>
       </x:c>
       <x:c r="J32" s="44" t="str">
-        <x:v>Schneller Bogen laut Itemtext, zusätzlich Bow-Skill +4 (MAW: +5 bei Level 100).</x:v>
+        <x:v>+10 Armsmaster (MAW bei Level 100 +13): steigert physischen Schaden und Tempo.</x:v>
       </x:c>
       <x:c r="K32" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L32" s="44" t="str">
-        <x:v>Swift-Auswirkung nicht in DPS.</x:v>
+        <x:v>Skillbonus ist im Modell-DPS berücksichtigt.</x:v>
       </x:c>
       <x:c r="M32" s="44" t="str">
         <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
@@ -9894,7 +10155,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X32" s="44" t="n">
-        <x:v>736</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="Y32" s="44" t="n">
         <x:v>1</x:v>
@@ -9935,31 +10196,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI32" s="44" t="str">
-        <x:v>Itemtext + MAW-Skills</x:v>
+        <x:v>MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ32" s="44" t="str">
-        <x:v>15d2+14</x:v>
+        <x:v>3d4+15</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="49" customHeight="1">
+    <x:row r="33" ht="149" customHeight="1">
       <x:c r="A33" s="44" t="n">
         <x:v>22</x:v>
       </x:c>
       <x:c r="B33" s="44" t="str">
-        <x:v>Elfbane</x:v>
+        <x:v>Blade of Mercy</x:v>
       </x:c>
       <x:c r="C33" s="44" t="str">
-        <x:v>2H-Schwert</x:v>
+        <x:v>Dolch</x:v>
       </x:c>
       <x:c r="D33" s="44" t="str">
-        <x:v>MM7</x:v>
+        <x:v>MM8</x:v>
       </x:c>
       <x:c r="E33" s="50" t="n">
         <x:f>ROUND(X33*Y33,0)</x:f>
-        <x:v>685</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="F33" s="51" t="n">
-        <x:f>ROUND(($B$5+N33*$H$5+W33)/(1-(AH33/2+(AA33+AB33+AC33+AD33+AE33+AF33)/16+AG33/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N33*$H$5+W33)/(1-(AH33/2+(AA33+AB33+AC33+AD33+AE33+AF33)/16+MIN(AA33:AF33)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G33" s="51" t="n">
@@ -9970,19 +10231,21 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I33" s="44" t="str">
-        <x:v>+100 Speed vor Levelskalierung; Schutz-/Schildbonus nicht in Vitality-Modell enthalten.</x:v>
+        <x:v>+100 Might, +100 Accuracy vor Levelskalierung (Code und Itemtext stimmen überein).</x:v>
       </x:c>
       <x:c r="J33" s="44" t="str">
-        <x:v>Doppelter Trefferschaden gegen Elfen; zusätzlich Schutzzauber laut Itemtext.</x:v>
+        <x:v>Elektrizitätsschaden 8–20 pro Treffer laut Itemtext (MM8-Engine/Itemtext, nicht in Lua), vermutlich wirkungslos, da zzMaw_Legendaries.lua:19 ItemAdditionalDamage am Tag 4.5 auf 0 setzt; hohe Might-/Accuracy-Boni im MAW-Code.</x:v>
       </x:c>
       <x:c r="K33" s="44" t="str">
-        <x:v>Nur Goblins (laut ExtraArtifacts).</x:v>
+        <x:v>Nur Necromancer-/Lich-Klassen (ExtraArtifacts).</x:v>
       </x:c>
       <x:c r="L33" s="44" t="str">
-        <x:v>Elf-Slaying und Shielding nicht in DPS.</x:v>
+        <x:v>Elektrizität nicht in DPS.</x:v>
       </x:c>
       <x:c r="M33" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N33" s="54" t="n">
         <x:v>0</x:v>
@@ -10015,7 +10278,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X33" s="44" t="n">
-        <x:v>685</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="Y33" s="44" t="n">
         <x:v>1</x:v>
@@ -10059,28 +10322,28 @@
         <x:v>Skript + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ33" s="44" t="str">
-        <x:v>8d8+32</x:v>
+        <x:v>2d2+15</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="49" customHeight="1">
+    <x:row r="34" ht="149" customHeight="1">
       <x:c r="A34" s="44" t="n">
         <x:v>23</x:v>
       </x:c>
       <x:c r="B34" s="44" t="str">
-        <x:v>Ghoulsbane</x:v>
+        <x:v>Iron Feather</x:v>
       </x:c>
       <x:c r="C34" s="44" t="str">
-        <x:v>2H-Axt</x:v>
+        <x:v>2H-Schwert</x:v>
       </x:c>
       <x:c r="D34" s="44" t="str">
         <x:v>MM7</x:v>
       </x:c>
       <x:c r="E34" s="50" t="n">
         <x:f>ROUND(X34*Y34,0)</x:f>
-        <x:v>683</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="F34" s="51" t="n">
-        <x:f>ROUND(($B$5+N34*$H$5+W34)/(1-(AH34/2+(AA34+AB34+AC34+AD34+AE34+AF34)/16+AG34/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N34*$H$5+W34)/(1-(AH34/2+(AA34+AB34+AC34+AD34+AE34+AF34)/16+MIN(AA34:AF34)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G34" s="51" t="n">
@@ -10091,19 +10354,21 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I34" s="44" t="str">
-        <x:v>Immunität gegen Paralyse laut ExtraArtifacts.</x:v>
+        <x:v>+80 Might vor Levelskalierung.</x:v>
       </x:c>
       <x:c r="J34" s="44" t="str">
-        <x:v>Untote erleiden doppelten Trefferschaden; zusätzlich geskripteter Feuerschaden (15 Basis je Treffer).</x:v>
+        <x:v>Geskripteter Luft-/Elektrizitätsschaden 15 Basis je Treffer (×2 bei Level 100); am Tag 4.5 von zzMaw_Legendaries.lua:19 (t.Result=0) wieder genullt.</x:v>
       </x:c>
       <x:c r="K34" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L34" s="44" t="str">
-        <x:v>Undead-Slaying und Feuerschaden nicht enthalten.</x:v>
+        <x:v>Luftschaden nicht in DPS.</x:v>
       </x:c>
       <x:c r="M34" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N34" s="54" t="n">
         <x:v>0</x:v>
@@ -10136,7 +10401,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X34" s="44" t="n">
-        <x:v>683</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="Y34" s="44" t="n">
         <x:v>1</x:v>
@@ -10177,31 +10442,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI34" s="44" t="str">
-        <x:v>Skript</x:v>
+        <x:v>Skript + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ34" s="44" t="str">
-        <x:v>6d9+19</x:v>
+        <x:v>4d5+14</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="49" customHeight="1">
+    <x:row r="35" ht="149" customHeight="1">
       <x:c r="A35" s="44" t="n">
         <x:v>24</x:v>
       </x:c>
       <x:c r="B35" s="44" t="str">
-        <x:v>Wallace</x:v>
+        <x:v>Excalibur</x:v>
       </x:c>
       <x:c r="C35" s="44" t="str">
         <x:v>1H-Schwert</x:v>
       </x:c>
       <x:c r="D35" s="44" t="str">
-        <x:v>MM7</x:v>
+        <x:v>MM6</x:v>
       </x:c>
       <x:c r="E35" s="50" t="n">
         <x:f>ROUND(X35*Y35,0)</x:f>
-        <x:v>649</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="F35" s="51" t="n">
-        <x:f>ROUND(($B$5+N35*$H$5+W35)/(1-(AH35/2+(AA35+AB35+AC35+AD35+AE35+AF35)/16+AG35/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N35*$H$5+W35)/(1-(AH35/2+(AA35+AB35+AC35+AD35+AE35+AF35)/16+MIN(AA35:AF35)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G35" s="51" t="n">
@@ -10212,19 +10477,21 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I35" s="44" t="str">
-        <x:v>+40 Personality vor Levelskalierung, kaum direkter Vitality-Effekt.</x:v>
+        <x:v>+100 Might vor Levelskalierung; Bless nicht in Vitality.</x:v>
       </x:c>
       <x:c r="J35" s="44" t="str">
-        <x:v>+10 Armsmaster (MAW bei Level 100 +13): steigert physischen Schaden und Tempo.</x:v>
+        <x:v>Bless-Buff dauerhaft (ExtraArtifacts); geskripteter Zusatzschaden 10 Basis je Treffer (×2 bei Level 100), gegen Drachen verdoppelt – nur der Zusatzschaden, nicht der Waffentreffer; am Tag 4.5 von zzMaw_Legendaries.lua:19 (t.Result=0) wieder genullt.</x:v>
       </x:c>
       <x:c r="K35" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L35" s="44" t="str">
-        <x:v>Skillbonus ist im Modell-DPS berücksichtigt.</x:v>
+        <x:v>Slayer-Verdopplung und Bless-Buff nicht im DPS.</x:v>
       </x:c>
       <x:c r="M35" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N35" s="54" t="n">
         <x:v>0</x:v>
@@ -10257,7 +10524,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X35" s="44" t="n">
-        <x:v>649</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="Y35" s="44" t="n">
         <x:v>1</x:v>
@@ -10298,31 +10565,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI35" s="44" t="str">
-        <x:v>MAW-Stats</x:v>
+        <x:v>Skript + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ35" s="44" t="str">
-        <x:v>5d4+30</x:v>
+        <x:v>3d4+15</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="49" customHeight="1">
+    <x:row r="36" ht="199" customHeight="1">
       <x:c r="A36" s="44" t="n">
         <x:v>25</x:v>
       </x:c>
       <x:c r="B36" s="44" t="str">
-        <x:v>Ullyses</x:v>
+        <x:v>Elderaxe</x:v>
       </x:c>
       <x:c r="C36" s="44" t="str">
-        <x:v>Bogen</x:v>
+        <x:v>1H-Axt</x:v>
       </x:c>
       <x:c r="D36" s="44" t="str">
-        <x:v>MM7</x:v>
+        <x:v>MM8</x:v>
       </x:c>
       <x:c r="E36" s="50" t="n">
         <x:f>ROUND(X36*Y36,0)</x:f>
-        <x:v>634</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="F36" s="51" t="n">
-        <x:f>ROUND(($B$5+N36*$H$5+W36)/(1-(AH36/2+(AA36+AB36+AC36+AD36+AE36+AF36)/16+AG36/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N36*$H$5+W36)/(1-(AH36/2+(AA36+AB36+AC36+AD36+AE36+AF36)/16+MIN(AA36:AF36)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G36" s="51" t="n">
@@ -10333,19 +10600,22 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I36" s="44" t="str">
-        <x:v>+80 Accuracy vor Skalierung.</x:v>
+        <x:v>+100 Might vor Levelskalierung.</x:v>
       </x:c>
       <x:c r="J36" s="44" t="str">
-        <x:v>Geskripteter Wasserschaden (+15 Basis) bei Treffer.</x:v>
+        <x:v>Kälteschaden 12–24 und Swift laut Itemtext (MM8-Engine/Itemtext, nicht in Lua); Kälteschaden vermutlich wirkungslos, da zzMaw_Legendaries.lua:19 ItemAdditionalDamage am Tag 4.5 auf 0 setzt; Swift vom MAW-Angriffstempo nicht berücksichtigt (zzMAW-Skills.lua:185 setzt t.Result neu, Swift nur über Enchant 41/59).</x:v>
       </x:c>
       <x:c r="K36" s="44" t="str">
-        <x:v>—</x:v>
+        <x:v>Nur Minotauren (ExtraArtifacts).</x:v>
       </x:c>
       <x:c r="L36" s="44" t="str">
-        <x:v>Wasserschaden nicht in DPS.</x:v>
+        <x:v>Kälte und Swift nicht in DPS.</x:v>
       </x:c>
       <x:c r="M36" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMAW-Skills.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N36" s="54" t="n">
         <x:v>0</x:v>
@@ -10378,7 +10648,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X36" s="44" t="n">
-        <x:v>634</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="Y36" s="44" t="n">
         <x:v>1</x:v>
@@ -10419,31 +10689,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI36" s="44" t="str">
-        <x:v>Skript</x:v>
+        <x:v>Text + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ36" s="44" t="str">
-        <x:v>10d4+14</x:v>
+        <x:v>4d2+16</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="49" customHeight="1">
+    <x:row r="37" ht="100" customHeight="1">
       <x:c r="A37" s="44" t="n">
         <x:v>26</x:v>
       </x:c>
       <x:c r="B37" s="44" t="str">
-        <x:v>Elderaxe</x:v>
+        <x:v>Puck</x:v>
       </x:c>
       <x:c r="C37" s="44" t="str">
-        <x:v>1H-Axt</x:v>
+        <x:v>1H-Schwert</x:v>
       </x:c>
       <x:c r="D37" s="44" t="str">
-        <x:v>MM8</x:v>
+        <x:v>MM7</x:v>
       </x:c>
       <x:c r="E37" s="50" t="n">
         <x:f>ROUND(X37*Y37,0)</x:f>
-        <x:v>542</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="F37" s="51" t="n">
-        <x:f>ROUND(($B$5+N37*$H$5+W37)/(1-(AH37/2+(AA37+AB37+AC37+AD37+AE37+AF37)/16+AG37/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N37*$H$5+W37)/(1-(AH37/2+(AA37+AB37+AC37+AD37+AE37+AF37)/16+MIN(AA37:AF37)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G37" s="51" t="n">
@@ -10454,19 +10724,20 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I37" s="44" t="str">
-        <x:v>+100 Might vor Levelskalierung.</x:v>
+        <x:v>+80 Speed vor Levelskalierung.</x:v>
       </x:c>
       <x:c r="J37" s="44" t="str">
-        <x:v>Kälteschaden pro Treffer, Swift laut Itemtext; Swift-Auswirkung auf Recovery nicht separat bestätigt.</x:v>
+        <x:v>Swift im Itemtext; geskriptete Erholungsmodifikation −20, in ExtraArtifacts effektiv ca. −10 %.</x:v>
       </x:c>
       <x:c r="K37" s="44" t="str">
-        <x:v>Nur Minotauren (ExtraArtifacts).</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="L37" s="44" t="str">
-        <x:v>Kälte und Swift nicht in DPS.</x:v>
+        <x:v>Angriffsverzögerung −20 (×0,9, ExtraArtifacts.lua:269) ist im Modell-DPS enthalten; Swift laut Itemtext nicht (wirkt am Tag 4.5 nicht).</x:v>
       </x:c>
       <x:c r="M37" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
       </x:c>
       <x:c r="N37" s="54" t="n">
         <x:v>0</x:v>
@@ -10499,7 +10770,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X37" s="44" t="n">
-        <x:v>542</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="Y37" s="44" t="n">
         <x:v>1</x:v>
@@ -10540,31 +10811,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI37" s="44" t="str">
-        <x:v>Text + MAW-Stats</x:v>
+        <x:v>Skript + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ37" s="44" t="str">
-        <x:v>8d6+16</x:v>
+        <x:v>3d3+17</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="49" customHeight="1">
+    <x:row r="38" ht="149" customHeight="1">
       <x:c r="A38" s="44" t="n">
         <x:v>27</x:v>
       </x:c>
       <x:c r="B38" s="44" t="str">
-        <x:v>Hell's Cleaver</x:v>
+        <x:v>Elfbane</x:v>
       </x:c>
       <x:c r="C38" s="44" t="str">
-        <x:v>1H-Axt</x:v>
+        <x:v>2H-Schwert</x:v>
       </x:c>
       <x:c r="D38" s="44" t="str">
-        <x:v>MM8</x:v>
+        <x:v>MM7</x:v>
       </x:c>
       <x:c r="E38" s="50" t="n">
         <x:f>ROUND(X38*Y38,0)</x:f>
-        <x:v>542</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="F38" s="51" t="n">
-        <x:f>ROUND(($B$5+N38*$H$5+W38)/(1-(AH38/2+(AA38+AB38+AC38+AD38+AE38+AF38)/16+AG38/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N38*$H$5+W38)/(1-(AH38/2+(AA38+AB38+AC38+AD38+AE38+AF38)/16+MIN(AA38:AF38)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G38" s="51" t="n">
@@ -10575,19 +10846,21 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I38" s="44" t="str">
-        <x:v>+70 Might, +70 Accuracy, +50 Intellect/Personality im MAW-Code (Itemtext weicht bei Vorzeichen ab).</x:v>
+        <x:v>+100 Speed vor Levelskalierung; Schutz-/Schildbonus nicht in Vitality-Modell enthalten.</x:v>
       </x:c>
       <x:c r="J38" s="44" t="str">
-        <x:v>Hohe Might-/Accuracy-Boni statt direktem Trefferproc.</x:v>
+        <x:v>Elf Slaying: ExtraArtifacts verdoppelt nur den ItemAdditionalDamage-Wert (bei Elfbane 0, zudem am Tag 4.5 von zzMaw_Legendaries.lua:19 (t.Result=0) wieder genullt) – praktisch wirkungslos; dauerhafter Shield-Buff (Stufe 3) per ExtraArtifacts.</x:v>
       </x:c>
       <x:c r="K38" s="44" t="str">
-        <x:v>—</x:v>
+        <x:v>Nur Goblins (laut ExtraArtifacts).</x:v>
       </x:c>
       <x:c r="L38" s="44" t="str">
-        <x:v>Keine externen Schadenseffekte enthalten.</x:v>
+        <x:v>Elf-Slaying und Shielding nicht in DPS.</x:v>
       </x:c>
       <x:c r="M38" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N38" s="54" t="n">
         <x:v>0</x:v>
@@ -10620,7 +10893,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X38" s="44" t="n">
-        <x:v>542</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="Y38" s="44" t="n">
         <x:v>1</x:v>
@@ -10661,31 +10934,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI38" s="44" t="str">
-        <x:v>MAW-Stats; Textkonflikt</x:v>
+        <x:v>Skript + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ38" s="44" t="str">
-        <x:v>8d4+24</x:v>
+        <x:v>4d6+14</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="49" customHeight="1">
+    <x:row r="39" ht="50" customHeight="1">
       <x:c r="A39" s="44" t="n">
         <x:v>28</x:v>
       </x:c>
       <x:c r="B39" s="44" t="str">
-        <x:v>Blade of Mercy</x:v>
+        <x:v>Charele</x:v>
       </x:c>
       <x:c r="C39" s="44" t="str">
-        <x:v>Dolch</x:v>
+        <x:v>Speer</x:v>
       </x:c>
       <x:c r="D39" s="44" t="str">
-        <x:v>MM8</x:v>
+        <x:v>MM7</x:v>
       </x:c>
       <x:c r="E39" s="50" t="n">
         <x:f>ROUND(X39*Y39,0)</x:f>
-        <x:v>511</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="F39" s="51" t="n">
-        <x:f>ROUND(($B$5+N39*$H$5+W39)/(1-(AH39/2+(AA39+AB39+AC39+AD39+AE39+AF39)/16+AG39/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N39*$H$5+W39)/(1-(AH39/2+(AA39+AB39+AC39+AD39+AE39+AF39)/16+MIN(AA39:AF39)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G39" s="51" t="n">
@@ -10696,19 +10969,19 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I39" s="44" t="str">
-        <x:v>+100 Might, +100 Accuracy vor Skalierung; Itemtext weicht teils ab.</x:v>
+        <x:v>Keine spezifischen Defensivboni dokumentiert.</x:v>
       </x:c>
       <x:c r="J39" s="44" t="str">
-        <x:v>Elektrizitätsschaden pro Treffer; besonders hohe Might-/Accuracy-Boni im MAW-Code.</x:v>
+        <x:v>Hoher physischer Grundschaden ohne klaren Trefferproc.</x:v>
       </x:c>
       <x:c r="K39" s="44" t="str">
-        <x:v>Nur Necromancer-/Lich-Klassen (ExtraArtifacts).</x:v>
+        <x:v>1H/2H-fähig.</x:v>
       </x:c>
       <x:c r="L39" s="44" t="str">
-        <x:v>Elektrizität nicht in DPS.</x:v>
+        <x:v>Keine besonderen Schadensprocs.</x:v>
       </x:c>
       <x:c r="M39" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
       </x:c>
       <x:c r="N39" s="54" t="n">
         <x:v>0</x:v>
@@ -10741,7 +11014,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X39" s="44" t="n">
-        <x:v>511</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="Y39" s="44" t="n">
         <x:v>1</x:v>
@@ -10782,31 +11055,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI39" s="44" t="str">
-        <x:v>Skript + MAW-Stats</x:v>
+        <x:v>Itemdaten; Lua nur Upscaler-Liste (zzMaw-Items.lua:2451)</x:v>
       </x:c>
       <x:c r="AJ39" s="44" t="str">
-        <x:v>8d3+15</x:v>
+        <x:v>3d15+30</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="49" customHeight="1">
+    <x:row r="40" ht="50" customHeight="1">
       <x:c r="A40" s="44" t="n">
         <x:v>29</x:v>
       </x:c>
       <x:c r="B40" s="44" t="str">
-        <x:v>Excalibur</x:v>
+        <x:v>Hell's Cleaver</x:v>
       </x:c>
       <x:c r="C40" s="44" t="str">
-        <x:v>1H-Schwert</x:v>
+        <x:v>1H-Axt</x:v>
       </x:c>
       <x:c r="D40" s="44" t="str">
-        <x:v>MM6</x:v>
+        <x:v>MM8</x:v>
       </x:c>
       <x:c r="E40" s="50" t="n">
         <x:f>ROUND(X40*Y40,0)</x:f>
-        <x:v>498</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="F40" s="51" t="n">
-        <x:f>ROUND(($B$5+N40*$H$5+W40)/(1-(AH40/2+(AA40+AB40+AC40+AD40+AE40+AF40)/16+AG40/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N40*$H$5+W40)/(1-(AH40/2+(AA40+AB40+AC40+AD40+AE40+AF40)/16+MIN(AA40:AF40)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G40" s="51" t="n">
@@ -10817,19 +11090,19 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I40" s="44" t="str">
-        <x:v>+100 Might vor Levelskalierung; Bless nicht in Vitality.</x:v>
+        <x:v>+70 Might, +70 Accuracy, +50 Intellect/Personality im MAW-Code (Itemtext weicht bei Vorzeichen ab).</x:v>
       </x:c>
       <x:c r="J40" s="44" t="str">
-        <x:v>Geskripteter zusätzlicher Trefferschaden (10 Basis); doppelter Schaden gegen Drachen; Bless-Buff.</x:v>
+        <x:v>Hohe Might-/Accuracy-Boni statt direktem Trefferproc.</x:v>
       </x:c>
       <x:c r="K40" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L40" s="44" t="str">
-        <x:v>Slayer, Trefferbonus und Bless nicht in DPS.</x:v>
+        <x:v>Keine externen Schadenseffekte enthalten.</x:v>
       </x:c>
       <x:c r="M40" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
       </x:c>
       <x:c r="N40" s="54" t="n">
         <x:v>0</x:v>
@@ -10862,7 +11135,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X40" s="44" t="n">
-        <x:v>498</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="Y40" s="44" t="n">
         <x:v>1</x:v>
@@ -10903,13 +11176,13 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI40" s="44" t="str">
-        <x:v>Skript</x:v>
+        <x:v>MAW-Stats; Textkonflikt</x:v>
       </x:c>
       <x:c r="AJ40" s="44" t="str">
-        <x:v>8d5+15</x:v>
+        <x:v>4d2+14</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="49" customHeight="1">
+    <x:row r="41" ht="100" customHeight="1">
       <x:c r="A41" s="44" t="n">
         <x:v>30</x:v>
       </x:c>
@@ -10924,10 +11197,10 @@
       </x:c>
       <x:c r="E41" s="50" t="n">
         <x:f>ROUND(X41*Y41,0)</x:f>
-        <x:v>489</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="F41" s="51" t="n">
-        <x:f>ROUND(($B$5+N41*$H$5+W41)/(1-(AH41/2+(AA41+AB41+AC41+AD41+AE41+AF41)/16+AG41/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N41*$H$5+W41)/(1-(AH41/2+(AA41+AB41+AC41+AD41+AE41+AF41)/16+MIN(AA41:AF41)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G41" s="51" t="n">
@@ -10941,7 +11214,7 @@
         <x:v>+60 Might vor Levelskalierung.</x:v>
       </x:c>
       <x:c r="J41" s="44" t="str">
-        <x:v>Dunkelschaden pro Treffer; effektiv gegen Gegner ohne Dunkelresistenz.</x:v>
+        <x:v>Dunkelschaden 20–40 pro Treffer laut Itemtext (MM8-Engine/Itemtext, nicht in Lua); vermutlich wirkungslos, da zzMaw_Legendaries.lua:19 ItemAdditionalDamage am Tag 4.5 auf 0 setzt.</x:v>
       </x:c>
       <x:c r="K41" s="44" t="str">
         <x:v>—</x:v>
@@ -10950,7 +11223,8 @@
         <x:v>Dunkelschaden nicht enthalten.</x:v>
       </x:c>
       <x:c r="M41" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N41" s="54" t="n">
         <x:v>0</x:v>
@@ -10983,7 +11257,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X41" s="44" t="n">
-        <x:v>489</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="Y41" s="44" t="n">
         <x:v>1</x:v>
@@ -11027,28 +11301,28 @@
         <x:v>Text + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ41" s="44" t="str">
-        <x:v>8d4+20</x:v>
+        <x:v>3d3+17</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" ht="49" customHeight="1">
+    <x:row r="42" ht="149" customHeight="1">
       <x:c r="A42" s="44" t="n">
         <x:v>31</x:v>
       </x:c>
       <x:c r="B42" s="44" t="str">
-        <x:v>Corsair</x:v>
+        <x:v>Lightning Crossbow</x:v>
       </x:c>
       <x:c r="C42" s="44" t="str">
-        <x:v>1H-Schwert</x:v>
+        <x:v>Armbrust</x:v>
       </x:c>
       <x:c r="D42" s="44" t="str">
-        <x:v>MM7</x:v>
+        <x:v>MM8</x:v>
       </x:c>
       <x:c r="E42" s="50" t="n">
         <x:f>ROUND(X42*Y42,0)</x:f>
-        <x:v>472</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="F42" s="51" t="n">
-        <x:f>ROUND(($B$5+N42*$H$5+W42)/(1-(AH42/2+(AA42+AB42+AC42+AD42+AE42+AF42)/16+AG42/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N42*$H$5+W42)/(1-(AH42/2+(AA42+AB42+AC42+AD42+AE42+AF42)/16+MIN(AA42:AF42)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G42" s="51" t="n">
@@ -11059,19 +11333,21 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I42" s="44" t="str">
-        <x:v>+80 Luck vor Levelskalierung; begünstigt Kritchance.</x:v>
+        <x:v>+60 Might und Speed vor Skalierung.</x:v>
       </x:c>
       <x:c r="J42" s="44" t="str">
-        <x:v>Stealing/Disarm-Boni statt unmittelbarer Schadensprocs.</x:v>
+        <x:v>Swift laut Itemtext (MM8-Engine/Itemtext, nicht in Lua), vom MAW-Angriffstempo nicht berücksichtigt (zzMAW-Skills.lua:185 setzt t.Result neu, Swift nur über Enchant 41/59); hohe Might-/Speed-Boni.</x:v>
       </x:c>
       <x:c r="K42" s="44" t="str">
-        <x:v>—</x:v>
+        <x:v>Nur Elfen/Dunkelelfen (ExtraArtifacts).</x:v>
       </x:c>
       <x:c r="L42" s="44" t="str">
-        <x:v>Luck-Krit im Modell eingerechnet.</x:v>
+        <x:v>Swift nicht in DPS (wirkt am Tag 4.5 nicht).</x:v>
       </x:c>
       <x:c r="M42" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMAW-Skills.lua</x:v>
       </x:c>
       <x:c r="N42" s="54" t="n">
         <x:v>0</x:v>
@@ -11104,7 +11380,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X42" s="44" t="n">
-        <x:v>472</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="Y42" s="44" t="n">
         <x:v>1</x:v>
@@ -11145,13 +11421,13 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI42" s="44" t="str">
-        <x:v>MAW-Stats</x:v>
+        <x:v>Itemtext + MAW-Stats + Skript (Tragbedingung)</x:v>
       </x:c>
       <x:c r="AJ42" s="44" t="str">
-        <x:v>8d5+16</x:v>
+        <x:v>5d2+15</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" ht="49" customHeight="1">
+    <x:row r="43" ht="100" customHeight="1">
       <x:c r="A43" s="44" t="n">
         <x:v>32</x:v>
       </x:c>
@@ -11166,10 +11442,10 @@
       </x:c>
       <x:c r="E43" s="50" t="n">
         <x:f>ROUND(X43*Y43,0)</x:f>
-        <x:v>469</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="F43" s="51" t="n">
-        <x:f>ROUND(($B$5+N43*$H$5+W43)/(1-(AH43/2+(AA43+AB43+AC43+AD43+AE43+AF43)/16+AG43/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N43*$H$5+W43)/(1-(AH43/2+(AA43+AB43+AC43+AD43+AE43+AF43)/16+MIN(AA43:AF43)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G43" s="51" t="n">
@@ -11183,7 +11459,7 @@
         <x:v>+60 Accuracy vor Levelskalierung.</x:v>
       </x:c>
       <x:c r="J43" s="44" t="str">
-        <x:v>Lichtschaden pro Treffer; gegen manche Gegner sehr wirksam.</x:v>
+        <x:v>Lichtschaden 20–40 pro Treffer laut Itemtext (MM8-Engine/Itemtext, nicht in Lua); vermutlich wirkungslos, da zzMaw_Legendaries.lua:19 ItemAdditionalDamage am Tag 4.5 auf 0 setzt.</x:v>
       </x:c>
       <x:c r="K43" s="44" t="str">
         <x:v>—</x:v>
@@ -11192,7 +11468,8 @@
         <x:v>Lichtschaden nicht enthalten.</x:v>
       </x:c>
       <x:c r="M43" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N43" s="54" t="n">
         <x:v>0</x:v>
@@ -11225,7 +11502,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X43" s="44" t="n">
-        <x:v>469</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="Y43" s="44" t="n">
         <x:v>1</x:v>
@@ -11269,28 +11546,28 @@
         <x:v>Text + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ43" s="44" t="str">
-        <x:v>8d4+20</x:v>
+        <x:v>3d3+17</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" ht="49" customHeight="1">
+    <x:row r="44" ht="100" customHeight="1">
       <x:c r="A44" s="44" t="n">
         <x:v>33</x:v>
       </x:c>
       <x:c r="B44" s="44" t="str">
-        <x:v>Puck</x:v>
+        <x:v>Gibbet</x:v>
       </x:c>
       <x:c r="C44" s="44" t="str">
-        <x:v>1H-Schwert</x:v>
+        <x:v>Speer</x:v>
       </x:c>
       <x:c r="D44" s="44" t="str">
         <x:v>MM7</x:v>
       </x:c>
       <x:c r="E44" s="50" t="n">
         <x:f>ROUND(X44*Y44,0)</x:f>
-        <x:v>460</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="F44" s="51" t="n">
-        <x:f>ROUND(($B$5+N44*$H$5+W44)/(1-(AH44/2+(AA44+AB44+AC44+AD44+AE44+AF44)/16+AG44/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N44*$H$5+W44)/(1-(AH44/2+(AA44+AB44+AC44+AD44+AE44+AF44)/16+MIN(AA44:AF44)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G44" s="51" t="n">
@@ -11301,19 +11578,20 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I44" s="44" t="str">
-        <x:v>+80 Speed vor Levelskalierung.</x:v>
+        <x:v>Keine direkten Attribute; hoher situativer Offensivnutzen.</x:v>
       </x:c>
       <x:c r="J44" s="44" t="str">
-        <x:v>Swift im Itemtext; geskriptete Erholungsmodifikation −20, in ExtraArtifacts effektiv ca. −10 %.</x:v>
+        <x:v>Geskripteter Feuerschaden 15 Basis je Treffer (×2 bei Level 100), gegen Drachen, Dämonen und Untote verdoppelt – nur der Zusatzschaden, nicht der Waffentreffer; am Tag 4.5 von zzMaw_Legendaries.lua:19 (t.Result=0) wieder genullt.</x:v>
       </x:c>
       <x:c r="K44" s="44" t="str">
-        <x:v>—</x:v>
+        <x:v>1H/2H-fähig.</x:v>
       </x:c>
       <x:c r="L44" s="44" t="str">
-        <x:v>Besondere Recovery nicht in Tabellen-DPS.</x:v>
+        <x:v>Slayer und Feuerschaden nicht enthalten.</x:v>
       </x:c>
       <x:c r="M44" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N44" s="54" t="n">
         <x:v>0</x:v>
@@ -11346,7 +11624,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X44" s="44" t="n">
-        <x:v>460</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="Y44" s="44" t="n">
         <x:v>1</x:v>
@@ -11387,31 +11665,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI44" s="44" t="str">
-        <x:v>Skript + MAW-Stats</x:v>
+        <x:v>Skript</x:v>
       </x:c>
       <x:c r="AJ44" s="44" t="str">
-        <x:v>6d6+17</x:v>
+        <x:v>3d9+30</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" ht="49" customHeight="1">
+    <x:row r="45" ht="50" customHeight="1">
       <x:c r="A45" s="44" t="n">
         <x:v>34</x:v>
       </x:c>
       <x:c r="B45" s="44" t="str">
-        <x:v>Lightning Crossbow</x:v>
+        <x:v>Corsair</x:v>
       </x:c>
       <x:c r="C45" s="44" t="str">
-        <x:v>Armbrust</x:v>
+        <x:v>1H-Schwert</x:v>
       </x:c>
       <x:c r="D45" s="44" t="str">
-        <x:v>MM8</x:v>
+        <x:v>MM7</x:v>
       </x:c>
       <x:c r="E45" s="50" t="n">
         <x:f>ROUND(X45*Y45,0)</x:f>
-        <x:v>460</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="F45" s="51" t="n">
-        <x:f>ROUND(($B$5+N45*$H$5+W45)/(1-(AH45/2+(AA45+AB45+AC45+AD45+AE45+AF45)/16+AG45/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N45*$H$5+W45)/(1-(AH45/2+(AA45+AB45+AC45+AD45+AE45+AF45)/16+MIN(AA45:AF45)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G45" s="51" t="n">
@@ -11422,16 +11700,16 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I45" s="44" t="str">
-        <x:v>+60 Might und Speed vor Skalierung.</x:v>
+        <x:v>+80 Luck vor Levelskalierung; begünstigt Kritchance.</x:v>
       </x:c>
       <x:c r="J45" s="44" t="str">
-        <x:v>Swift laut Itemtext; besonders für Bogen-/Armbrustnutzer.</x:v>
+        <x:v>Disarm Traps +10 vor Levelskalierung (Level 100: +13); Itemtext nennt Stealing +5/Disarm +5, Stealing ist in Lua nicht umgesetzt; keine Schadensprocs.</x:v>
       </x:c>
       <x:c r="K45" s="44" t="str">
-        <x:v>Nur Elfen/Dunkelelfen (ExtraArtifacts).</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="L45" s="44" t="str">
-        <x:v>Swift-Auswirkung nicht in DPS.</x:v>
+        <x:v>Luck-Krit im Modell eingerechnet.</x:v>
       </x:c>
       <x:c r="M45" s="44" t="str">
         <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
@@ -11467,7 +11745,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X45" s="44" t="n">
-        <x:v>460</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="Y45" s="44" t="n">
         <x:v>1</x:v>
@@ -11508,31 +11786,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI45" s="44" t="str">
-        <x:v>Itemtext + MAW-Stats</x:v>
+        <x:v>MAW-Stats + MAW-Skills</x:v>
       </x:c>
       <x:c r="AJ45" s="44" t="str">
-        <x:v>20d3+15</x:v>
+        <x:v>2d4+16</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="49" customHeight="1">
+    <x:row r="46" ht="50" customHeight="1">
       <x:c r="A46" s="44" t="n">
         <x:v>35</x:v>
       </x:c>
       <x:c r="B46" s="44" t="str">
-        <x:v>Old Nick</x:v>
+        <x:v>Justice</x:v>
       </x:c>
       <x:c r="C46" s="44" t="str">
-        <x:v>Dolch</x:v>
+        <x:v>Mace</x:v>
       </x:c>
       <x:c r="D46" s="44" t="str">
         <x:v>MM7</x:v>
       </x:c>
       <x:c r="E46" s="50" t="n">
         <x:f>ROUND(X46*Y46,0)</x:f>
-        <x:v>418</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="F46" s="51" t="n">
-        <x:f>ROUND(($B$5+N46*$H$5+W46)/(1-(AH46/2+(AA46+AB46+AC46+AD46+AE46+AF46)/16+AG46/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N46*$H$5+W46)/(1-(AH46/2+(AA46+AB46+AC46+AD46+AE46+AF46)/16+MIN(AA46:AF46)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G46" s="51" t="n">
@@ -11543,19 +11821,19 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I46" s="44" t="str">
-        <x:v>Disarm-Skillbonus; kein direkter Vitality-Effekt.</x:v>
+        <x:v>−40 Speed vor Skalierung.</x:v>
       </x:c>
       <x:c r="J46" s="44" t="str">
-        <x:v>Geskripteter zusätzlicher Wasserschaden (36 Basis); doppelter Trefferschaden gegen Elfen.</x:v>
+        <x:v>Undead Slaying nur laut Itemtext (nicht in Lua); Mind- und Body-Magie je +50 % des Basis-Skills (artifactSpellBonus).</x:v>
       </x:c>
       <x:c r="K46" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L46" s="44" t="str">
-        <x:v>Wasser und Elf-Slaying nicht in DPS.</x:v>
+        <x:v>Slayer/Zauber-Boni nicht in DPS.</x:v>
       </x:c>
       <x:c r="M46" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
       </x:c>
       <x:c r="N46" s="54" t="n">
         <x:v>0</x:v>
@@ -11588,7 +11866,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X46" s="44" t="n">
-        <x:v>418</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="Y46" s="44" t="n">
         <x:v>1</x:v>
@@ -11629,31 +11907,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI46" s="44" t="str">
-        <x:v>Skript</x:v>
+        <x:v>Text + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ46" s="44" t="str">
-        <x:v>8d5+10</x:v>
+        <x:v>2d8+24</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" ht="49" customHeight="1">
+    <x:row r="47" ht="149" customHeight="1">
       <x:c r="A47" s="44" t="n">
         <x:v>36</x:v>
       </x:c>
       <x:c r="B47" s="44" t="str">
-        <x:v>Charele</x:v>
+        <x:v>Foulfang</x:v>
       </x:c>
       <x:c r="C47" s="44" t="str">
-        <x:v>Speer</x:v>
+        <x:v>Dolch</x:v>
       </x:c>
       <x:c r="D47" s="44" t="str">
-        <x:v>MM7</x:v>
+        <x:v>MM8</x:v>
       </x:c>
       <x:c r="E47" s="50" t="n">
         <x:f>ROUND(X47*Y47,0)</x:f>
-        <x:v>383</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="F47" s="51" t="n">
-        <x:f>ROUND(($B$5+N47*$H$5+W47)/(1-(AH47/2+(AA47+AB47+AC47+AD47+AE47+AF47)/16+AG47/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N47*$H$5+W47)/(1-(AH47/2+(AA47+AB47+AC47+AD47+AE47+AF47)/16+MIN(AA47:AF47)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G47" s="51" t="n">
@@ -11661,22 +11939,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H47" s="44" t="str">
-        <x:v>Nein</x:v>
+        <x:v>Laut Itemtext (nicht in Lua)</x:v>
       </x:c>
       <x:c r="I47" s="44" t="str">
-        <x:v>Keine spezifischen Defensivboni dokumentiert.</x:v>
+        <x:v>Potenzielle Selbstheilung, nicht in der Stats-Menü-Vitality.</x:v>
       </x:c>
       <x:c r="J47" s="44" t="str">
-        <x:v>Hoher physischer Grundschaden ohne klaren Trefferproc.</x:v>
+        <x:v>Vampiric und 20 Giftschaden laut Itemtext (MM8-Engine/Itemtext, nicht in Lua); MAW-Leech (zzMaw-Items.lua:3722) erfasst nur Enchant 16/41; Giftschaden vermutlich wirkungslos, da zzMaw_Legendaries.lua:19 ItemAdditionalDamage am Tag 4.5 auf 0 setzt.</x:v>
       </x:c>
       <x:c r="K47" s="44" t="str">
-        <x:v>1H/2H-fähig.</x:v>
+        <x:v>Nur Vampire (ExtraArtifacts).</x:v>
       </x:c>
       <x:c r="L47" s="44" t="str">
-        <x:v>Keine besonderen Schadensprocs.</x:v>
+        <x:v>Gift und Lifesteal nicht in DPS.</x:v>
       </x:c>
       <x:c r="M47" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N47" s="54" t="n">
         <x:v>0</x:v>
@@ -11709,7 +11989,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X47" s="44" t="n">
-        <x:v>383</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="Y47" s="44" t="n">
         <x:v>1</x:v>
@@ -11750,13 +12030,13 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI47" s="44" t="str">
-        <x:v>Itemdaten</x:v>
+        <x:v>Itemtext; Lua nur Tragbedingung (Vampire), kein Leech-Eintrag</x:v>
       </x:c>
       <x:c r="AJ47" s="44" t="str">
-        <x:v>9d9+18</x:v>
+        <x:v>2d3+12</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" ht="49" customHeight="1">
+    <x:row r="48" ht="50" customHeight="1">
       <x:c r="A48" s="44" t="n">
         <x:v>37</x:v>
       </x:c>
@@ -11771,10 +12051,10 @@
       </x:c>
       <x:c r="E48" s="50" t="n">
         <x:f>ROUND(X48*Y48,0)</x:f>
-        <x:v>357</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="F48" s="51" t="n">
-        <x:f>ROUND(($B$5+N48*$H$5+W48)/(1-(AH48/2+(AA48+AB48+AC48+AD48+AE48+AF48)/16+AG48/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N48*$H$5+W48)/(1-(AH48/2+(AA48+AB48+AC48+AD48+AE48+AF48)/16+MIN(AA48:AF48)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G48" s="51" t="n">
@@ -11830,7 +12110,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X48" s="44" t="n">
-        <x:v>357</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="Y48" s="44" t="n">
         <x:v>1</x:v>
@@ -11874,28 +12154,28 @@
         <x:v>MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ48" s="44" t="str">
-        <x:v>6d6+15</x:v>
+        <x:v>1d3+15</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" ht="49" customHeight="1">
+    <x:row r="49" ht="149" customHeight="1">
       <x:c r="A49" s="44" t="n">
         <x:v>38</x:v>
       </x:c>
       <x:c r="B49" s="44" t="str">
-        <x:v>Percival</x:v>
+        <x:v>Thor</x:v>
       </x:c>
       <x:c r="C49" s="44" t="str">
-        <x:v>Bogen</x:v>
+        <x:v>Mace</x:v>
       </x:c>
       <x:c r="D49" s="44" t="str">
         <x:v>MM6</x:v>
       </x:c>
       <x:c r="E49" s="50" t="n">
         <x:f>ROUND(X49*Y49,0)</x:f>
-        <x:v>355</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="F49" s="51" t="n">
-        <x:f>ROUND(($B$5+N49*$H$5+W49)/(1-(AH49/2+(AA49+AB49+AC49+AD49+AE49+AF49)/16+AG49/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N49*$H$5+W49)/(1-(AH49/2+(AA49+AB49+AC49+AD49+AE49+AF49)/16+MIN(AA49:AF49)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G49" s="51" t="n">
@@ -11906,19 +12186,21 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I49" s="44" t="str">
-        <x:v>+40 Speed vor Skalierung; Bonus-Erholung reduziert Schaden nicht direkt.</x:v>
+        <x:v>+75 Might vor Levelskalierung.</x:v>
       </x:c>
       <x:c r="J49" s="44" t="str">
-        <x:v>Feuerexplosion beim Pfeileinschlag (geskriptet), besonders gegen Gruppen; geringere Erholungszeit.</x:v>
+        <x:v>Geskripteter Zusatzschaden 10 Basis je Treffer (×2 bei Level 100); bei Treffer Wing Buffet (Rückstoß, Zauber 125) und Lightning Bolt (Zauber 18), falls das Ziel überlebt; Zusatzschaden am Tag 4.5 von zzMaw_Legendaries.lua:19 (t.Result=0) wieder genullt.</x:v>
       </x:c>
       <x:c r="K49" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L49" s="44" t="str">
-        <x:v>Explosion und Recovery-Bonus nicht in Modell-DPS.</x:v>
+        <x:v>Zauber und Bonus-Hit nicht in DPS.</x:v>
       </x:c>
       <x:c r="M49" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N49" s="54" t="n">
         <x:v>0</x:v>
@@ -11951,7 +12233,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X49" s="44" t="n">
-        <x:v>355</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="Y49" s="44" t="n">
         <x:v>1</x:v>
@@ -11992,31 +12274,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI49" s="44" t="str">
-        <x:v>Skript</x:v>
+        <x:v>Skript + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ49" s="44" t="str">
-        <x:v>6d2+13</x:v>
+        <x:v>2d5+14</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" ht="49" customHeight="1">
+    <x:row r="50" ht="149" customHeight="1">
       <x:c r="A50" s="44" t="n">
         <x:v>39</x:v>
       </x:c>
       <x:c r="B50" s="44" t="str">
-        <x:v>Staff of the Swamp</x:v>
+        <x:v>Old Nick</x:v>
       </x:c>
       <x:c r="C50" s="44" t="str">
-        <x:v>Staff</x:v>
+        <x:v>Dolch</x:v>
       </x:c>
       <x:c r="D50" s="44" t="str">
-        <x:v>MM8</x:v>
+        <x:v>MM7</x:v>
       </x:c>
       <x:c r="E50" s="50" t="n">
         <x:f>ROUND(X50*Y50,0)</x:f>
-        <x:v>352</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="F50" s="51" t="n">
-        <x:f>ROUND(($B$5+N50*$H$5+W50)/(1-(AH50/2+(AA50+AB50+AC50+AD50+AE50+AF50)/16+AG50/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N50*$H$5+W50)/(1-(AH50/2+(AA50+AB50+AC50+AD50+AE50+AF50)/16+MIN(AA50:AF50)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G50" s="51" t="n">
@@ -12027,19 +12309,21 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I50" s="44" t="str">
-        <x:v>Immunität gegen Krankheit, Paralyse und Gift laut Itemdaten; Wert nicht in Vitality.</x:v>
+        <x:v>+5 Disarm Traps vor Levelskalierung (Level 100: +6); kein direkter Vitality-Effekt.</x:v>
       </x:c>
       <x:c r="J50" s="44" t="str">
-        <x:v>Schutzstab ohne direkten Schadensproc; Shielding laut Text.</x:v>
+        <x:v>Geskripteter Wasserschaden 36 Basis je Treffer (×2 bei Level 100; Itemtext: 54 Gift), gegen Elfen verdoppelt – nur der Zusatzschaden, nicht der Waffentreffer; am Tag 4.5 von zzMaw_Legendaries.lua:19 (t.Result=0) wieder genullt.</x:v>
       </x:c>
       <x:c r="K50" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L50" s="44" t="str">
-        <x:v>Immunitäten nicht als DPS.</x:v>
+        <x:v>Wasser und Elf-Slaying nicht in DPS.</x:v>
       </x:c>
       <x:c r="M50" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N50" s="54" t="n">
         <x:v>0</x:v>
@@ -12072,7 +12356,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X50" s="44" t="n">
-        <x:v>352</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="Y50" s="44" t="n">
         <x:v>1</x:v>
@@ -12113,31 +12397,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI50" s="44" t="str">
-        <x:v>Itemtext</x:v>
+        <x:v>Skript + MAW-Skills</x:v>
       </x:c>
       <x:c r="AJ50" s="44" t="str">
-        <x:v>8d4+11</x:v>
+        <x:v>2d2+10</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" ht="49" customHeight="1">
+    <x:row r="51" ht="50" customHeight="1">
       <x:c r="A51" s="44" t="n">
         <x:v>40</x:v>
       </x:c>
       <x:c r="B51" s="44" t="str">
-        <x:v>Merlin</x:v>
+        <x:v>Spiritslayer</x:v>
       </x:c>
       <x:c r="C51" s="44" t="str">
-        <x:v>Staff</x:v>
+        <x:v>Speer</x:v>
       </x:c>
       <x:c r="D51" s="44" t="str">
-        <x:v>MM6</x:v>
+        <x:v>MM8</x:v>
       </x:c>
       <x:c r="E51" s="50" t="n">
         <x:f>ROUND(X51*Y51,0)</x:f>
-        <x:v>350</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="F51" s="51" t="n">
-        <x:f>ROUND(($B$5+N51*$H$5+W51)/(1-(AH51/2+(AA51+AB51+AC51+AD51+AE51+AF51)/16+AG51/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N51*$H$5+W51)/(1-(AH51/2+(AA51+AB51+AC51+AD51+AE51+AF51)/16+MIN(AA51:AF51)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G51" s="51" t="n">
@@ -12145,22 +12429,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H51" s="44" t="str">
-        <x:v>Nein</x:v>
+        <x:v>Laut Itemtext (nicht in Lua)</x:v>
       </x:c>
       <x:c r="I51" s="44" t="str">
-        <x:v>+120 Intellect und Personality, +200 SP, SP-Regeneration; ohne Mana Shield kein Vitality-Bonus.</x:v>
+        <x:v>+80 Might, −40 Luck vor Skalierung; Lebensraub separat.</x:v>
       </x:c>
       <x:c r="J51" s="44" t="str">
-        <x:v>Angriffserholungsbonus −20 (effektiv ca. −10 %) im Skript; als Caster-Waffe interessant.</x:v>
+        <x:v>Vampiric laut Itemtext (MM8-Engine/Itemtext, nicht in Lua): heilt potenziell beim Treffer; MAW-Leech (zzMaw-Items.lua:3722) erfasst nur Enchant 16/41.</x:v>
       </x:c>
       <x:c r="K51" s="44" t="str">
-        <x:v>—</x:v>
+        <x:v>1H/2H-fähig.</x:v>
       </x:c>
       <x:c r="L51" s="44" t="str">
-        <x:v>Erholungseffekt nicht in Modell-DPS.</x:v>
+        <x:v>Lifesteal nicht in Vitality oder DPS.</x:v>
       </x:c>
       <x:c r="M51" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
       </x:c>
       <x:c r="N51" s="54" t="n">
         <x:v>0</x:v>
@@ -12193,7 +12477,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X51" s="44" t="n">
-        <x:v>350</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="Y51" s="44" t="n">
         <x:v>1</x:v>
@@ -12234,31 +12518,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI51" s="44" t="str">
-        <x:v>Skript</x:v>
+        <x:v>MAW-Stats + Itemtext; Vampiric nicht in Lua</x:v>
       </x:c>
       <x:c r="AJ51" s="44" t="str">
-        <x:v>6d6+10</x:v>
+        <x:v>1d9+16</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" ht="49" customHeight="1">
+    <x:row r="52" ht="50" customHeight="1">
       <x:c r="A52" s="44" t="n">
         <x:v>41</x:v>
       </x:c>
       <x:c r="B52" s="44" t="str">
-        <x:v>Thor</x:v>
+        <x:v>Staff of the Swamp</x:v>
       </x:c>
       <x:c r="C52" s="44" t="str">
-        <x:v>Mace</x:v>
+        <x:v>Staff</x:v>
       </x:c>
       <x:c r="D52" s="44" t="str">
-        <x:v>MM6</x:v>
+        <x:v>MM8</x:v>
       </x:c>
       <x:c r="E52" s="50" t="n">
         <x:f>ROUND(X52*Y52,0)</x:f>
-        <x:v>338</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="F52" s="51" t="n">
-        <x:f>ROUND(($B$5+N52*$H$5+W52)/(1-(AH52/2+(AA52+AB52+AC52+AD52+AE52+AF52)/16+AG52/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N52*$H$5+W52)/(1-(AH52/2+(AA52+AB52+AC52+AD52+AE52+AF52)/16+MIN(AA52:AF52)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G52" s="51" t="n">
@@ -12269,19 +12553,19 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I52" s="44" t="str">
-        <x:v>+75 Might vor Levelskalierung.</x:v>
+        <x:v>Immunität gegen Krankheit, Paralyse und Gift laut Itemtext (MM8-Engine/Itemtext, nicht in Lua); nicht in Vitality.</x:v>
       </x:c>
       <x:c r="J52" s="44" t="str">
-        <x:v>Geskripteter zusätzlicher Treffer-Schaden (10 Basis) und Spezialzauber beim Treffer.</x:v>
+        <x:v>Schutzstab ohne direkten Schadensproc; Shielding laut Itemtext (MM8-Engine/Itemtext, nicht in Lua).</x:v>
       </x:c>
       <x:c r="K52" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L52" s="44" t="str">
-        <x:v>Zauber und Bonus-Hit nicht in DPS.</x:v>
+        <x:v>Immunitäten nicht als DPS.</x:v>
       </x:c>
       <x:c r="M52" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
       </x:c>
       <x:c r="N52" s="54" t="n">
         <x:v>0</x:v>
@@ -12314,7 +12598,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X52" s="44" t="n">
-        <x:v>338</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="Y52" s="44" t="n">
         <x:v>1</x:v>
@@ -12355,31 +12639,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI52" s="44" t="str">
-        <x:v>Skript</x:v>
+        <x:v>Itemtext; Lua nur Upscaler-Liste (zzMaw-Items.lua:2452)</x:v>
       </x:c>
       <x:c r="AJ52" s="44" t="str">
-        <x:v>8d5+14</x:v>
+        <x:v>3d4+11</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" ht="49" customHeight="1">
+    <x:row r="53" ht="100" customHeight="1">
       <x:c r="A53" s="44" t="n">
         <x:v>42</x:v>
       </x:c>
       <x:c r="B53" s="44" t="str">
-        <x:v>Gibbet</x:v>
+        <x:v>Merlin</x:v>
       </x:c>
       <x:c r="C53" s="44" t="str">
-        <x:v>Speer</x:v>
+        <x:v>Staff</x:v>
       </x:c>
       <x:c r="D53" s="44" t="str">
-        <x:v>MM7</x:v>
+        <x:v>MM6</x:v>
       </x:c>
       <x:c r="E53" s="50" t="n">
         <x:f>ROUND(X53*Y53,0)</x:f>
-        <x:v>281</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="F53" s="51" t="n">
-        <x:f>ROUND(($B$5+N53*$H$5+W53)/(1-(AH53/2+(AA53+AB53+AC53+AD53+AE53+AF53)/16+AG53/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N53*$H$5+W53)/(1-(AH53/2+(AA53+AB53+AC53+AD53+AE53+AF53)/16+MIN(AA53:AF53)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G53" s="51" t="n">
@@ -12390,19 +12674,20 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I53" s="44" t="str">
-        <x:v>Keine direkten Attribute; hoher situativer Offensivnutzen.</x:v>
+        <x:v>+120 Intellect und Personality, +200 SP, SP-Regeneration; ohne Mana Shield kein Vitality-Bonus.</x:v>
       </x:c>
       <x:c r="J53" s="44" t="str">
-        <x:v>Geskripteter doppelter Trefferschaden gegen Drachen, Dämonen und Untote; zusätzlicher Feuerschaden (15 Basis).</x:v>
+        <x:v>Angriffserholungsbonus −20 (effektiv ca. −10 %) im Skript; als Caster-Waffe interessant.</x:v>
       </x:c>
       <x:c r="K53" s="44" t="str">
-        <x:v>1H/2H-fähig.</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="L53" s="44" t="str">
-        <x:v>Slayer und Feuerschaden nicht enthalten.</x:v>
+        <x:v>Angriffsverzögerung −20 (×0,9, ExtraArtifacts.lua:269) ist im Modell-DPS enthalten; Zauberboni (Intellect/Personality, SP, SP-Regeneration) nicht.</x:v>
       </x:c>
       <x:c r="M53" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
       </x:c>
       <x:c r="N53" s="54" t="n">
         <x:v>0</x:v>
@@ -12435,7 +12720,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X53" s="44" t="n">
-        <x:v>281</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="Y53" s="44" t="n">
         <x:v>1</x:v>
@@ -12476,31 +12761,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI53" s="44" t="str">
-        <x:v>Skript</x:v>
+        <x:v>Skript + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ53" s="44" t="str">
-        <x:v>6d6+18</x:v>
+        <x:v>2d4+10</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" ht="49" customHeight="1">
+    <x:row r="54" ht="149" customHeight="1">
       <x:c r="A54" s="44" t="n">
         <x:v>43</x:v>
       </x:c>
       <x:c r="B54" s="44" t="str">
-        <x:v>Justice</x:v>
+        <x:v>Hades</x:v>
       </x:c>
       <x:c r="C54" s="44" t="str">
-        <x:v>Mace</x:v>
+        <x:v>1H-Schwert</x:v>
       </x:c>
       <x:c r="D54" s="44" t="str">
-        <x:v>MM7</x:v>
+        <x:v>MM6</x:v>
       </x:c>
       <x:c r="E54" s="50" t="n">
         <x:f>ROUND(X54*Y54,0)</x:f>
-        <x:v>219</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="F54" s="51" t="n">
-        <x:f>ROUND(($B$5+N54*$H$5+W54)/(1-(AH54/2+(AA54+AB54+AC54+AD54+AE54+AF54)/16+AG54/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N54*$H$5+W54)/(1-(AH54/2+(AA54+AB54+AC54+AD54+AE54+AF54)/16+MIN(AA54:AF54)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G54" s="51" t="n">
@@ -12511,19 +12796,21 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I54" s="44" t="str">
-        <x:v>−40 Speed vor Skalierung.</x:v>
+        <x:v>+60 Luck; −3 HP-Regen (Schaden über Zeit für Träger).</x:v>
       </x:c>
       <x:c r="J54" s="44" t="str">
-        <x:v>Undead Slaying; Boni auf Mind-/Body-Magic.</x:v>
+        <x:v>Geskripteter Wasserschaden 20 Basis je Treffer (×2 bei Level 100; Itemtext: Gift) und Acid Burst (Zauber 29) bei Treffer; Disarm Traps +10 vor Levelskalierung (Level 100: +13); Wasserschaden am Tag 4.5 von zzMaw_Legendaries.lua:19 (t.Result=0) wieder genullt.</x:v>
       </x:c>
       <x:c r="K54" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L54" s="44" t="str">
-        <x:v>Slayer/Zauber-Boni nicht in DPS.</x:v>
+        <x:v>Zauber und zusätzlicher Wasserschaden nicht enthalten.</x:v>
       </x:c>
       <x:c r="M54" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N54" s="54" t="n">
         <x:v>0</x:v>
@@ -12556,13 +12843,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X54" s="44" t="n">
-        <x:v>219</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="Y54" s="44" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Z54" s="44" t="n">
-        <x:v>0</x:v>
+        <x:v>-3</x:v>
       </x:c>
       <x:c r="AA54" s="56" t="n">
         <x:f>IF($F$5+P54&gt;=65000,1,1-1/(1+($F$5+P54)/(60+$J$5*0.5)))</x:f>
@@ -12597,31 +12884,31 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI54" s="44" t="str">
-        <x:v>Text + MAW-Stats</x:v>
+        <x:v>Skript + MAW-Stats/Skills; Z: −3 HP je Regen-Tick (ExtraArtifacts.lua:194-199, 760)</x:v>
       </x:c>
       <x:c r="AJ54" s="44" t="str">
-        <x:v>2d4+16</x:v>
+        <x:v>3d3+18</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" ht="49" customHeight="1">
+    <x:row r="55" ht="100" customHeight="1">
       <x:c r="A55" s="44" t="n">
         <x:v>44</x:v>
       </x:c>
       <x:c r="B55" s="44" t="str">
-        <x:v>Hades</x:v>
+        <x:v>Ethric's Staff</x:v>
       </x:c>
       <x:c r="C55" s="44" t="str">
-        <x:v>1H-Schwert</x:v>
+        <x:v>Staff</x:v>
       </x:c>
       <x:c r="D55" s="44" t="str">
-        <x:v>MM6</x:v>
+        <x:v>MM7</x:v>
       </x:c>
       <x:c r="E55" s="50" t="n">
         <x:f>ROUND(X55*Y55,0)</x:f>
-        <x:v>467</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F55" s="51" t="n">
-        <x:f>ROUND(($B$5+N55*$H$5+W55)/(1-(AH55/2+(AA55+AB55+AC55+AD55+AE55+AF55)/16+AG55/8)),0)</x:f>
+        <x:f>ROUND(($B$5+N55*$H$5+W55)/(1-(AH55/2+(AA55+AB55+AC55+AD55+AE55+AF55)/16+MIN(AA55:AF55)/8)),0)</x:f>
         <x:v>3842</x:v>
       </x:c>
       <x:c r="G55" s="51" t="n">
@@ -12632,19 +12919,20 @@
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I55" s="44" t="str">
-        <x:v>+60 Luck; −3 HP-Regen (Schaden über Zeit für Träger).</x:v>
+        <x:v>Verliert als Nicht-Lich fortlaufend HP (Skript); negativer Defensiveffekt.</x:v>
       </x:c>
       <x:c r="J55" s="44" t="str">
-        <x:v>Geskripteter Wasserschaden (+20 Basis je Treffer) und zusätzlicher Zaubereffekt.</x:v>
+        <x:v>Dark-Magie +50 % des Basis-Skills (artifactSpellBonus) und Meditation +8 vor Levelskalierung (Level 100: +10) für Zauberwirker.</x:v>
       </x:c>
       <x:c r="K55" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L55" s="44" t="str">
-        <x:v>Zauber und zusätzlicher Wasserschaden nicht enthalten.</x:v>
+        <x:v>Magische Vorteile nicht als physische DPS gerechnet.</x:v>
       </x:c>
       <x:c r="M55" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
       </x:c>
       <x:c r="N55" s="54" t="n">
         <x:v>0</x:v>
@@ -12677,7 +12965,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X55" s="44" t="n">
-        <x:v>467</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="Y55" s="44" t="n">
         <x:v>1</x:v>
@@ -12718,51 +13006,51 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI55" s="44" t="str">
-        <x:v>Skript</x:v>
+        <x:v>Skript + MAW-Skills; Z: −3 HP je Regen-Tick (ExtraArtifacts.lua:194-199, 787)</x:v>
       </x:c>
       <x:c r="AJ55" s="44" t="str">
-        <x:v>6d6+18</x:v>
+        <x:v>2d4+11</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" ht="49" customHeight="1">
+    <x:row r="56" ht="50" customHeight="1">
       <x:c r="A56" s="44" t="n">
         <x:v>45</x:v>
       </x:c>
       <x:c r="B56" s="44" t="str">
-        <x:v>Ethric's Staff</x:v>
+        <x:v>Trident of Rulership</x:v>
       </x:c>
       <x:c r="C56" s="44" t="str">
-        <x:v>Staff</x:v>
+        <x:v>Speer</x:v>
       </x:c>
       <x:c r="D56" s="44" t="str">
-        <x:v>MM7</x:v>
+        <x:v>MM8</x:v>
       </x:c>
       <x:c r="E56" s="50" t="n">
         <x:f>ROUND(X56*Y56,0)</x:f>
-        <x:v>153</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="F56" s="51" t="n">
-        <x:f>ROUND(($B$5+N56*$H$5+W56)/(1-(AH56/2+(AA56+AB56+AC56+AD56+AE56+AF56)/16+AG56/8)),0)</x:f>
-        <x:v>3842</x:v>
+        <x:f>ROUND(($B$5+N56*$H$5+W56)/(1-(AH56/2+(AA56+AB56+AC56+AD56+AE56+AF56)/16+MIN(AA56:AF56)/8)),0)</x:f>
+        <x:v>3592</x:v>
       </x:c>
       <x:c r="G56" s="51" t="n">
         <x:f>F56-$B$8</x:f>
-        <x:v>0</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="H56" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I56" s="44" t="str">
-        <x:v>Verliert als Nicht-Lich fortlaufend HP (Skript); negativer Defensiveffekt.</x:v>
+        <x:v>+140 Wasserresistenz, −40 Feuerresistenz vor Skalierung.</x:v>
       </x:c>
       <x:c r="J56" s="44" t="str">
-        <x:v>Dark-Magic- und Meditation-Bonus für Zauberwirker.</x:v>
+        <x:v>Water Breathing laut Itemtext (MM8-Engine/Itemtext, nicht in Lua); offensiver Grundschaden ohne Zusatzproc.</x:v>
       </x:c>
       <x:c r="K56" s="44" t="str">
-        <x:v>—</x:v>
+        <x:v>1H/2H-fähig.</x:v>
       </x:c>
       <x:c r="L56" s="44" t="str">
-        <x:v>Magische Vorteile nicht als physische DPS gerechnet.</x:v>
+        <x:v>Kein zusätzlicher DPS-Proc.</x:v>
       </x:c>
       <x:c r="M56" s="44" t="str">
         <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
@@ -12774,13 +13062,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="P56" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>-50</x:v>
       </x:c>
       <x:c r="Q56" s="54" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R56" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="S56" s="54" t="n">
         <x:v>0</x:v>
@@ -12798,17 +13086,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X56" s="44" t="n">
-        <x:v>153</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="Y56" s="44" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Z56" s="44" t="n">
-        <x:v>-3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AA56" s="56" t="n">
         <x:f>IF($F$5+P56&gt;=65000,1,1-1/(1+($F$5+P56)/(60+$J$5*0.5)))</x:f>
-        <x:v>0.3125</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AB56" s="56" t="n">
         <x:f>IF($F$5+Q56&gt;=65000,1,1-1/(1+($F$5+Q56)/(60+$J$5*0.5)))</x:f>
@@ -12816,7 +13104,7 @@
       </x:c>
       <x:c r="AC56" s="56" t="n">
         <x:f>IF($F$5+R56&gt;=65000,1,1-1/(1+($F$5+R56)/(60+$J$5*0.5)))</x:f>
-        <x:v>0.3125</x:v>
+        <x:v>0.6716417910447761</x:v>
       </x:c>
       <x:c r="AD56" s="56" t="n">
         <x:f>IF($F$5+S56&gt;=65000,1,1-1/(1+($F$5+S56)/(60+$J$5*0.5)))</x:f>
@@ -12839,51 +13127,51 @@
         <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI56" s="44" t="str">
-        <x:v>Skript</x:v>
+        <x:v>MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ56" s="44" t="str">
-        <x:v>2d4+11</x:v>
+        <x:v>2d6+16</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" ht="49" customHeight="1">
+    <x:row r="57" ht="50" customHeight="1">
       <x:c r="A57" s="44" t="n">
         <x:v>46</x:v>
       </x:c>
       <x:c r="B57" s="44" t="str">
-        <x:v>Snake</x:v>
+        <x:v>Tournament Bow</x:v>
       </x:c>
       <x:c r="C57" s="44" t="str">
-        <x:v>1H-Schwert</x:v>
+        <x:v>Bogen</x:v>
       </x:c>
       <x:c r="D57" s="44" t="str">
         <x:v>MM8</x:v>
       </x:c>
       <x:c r="E57" s="50" t="n">
         <x:f>ROUND(X57*Y57,0)</x:f>
-        <x:v>442</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="F57" s="51" t="n">
-        <x:f>ROUND(($B$5+N57*$H$5+W57)/(1-(AH57/2+(AA57+AB57+AC57+AD57+AE57+AF57)/16+AG57/8)),0)</x:f>
-        <x:v>3649</x:v>
+        <x:f>ROUND(($B$5+N57*$H$5+W57)/(1-(AH57/2+(AA57+AB57+AC57+AD57+AE57+AF57)/16+MIN(AA57:AF57)/8)),0)</x:f>
+        <x:v>3562</x:v>
       </x:c>
       <x:c r="G57" s="51" t="n">
         <x:f>F57-$B$8</x:f>
-        <x:v>-193</x:v>
+        <x:v>-280</x:v>
       </x:c>
       <x:c r="H57" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I57" s="44" t="str">
-        <x:v>+100 Speed, −50 Wasserresistenz, −15 Personality vor Skalierung.</x:v>
+        <x:v>+100 Accuracy, −20 AC vor Levelskalierung (MAW-Code, wie Itemtext).</x:v>
       </x:c>
       <x:c r="J57" s="44" t="str">
-        <x:v>Verlangsamt das Ziel bei Treffer (Slow).</x:v>
+        <x:v>Bow-Skill +4 vor Levelskalierung (Level 100: +5; Itemtext nennt +5) und hohe Accuracy; kein zusätzlicher Trefferproc.</x:v>
       </x:c>
       <x:c r="K57" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L57" s="44" t="str">
-        <x:v>Verlangsamung nicht in DPS.</x:v>
+        <x:v>Skillbonus in Modell-DPS.</x:v>
       </x:c>
       <x:c r="M57" s="44" t="str">
         <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
@@ -12892,7 +13180,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O57" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>-25</x:v>
       </x:c>
       <x:c r="P57" s="54" t="n">
         <x:v>0</x:v>
@@ -12901,7 +13189,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="R57" s="54" t="n">
-        <x:v>-62.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="S57" s="54" t="n">
         <x:v>0</x:v>
@@ -12919,7 +13207,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X57" s="44" t="n">
-        <x:v>442</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="Y57" s="44" t="n">
         <x:v>1</x:v>
@@ -12937,7 +13225,7 @@
       </x:c>
       <x:c r="AC57" s="56" t="n">
         <x:f>IF($F$5+R57&gt;=65000,1,1-1/(1+($F$5+R57)/(60+$J$5*0.5)))</x:f>
-        <x:v>-0.1282051282051282</x:v>
+        <x:v>0.3125</x:v>
       </x:c>
       <x:c r="AD57" s="56" t="n">
         <x:f>IF($F$5+S57&gt;=65000,1,1-1/(1+($F$5+S57)/(60+$J$5*0.5)))</x:f>
@@ -12957,75 +13245,75 @@
       </x:c>
       <x:c r="AH57" s="56" t="n">
         <x:f>1-((5+$J$5*2)/(10+$J$5*2+MAX(0,$D$5+O57)))*(1/(1+MAX(0,$D$5+O57)/(90+$J$5*0.25)))</x:f>
-        <x:v>0.6462865716429107</x:v>
+        <x:v>0.5646352723915051</x:v>
       </x:c>
       <x:c r="AI57" s="44" t="str">
-        <x:v>Text + MAW-Stats</x:v>
+        <x:v>MAW-Stats + MAW-Skills</x:v>
       </x:c>
       <x:c r="AJ57" s="44" t="str">
-        <x:v>8d4+15</x:v>
+        <x:v>6d2+14</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" ht="49" customHeight="1">
+    <x:row r="58" ht="50" customHeight="1">
       <x:c r="A58" s="44" t="n">
         <x:v>47</x:v>
       </x:c>
       <x:c r="B58" s="44" t="str">
-        <x:v>Artemis</x:v>
+        <x:v>Havoc</x:v>
       </x:c>
       <x:c r="C58" s="44" t="str">
-        <x:v>Bogen</x:v>
+        <x:v>1H-Schwert</x:v>
       </x:c>
       <x:c r="D58" s="44" t="str">
-        <x:v>MM6</x:v>
+        <x:v>MM8</x:v>
       </x:c>
       <x:c r="E58" s="50" t="n">
         <x:f>ROUND(X58*Y58,0)</x:f>
-        <x:v>601</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="F58" s="51" t="n">
-        <x:f>ROUND(($B$5+N58*$H$5+W58)/(1-(AH58/2+(AA58+AB58+AC58+AD58+AE58+AF58)/16+AG58/8)),0)</x:f>
-        <x:v>3620</x:v>
+        <x:f>ROUND(($B$5+N58*$H$5+W58)/(1-(AH58/2+(AA58+AB58+AC58+AD58+AE58+AF58)/16+MIN(AA58:AF58)/8)),0)</x:f>
+        <x:v>3562</x:v>
       </x:c>
       <x:c r="G58" s="51" t="n">
         <x:f>F58-$B$8</x:f>
-        <x:v>-222</x:v>
+        <x:v>-280</x:v>
       </x:c>
       <x:c r="H58" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I58" s="44" t="str">
-        <x:v>−20 auf vier Elementarresistenzen vor Skalierung; schlechtere Abwehr.</x:v>
+        <x:v>+70 Speed, +70 Accuracy, −20 AC vor Levelskalierung.</x:v>
       </x:c>
       <x:c r="J58" s="44" t="str">
-        <x:v>Geskripteter Luft-/Elektrizitätsschaden (+20 Basis).</x:v>
+        <x:v>Sehr hohe Speed-/Accuracy-Werte; kein eigener Trefferproc.</x:v>
       </x:c>
       <x:c r="K58" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L58" s="44" t="str">
-        <x:v>Luftschaden nicht in DPS.</x:v>
+        <x:v>Kein Zusatzproc.</x:v>
       </x:c>
       <x:c r="M58" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
       </x:c>
       <x:c r="N58" s="54" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O58" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>-25</x:v>
       </x:c>
       <x:c r="P58" s="54" t="n">
-        <x:v>-25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Q58" s="54" t="n">
-        <x:v>-25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="R58" s="54" t="n">
-        <x:v>-25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="S58" s="54" t="n">
-        <x:v>-25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="T58" s="54" t="n">
         <x:v>0</x:v>
@@ -13040,7 +13328,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X58" s="44" t="n">
-        <x:v>601</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="Y58" s="44" t="n">
         <x:v>1</x:v>
@@ -13050,19 +13338,19 @@
       </x:c>
       <x:c r="AA58" s="56" t="n">
         <x:f>IF($F$5+P58&gt;=65000,1,1-1/(1+($F$5+P58)/(60+$J$5*0.5)))</x:f>
-        <x:v>0.18518518518518523</x:v>
+        <x:v>0.3125</x:v>
       </x:c>
       <x:c r="AB58" s="56" t="n">
         <x:f>IF($F$5+Q58&gt;=65000,1,1-1/(1+($F$5+Q58)/(60+$J$5*0.5)))</x:f>
-        <x:v>0.18518518518518523</x:v>
+        <x:v>0.3125</x:v>
       </x:c>
       <x:c r="AC58" s="56" t="n">
         <x:f>IF($F$5+R58&gt;=65000,1,1-1/(1+($F$5+R58)/(60+$J$5*0.5)))</x:f>
-        <x:v>0.18518518518518523</x:v>
+        <x:v>0.3125</x:v>
       </x:c>
       <x:c r="AD58" s="56" t="n">
         <x:f>IF($F$5+S58&gt;=65000,1,1-1/(1+($F$5+S58)/(60+$J$5*0.5)))</x:f>
-        <x:v>0.18518518518518523</x:v>
+        <x:v>0.3125</x:v>
       </x:c>
       <x:c r="AE58" s="56" t="n">
         <x:f>IF($F$5+T58&gt;=65000,1,1-1/(1+($F$5+T58)/(60+$J$5*0.5)))</x:f>
@@ -13078,75 +13366,77 @@
       </x:c>
       <x:c r="AH58" s="56" t="n">
         <x:f>1-((5+$J$5*2)/(10+$J$5*2+MAX(0,$D$5+O58)))*(1/(1+MAX(0,$D$5+O58)/(90+$J$5*0.25)))</x:f>
-        <x:v>0.6462865716429107</x:v>
+        <x:v>0.5646352723915051</x:v>
       </x:c>
       <x:c r="AI58" s="44" t="str">
-        <x:v>Skript + MAW-Stats</x:v>
+        <x:v>MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ58" s="44" t="str">
-        <x:v>12d3+15</x:v>
+        <x:v>3d3+18</x:v>
       </x:c>
     </x:row>
-    <x:row r="59" ht="49" customHeight="1">
+    <x:row r="59" ht="149" customHeight="1">
       <x:c r="A59" s="44" t="n">
         <x:v>48</x:v>
       </x:c>
       <x:c r="B59" s="44" t="str">
-        <x:v>Havoc</x:v>
+        <x:v>Artemis</x:v>
       </x:c>
       <x:c r="C59" s="44" t="str">
-        <x:v>1H-Schwert</x:v>
+        <x:v>Bogen</x:v>
       </x:c>
       <x:c r="D59" s="44" t="str">
-        <x:v>MM8</x:v>
+        <x:v>MM6</x:v>
       </x:c>
       <x:c r="E59" s="50" t="n">
         <x:f>ROUND(X59*Y59,0)</x:f>
-        <x:v>463</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="F59" s="51" t="n">
-        <x:f>ROUND(($B$5+N59*$H$5+W59)/(1-(AH59/2+(AA59+AB59+AC59+AD59+AE59+AF59)/16+AG59/8)),0)</x:f>
-        <x:v>3562</x:v>
+        <x:f>ROUND(($B$5+N59*$H$5+W59)/(1-(AH59/2+(AA59+AB59+AC59+AD59+AE59+AF59)/16+MIN(AA59:AF59)/8)),0)</x:f>
+        <x:v>3519</x:v>
       </x:c>
       <x:c r="G59" s="51" t="n">
         <x:f>F59-$B$8</x:f>
-        <x:v>-280</x:v>
+        <x:v>-323</x:v>
       </x:c>
       <x:c r="H59" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I59" s="44" t="str">
-        <x:v>+70 Speed, +70 Accuracy, −20 AC vor Levelskalierung.</x:v>
+        <x:v>−20 auf vier Elementarresistenzen vor Skalierung; schlechtere Abwehr.</x:v>
       </x:c>
       <x:c r="J59" s="44" t="str">
-        <x:v>Sehr hohe Speed-/Accuracy-Werte; kein eigener Trefferproc.</x:v>
+        <x:v>Geskripteter Luft-/Elektrizitätsschaden 20 Basis je Treffer (×2 bei Level 100); am Tag 4.5 von zzMaw_Legendaries.lua:19 (t.Result=0) wieder genullt.</x:v>
       </x:c>
       <x:c r="K59" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L59" s="44" t="str">
-        <x:v>Kein Zusatzproc.</x:v>
+        <x:v>Luftschaden nicht in DPS.</x:v>
       </x:c>
       <x:c r="M59" s="44" t="str">
-        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/ExtraArtifacts.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua
+https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/Global/zzMaw_Legendaries.lua</x:v>
       </x:c>
       <x:c r="N59" s="54" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O59" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P59" s="54" t="n">
         <x:v>-25</x:v>
       </x:c>
-      <x:c r="P59" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="Q59" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>-25</x:v>
       </x:c>
       <x:c r="R59" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>-25</x:v>
       </x:c>
       <x:c r="S59" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>-25</x:v>
       </x:c>
       <x:c r="T59" s="54" t="n">
         <x:v>0</x:v>
@@ -13161,7 +13451,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X59" s="44" t="n">
-        <x:v>463</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="Y59" s="44" t="n">
         <x:v>1</x:v>
@@ -13171,19 +13461,19 @@
       </x:c>
       <x:c r="AA59" s="56" t="n">
         <x:f>IF($F$5+P59&gt;=65000,1,1-1/(1+($F$5+P59)/(60+$J$5*0.5)))</x:f>
-        <x:v>0.3125</x:v>
+        <x:v>0.18518518518518523</x:v>
       </x:c>
       <x:c r="AB59" s="56" t="n">
         <x:f>IF($F$5+Q59&gt;=65000,1,1-1/(1+($F$5+Q59)/(60+$J$5*0.5)))</x:f>
-        <x:v>0.3125</x:v>
+        <x:v>0.18518518518518523</x:v>
       </x:c>
       <x:c r="AC59" s="56" t="n">
         <x:f>IF($F$5+R59&gt;=65000,1,1-1/(1+($F$5+R59)/(60+$J$5*0.5)))</x:f>
-        <x:v>0.3125</x:v>
+        <x:v>0.18518518518518523</x:v>
       </x:c>
       <x:c r="AD59" s="56" t="n">
         <x:f>IF($F$5+S59&gt;=65000,1,1-1/(1+($F$5+S59)/(60+$J$5*0.5)))</x:f>
-        <x:v>0.3125</x:v>
+        <x:v>0.18518518518518523</x:v>
       </x:c>
       <x:c r="AE59" s="56" t="n">
         <x:f>IF($F$5+T59&gt;=65000,1,1-1/(1+($F$5+T59)/(60+$J$5*0.5)))</x:f>
@@ -13199,48 +13489,48 @@
       </x:c>
       <x:c r="AH59" s="56" t="n">
         <x:f>1-((5+$J$5*2)/(10+$J$5*2+MAX(0,$D$5+O59)))*(1/(1+MAX(0,$D$5+O59)/(90+$J$5*0.25)))</x:f>
-        <x:v>0.5646352723915051</x:v>
+        <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI59" s="44" t="str">
-        <x:v>MAW-Stats</x:v>
+        <x:v>Skript + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ59" s="44" t="str">
-        <x:v>10d3+18</x:v>
+        <x:v>6d2+15</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" ht="49" customHeight="1">
+    <x:row r="60" ht="66" customHeight="1">
       <x:c r="A60" s="44" t="n">
         <x:v>49</x:v>
       </x:c>
       <x:c r="B60" s="44" t="str">
-        <x:v>Tournament Bow</x:v>
+        <x:v>Ania Selving</x:v>
       </x:c>
       <x:c r="C60" s="44" t="str">
-        <x:v>Bogen</x:v>
+        <x:v>Armbrust</x:v>
       </x:c>
       <x:c r="D60" s="44" t="str">
-        <x:v>MM8</x:v>
+        <x:v>MM7</x:v>
       </x:c>
       <x:c r="E60" s="50" t="n">
         <x:f>ROUND(X60*Y60,0)</x:f>
-        <x:v>382</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="F60" s="51" t="n">
-        <x:f>ROUND(($B$5+N60*$H$5+W60)/(1-(AH60/2+(AA60+AB60+AC60+AD60+AE60+AF60)/16+AG60/8)),0)</x:f>
-        <x:v>3562</x:v>
+        <x:f>ROUND(($B$5+N60*$H$5+W60)/(1-(AH60/2+(AA60+AB60+AC60+AD60+AE60+AF60)/16+MIN(AA60:AF60)/8)),0)</x:f>
+        <x:v>3485</x:v>
       </x:c>
       <x:c r="G60" s="51" t="n">
         <x:f>F60-$B$8</x:f>
-        <x:v>-280</x:v>
+        <x:v>-357</x:v>
       </x:c>
       <x:c r="H60" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I60" s="44" t="str">
-        <x:v>+100 Accuracy, −20 AC laut Itemtext; AC-Code nicht separat eingetragen.</x:v>
+        <x:v>+150 Accuracy, −25 AC vor Levelskalierung.</x:v>
       </x:c>
       <x:c r="J60" s="44" t="str">
-        <x:v>Bow-Skillbonus (+4 MAW-Code) und hohe Accuracy; kein zusätzlicher Trefferproc.</x:v>
+        <x:v>Bow-Skill +5 vor Levelskalierung (Level 100: +6) und sehr hohe Accuracy; kein zusätzlicher Trefferproc.</x:v>
       </x:c>
       <x:c r="K60" s="44" t="str">
         <x:v>—</x:v>
@@ -13255,7 +13545,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O60" s="54" t="n">
-        <x:v>-25</x:v>
+        <x:v>-31.25</x:v>
       </x:c>
       <x:c r="P60" s="54" t="n">
         <x:v>0</x:v>
@@ -13282,7 +13572,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X60" s="44" t="n">
-        <x:v>382</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="Y60" s="44" t="n">
         <x:v>1</x:v>
@@ -13320,54 +13610,54 @@
       </x:c>
       <x:c r="AH60" s="56" t="n">
         <x:f>1-((5+$J$5*2)/(10+$J$5*2+MAX(0,$D$5+O60)))*(1/(1+MAX(0,$D$5+O60)/(90+$J$5*0.25)))</x:f>
-        <x:v>0.5646352723915051</x:v>
+        <x:v>0.5397333821420944</x:v>
       </x:c>
       <x:c r="AI60" s="44" t="str">
-        <x:v>Skript + Text</x:v>
+        <x:v>MAW-Stats + MAW-Skills; ITEMS.txt-Equip-Stat lautet "Bow" statt "Missile" (Datenauffälligkeit)</x:v>
       </x:c>
       <x:c r="AJ60" s="44" t="str">
-        <x:v>12d3+14</x:v>
+        <x:v>5d2+12</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" ht="49" customHeight="1">
+    <x:row r="61" ht="50" customHeight="1">
       <x:c r="A61" s="44" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="B61" s="44" t="str">
-        <x:v>Staff of Elements</x:v>
+        <x:v>Snake</x:v>
       </x:c>
       <x:c r="C61" s="44" t="str">
-        <x:v>Staff</x:v>
+        <x:v>1H-Schwert</x:v>
       </x:c>
       <x:c r="D61" s="44" t="str">
         <x:v>MM8</x:v>
       </x:c>
       <x:c r="E61" s="50" t="n">
         <x:f>ROUND(X61*Y61,0)</x:f>
-        <x:v>188</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="F61" s="51" t="n">
-        <x:f>ROUND(($B$5+N61*$H$5+W61)/(1-(AH61/2+(AA61+AB61+AC61+AD61+AE61+AF61)/16+AG61/8)),0)</x:f>
-        <x:v>3234</x:v>
+        <x:f>ROUND(($B$5+N61*$H$5+W61)/(1-(AH61/2+(AA61+AB61+AC61+AD61+AE61+AF61)/16+MIN(AA61:AF61)/8)),0)</x:f>
+        <x:v>3315</x:v>
       </x:c>
       <x:c r="G61" s="51" t="n">
         <x:f>F61-$B$8</x:f>
-        <x:v>-608</x:v>
+        <x:v>-527</x:v>
       </x:c>
       <x:c r="H61" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I61" s="44" t="str">
-        <x:v>−40 AC vor Levelskalierung, macht anfälliger.</x:v>
+        <x:v>+100 Speed, −50 Wasserresistenz, −15 Personality vor Skalierung.</x:v>
       </x:c>
       <x:c r="J61" s="44" t="str">
-        <x:v>Verstärkt vier Elementarmagieschulen; für Zauberschaden wertvoll, nicht für Stab-DPS.</x:v>
+        <x:v>Verlangsamt das Ziel bei Treffer (Slow) laut Itemtext (MM8-Engine/Itemtext, nicht in Lua).</x:v>
       </x:c>
       <x:c r="K61" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L61" s="44" t="str">
-        <x:v>Zauberboni nicht in physischen DPS.</x:v>
+        <x:v>Verlangsamung nicht in DPS.</x:v>
       </x:c>
       <x:c r="M61" s="44" t="str">
         <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
@@ -13376,7 +13666,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O61" s="54" t="n">
-        <x:v>-50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="P61" s="54" t="n">
         <x:v>0</x:v>
@@ -13385,7 +13675,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="R61" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>-62.5</x:v>
       </x:c>
       <x:c r="S61" s="54" t="n">
         <x:v>0</x:v>
@@ -13403,7 +13693,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X61" s="44" t="n">
-        <x:v>188</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="Y61" s="44" t="n">
         <x:v>1</x:v>
@@ -13421,7 +13711,7 @@
       </x:c>
       <x:c r="AC61" s="56" t="n">
         <x:f>IF($F$5+R61&gt;=65000,1,1-1/(1+($F$5+R61)/(60+$J$5*0.5)))</x:f>
-        <x:v>0.3125</x:v>
+        <x:v>-0.1282051282051282</x:v>
       </x:c>
       <x:c r="AD61" s="56" t="n">
         <x:f>IF($F$5+S61&gt;=65000,1,1-1/(1+($F$5+S61)/(60+$J$5*0.5)))</x:f>
@@ -13441,54 +13731,54 @@
       </x:c>
       <x:c r="AH61" s="56" t="n">
         <x:f>1-((5+$J$5*2)/(10+$J$5*2+MAX(0,$D$5+O61)))*(1/(1+MAX(0,$D$5+O61)/(90+$J$5*0.25)))</x:f>
-        <x:v>0.45046620046620045</x:v>
+        <x:v>0.6462865716429107</x:v>
       </x:c>
       <x:c r="AI61" s="44" t="str">
-        <x:v>MAW-Stats</x:v>
+        <x:v>Text + MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ61" s="44" t="str">
-        <x:v>2d4+4</x:v>
+        <x:v>3d4+15</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" ht="49" customHeight="1">
+    <x:row r="62" ht="50" customHeight="1">
       <x:c r="A62" s="44" t="n">
         <x:v>51</x:v>
       </x:c>
       <x:c r="B62" s="44" t="str">
-        <x:v>Mekorig's Hammer</x:v>
+        <x:v>Staff of Elements</x:v>
       </x:c>
       <x:c r="C62" s="44" t="str">
-        <x:v>Mace</x:v>
+        <x:v>Staff</x:v>
       </x:c>
       <x:c r="D62" s="44" t="str">
-        <x:v>MM7</x:v>
+        <x:v>MM8</x:v>
       </x:c>
       <x:c r="E62" s="50" t="n">
         <x:f>ROUND(X62*Y62,0)</x:f>
-        <x:v>250</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F62" s="51" t="n">
-        <x:f>ROUND(($B$5+N62*$H$5+W62)/(1-(AH62/2+(AA62+AB62+AC62+AD62+AE62+AF62)/16+AG62/8)),0)</x:f>
-        <x:v>2967</x:v>
+        <x:f>ROUND(($B$5+N62*$H$5+W62)/(1-(AH62/2+(AA62+AB62+AC62+AD62+AE62+AF62)/16+MIN(AA62:AF62)/8)),0)</x:f>
+        <x:v>3234</x:v>
       </x:c>
       <x:c r="G62" s="51" t="n">
         <x:f>F62-$B$8</x:f>
-        <x:v>-875</x:v>
+        <x:v>-608</x:v>
       </x:c>
       <x:c r="H62" s="44" t="str">
         <x:v>Nein</x:v>
       </x:c>
       <x:c r="I62" s="44" t="str">
-        <x:v>+75 Might, −100 Luftresistenz vor Levelskalierung.</x:v>
+        <x:v>−40 AC vor Levelskalierung, macht anfälliger.</x:v>
       </x:c>
       <x:c r="J62" s="44" t="str">
-        <x:v>Spirit-Magic-Bonus; primär Hybrid-Zauberwaffe.</x:v>
+        <x:v>Feuer-, Luft-, Wasser- und Erdmagie je +50 % des Basis-Skills (artifactSpellBonus); für Zauberschaden wertvoll, nicht für Stab-DPS.</x:v>
       </x:c>
       <x:c r="K62" s="44" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="L62" s="44" t="str">
-        <x:v>Magiebonus nicht als Angriffsschaden eingerechnet.</x:v>
+        <x:v>Zauberboni nicht in physischen DPS.</x:v>
       </x:c>
       <x:c r="M62" s="44" t="str">
         <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
@@ -13497,13 +13787,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O62" s="54" t="n">
-        <x:v>0</x:v>
+        <x:v>-50</x:v>
       </x:c>
       <x:c r="P62" s="54" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q62" s="54" t="n">
-        <x:v>-125</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="R62" s="54" t="n">
         <x:v>0</x:v>
@@ -13524,7 +13814,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X62" s="44" t="n">
-        <x:v>250</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Y62" s="44" t="n">
         <x:v>1</x:v>
@@ -13538,7 +13828,7 @@
       </x:c>
       <x:c r="AB62" s="56" t="n">
         <x:f>IF($F$5+Q62&gt;=65000,1,1-1/(1+($F$5+Q62)/(60+$J$5*0.5)))</x:f>
-        <x:v>-2.1428571428571423</x:v>
+        <x:v>0.3125</x:v>
       </x:c>
       <x:c r="AC62" s="56" t="n">
         <x:f>IF($F$5+R62&gt;=65000,1,1-1/(1+($F$5+R62)/(60+$J$5*0.5)))</x:f>
@@ -13562,12 +13852,133 @@
       </x:c>
       <x:c r="AH62" s="56" t="n">
         <x:f>1-((5+$J$5*2)/(10+$J$5*2+MAX(0,$D$5+O62)))*(1/(1+MAX(0,$D$5+O62)/(90+$J$5*0.25)))</x:f>
-        <x:v>0.6462865716429107</x:v>
+        <x:v>0.45046620046620045</x:v>
       </x:c>
       <x:c r="AI62" s="44" t="str">
         <x:v>MAW-Stats</x:v>
       </x:c>
       <x:c r="AJ62" s="44" t="str">
+        <x:v>2d4+4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="50" customHeight="1">
+      <x:c r="A63" s="44" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B63" s="44" t="str">
+        <x:v>Mekorig's Hammer</x:v>
+      </x:c>
+      <x:c r="C63" s="44" t="str">
+        <x:v>Mace</x:v>
+      </x:c>
+      <x:c r="D63" s="44" t="str">
+        <x:v>MM7</x:v>
+      </x:c>
+      <x:c r="E63" s="50" t="n">
+        <x:f>ROUND(X63*Y63,0)</x:f>
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="F63" s="51" t="n">
+        <x:f>ROUND(($B$5+N63*$H$5+W63)/(1-(AH63/2+(AA63+AB63+AC63+AD63+AE63+AF63)/16+MIN(AA63:AF63)/8)),0)</x:f>
+        <x:v>2039</x:v>
+      </x:c>
+      <x:c r="G63" s="51" t="n">
+        <x:f>F63-$B$8</x:f>
+        <x:v>-1803</x:v>
+      </x:c>
+      <x:c r="H63" s="44" t="str">
+        <x:v>Nein</x:v>
+      </x:c>
+      <x:c r="I63" s="44" t="str">
+        <x:v>+75 Might, −100 Luftresistenz vor Levelskalierung.</x:v>
+      </x:c>
+      <x:c r="J63" s="44" t="str">
+        <x:v>Spirit-Magie +50 % des Basis-Skills (artifactSpellBonus); primär Hybrid-Zauberwaffe.</x:v>
+      </x:c>
+      <x:c r="K63" s="44" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="L63" s="44" t="str">
+        <x:v>Magiebonus nicht als Angriffsschaden eingerechnet.</x:v>
+      </x:c>
+      <x:c r="M63" s="44" t="str">
+        <x:v>https://github.com/Malekitsu/Maw-Mod-MMMerge/blob/4.5/Scripts/General/zzMaw-Items.lua</x:v>
+      </x:c>
+      <x:c r="N63" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O63" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P63" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q63" s="54" t="n">
+        <x:v>-125</x:v>
+      </x:c>
+      <x:c r="R63" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S63" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T63" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U63" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V63" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W63" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X63" s="44" t="n">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="Y63" s="44" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z63" s="44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA63" s="56" t="n">
+        <x:f>IF($F$5+P63&gt;=65000,1,1-1/(1+($F$5+P63)/(60+$J$5*0.5)))</x:f>
+        <x:v>0.3125</x:v>
+      </x:c>
+      <x:c r="AB63" s="56" t="n">
+        <x:f>IF($F$5+Q63&gt;=65000,1,1-1/(1+($F$5+Q63)/(60+$J$5*0.5)))</x:f>
+        <x:v>-2.1428571428571423</x:v>
+      </x:c>
+      <x:c r="AC63" s="56" t="n">
+        <x:f>IF($F$5+R63&gt;=65000,1,1-1/(1+($F$5+R63)/(60+$J$5*0.5)))</x:f>
+        <x:v>0.3125</x:v>
+      </x:c>
+      <x:c r="AD63" s="56" t="n">
+        <x:f>IF($F$5+S63&gt;=65000,1,1-1/(1+($F$5+S63)/(60+$J$5*0.5)))</x:f>
+        <x:v>0.3125</x:v>
+      </x:c>
+      <x:c r="AE63" s="56" t="n">
+        <x:f>IF($F$5+T63&gt;=65000,1,1-1/(1+($F$5+T63)/(60+$J$5*0.5)))</x:f>
+        <x:v>0.3125</x:v>
+      </x:c>
+      <x:c r="AF63" s="56" t="n">
+        <x:f>IF($F$5+U63&gt;=65000,1,1-1/(1+($F$5+U63)/(60+$J$5*0.5)))</x:f>
+        <x:v>0.3125</x:v>
+      </x:c>
+      <x:c r="AG63" s="56" t="n">
+        <x:f>IF($F$5+V63&gt;=65000,1,1-1/(1+($F$5+V63)/(60+$J$5*0.5)))</x:f>
+        <x:v>0.3125</x:v>
+      </x:c>
+      <x:c r="AH63" s="56" t="n">
+        <x:f>1-((5+$J$5*2)/(10+$J$5*2+MAX(0,$D$5+O63)))*(1/(1+MAX(0,$D$5+O63)/(90+$J$5*0.25)))</x:f>
+        <x:v>0.6462865716429107</x:v>
+      </x:c>
+      <x:c r="AI63" s="44" t="str">
+        <x:v>MAW-Stats + MAW-Zauberbonus</x:v>
+      </x:c>
+      <x:c r="AJ63" s="44" t="str">
         <x:v>2d5+15</x:v>
       </x:c>
     </x:row>
@@ -13576,11 +13987,13 @@
     <x:mergeCell ref="A1:M1"/>
     <x:mergeCell ref="A2:M2"/>
     <x:mergeCell ref="A3:M3"/>
+    <x:mergeCell ref="A4:M4"/>
     <x:mergeCell ref="A7:M7"/>
     <x:mergeCell ref="C8:M8"/>
     <x:mergeCell ref="A9:M9"/>
+    <x:mergeCell ref="A10:M10"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="E12:E62">
+  <x:conditionalFormatting sqref="E12:E63">
     <x:cfRule type="dataBar" priority="1">
       <x:dataBar>
         <x:cfvo type="min"/>
@@ -13594,7 +14007,7 @@
       </x:extLst>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="G12:G62">
+  <x:conditionalFormatting sqref="G12:G63">
     <x:cfRule type="colorScale" priority="2">
       <x:colorScale>
         <x:cfvo type="min"/>
@@ -13621,7 +14034,7 @@
               <x14:fillColor rgb="FF7AB6DE"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>E12:E62</xm:sqref>
+          <xm:sqref>E12:E63</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </x:ext>
